--- a/AI_LLM_Ethics_Living_Tracker.xlsx
+++ b/AI_LLM_Ethics_Living_Tracker.xlsx
@@ -22,16 +22,16 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2026 Only'!$A$4:$R$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2026 Reading Library'!$A$4:$R$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'New This Week'!$A$4:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'New This Week'!$A$4:$M$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Policy &amp; Regulation'!$A$4:$R$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Review Queue'!$A$4:$M$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Review Queue'!$A$4:$M$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2532" uniqueCount="761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2559" uniqueCount="767">
   <si>
     <t>AI &amp; LLM Ethics — Living Literature Dashboard</t>
   </si>
@@ -111,2113 +111,2131 @@
     <t>Run time</t>
   </si>
   <si>
+    <t>2026-08-16T07:39:54+00:00</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>scheduled/manual</t>
+  </si>
+  <si>
+    <t>Sources checked</t>
+  </si>
+  <si>
+    <t>Candidates fetched</t>
+  </si>
+  <si>
+    <t>New after dedupe</t>
+  </si>
+  <si>
+    <t>Errors / notes</t>
+  </si>
+  <si>
+    <t>Policy/IndiaAI Safe &amp; Trusted AI: HTTPError: 403 Client Error: Forbidden for url: https://indiaai.gov.in/hub/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>Start Here — 2026-aware AI &amp; LLM Ethics Reading Path</t>
+  </si>
+  <si>
+    <t>Use this sheet for a compact orientation. The automated discovery tabs are intentionally separate from the stable reading path.</t>
+  </si>
+  <si>
+    <t>Curated sources</t>
+  </si>
+  <si>
+    <t>2026 sources</t>
+  </si>
+  <si>
+    <t>Must Read</t>
+  </si>
+  <si>
+    <t>Official / institutional</t>
+  </si>
+  <si>
+    <t>Recommended 10-source reading path</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Read this</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Why now</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Source URL</t>
+  </si>
+  <si>
+    <t>Responsible AI | The 2026 AI Index Report</t>
+  </si>
+  <si>
+    <t>Current 2025–2026 evidence or governance update</t>
+  </si>
+  <si>
+    <t>https://hai.stanford.edu/ai-index/2026-ai-index-report/responsible-ai</t>
+  </si>
+  <si>
+    <t>AI Act | Shaping Europe's digital future</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/regulatory-framework-ai</t>
+  </si>
+  <si>
+    <t>Guidelines on transparency obligations for providers and deployers of AI systems</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-transparency-ai-generated-content</t>
+  </si>
+  <si>
+    <t>Persuasion with Large Language Models: A Survey of Empirical Studies</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2411.06837v2</t>
+  </si>
+  <si>
+    <t>Emotional Support with Conversational AI: Talking to Machines About Life</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2603.22618v1</t>
+  </si>
+  <si>
+    <t>An Evaluation of AI Companion Apps</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2605.08093v2</t>
+  </si>
+  <si>
+    <t>Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2606.04150</t>
+  </si>
+  <si>
+    <t>Towards Agentic AI Governance: A Preliminary Assessment</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2607.07612</t>
+  </si>
+  <si>
+    <t>The 2025 Foundation Model Transparency Index</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2512.10169</t>
+  </si>
+  <si>
+    <t>India AI Governance Guidelines: Empowering Ethical and Responsible AI</t>
+  </si>
+  <si>
+    <t>https://indiaai.gov.in/article/india-ai-governance-guidelines-empowering-ethical-and-responsible-ai</t>
+  </si>
+  <si>
+    <t>Ethics of Artificial Intelligence &amp; LLMs — Curated Reading Library</t>
+  </si>
+  <si>
+    <t>Stable curated sources. Automatically discovered items are triaged separately before promotion.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Subtopic</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Author / Body</t>
+  </si>
+  <si>
+    <t>Source Type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>What it covers</t>
+  </si>
+  <si>
+    <t>Why the reader benefits</t>
+  </si>
+  <si>
+    <t>Best use</t>
+  </si>
+  <si>
+    <t>2026 Relevance Score</t>
+  </si>
+  <si>
+    <t>Read Priority</t>
+  </si>
+  <si>
+    <t>Region / Scope</t>
+  </si>
+  <si>
+    <t>Key ethical question</t>
+  </si>
+  <si>
+    <t>Notes / status</t>
+  </si>
+  <si>
+    <t>Reader mode</t>
+  </si>
+  <si>
+    <t>Responsible AI state of the field</t>
+  </si>
+  <si>
+    <t>Stanford HAI / AI Index</t>
+  </si>
+  <si>
+    <t>Annual evidence report</t>
+  </si>
+  <si>
+    <t>Institutional / data-driven</t>
+  </si>
+  <si>
+    <t>Tracks AI incidents, safety evaluation, transparency, responsible-AI reporting, and the widening gap between capability and governance.</t>
+  </si>
+  <si>
+    <t>Best current snapshot for showing that AI capability is advancing faster than safety measurement and transparency.</t>
+  </si>
+  <si>
+    <t>Lecture opener; literature review motivation; 2026 statistics</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Are current evaluation and governance systems keeping pace with frontier AI capability?</t>
+  </si>
+  <si>
+    <t>2026 edition; strong source for current facts and figures.</t>
+  </si>
+  <si>
+    <t>Read closely</t>
+  </si>
+  <si>
+    <t>Foundation model transparency</t>
+  </si>
+  <si>
+    <t>Wan et al. / Stanford CRFM</t>
+  </si>
+  <si>
+    <t>Research report / index</t>
+  </si>
+  <si>
+    <t>Research report</t>
+  </si>
+  <si>
+    <t>Scores major foundation-model developers on disclosures covering data, compute, risk mitigation, usage and downstream impacts.</t>
+  </si>
+  <si>
+    <t>Lets readers move from vague calls for transparency to measurable disclosure dimensions and compare developers.</t>
+  </si>
+  <si>
+    <t>Transparency section; accountability case study; assignment</t>
+  </si>
+  <si>
+    <t>Global / industry</t>
+  </si>
+  <si>
+    <t>What information should frontier-model developers be required to disclose?</t>
+  </si>
+  <si>
+    <t>Average score fell from 58/100 in 2024 to 40/100 in 2025.</t>
+  </si>
+  <si>
+    <t>EU AI Act implementation</t>
+  </si>
+  <si>
+    <t>European Commission</t>
+  </si>
+  <si>
+    <t>Regulation / official guidance</t>
+  </si>
+  <si>
+    <t>Official</t>
+  </si>
+  <si>
+    <t>Official overview of the EU AI Act, risk-based obligations, implementation timeline, GPAI rules and transparency requirements.</t>
+  </si>
+  <si>
+    <t>Provides the clearest bridge between ethics principles and enforceable legal duties in 2026.</t>
+  </si>
+  <si>
+    <t>Regulation module; compliance discussion; policy comparison</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>When should ethical expectations become legal obligations?</t>
+  </si>
+  <si>
+    <t>General application date: 2 August 2026, with exceptions and phased provisions.</t>
+  </si>
+  <si>
+    <t>AI-generated content disclosure</t>
+  </si>
+  <si>
+    <t>Regulatory guidance</t>
+  </si>
+  <si>
+    <t>Explains Article 50 duties concerning user disclosure, machine-readable marking, AI-generated content and deepfakes.</t>
+  </si>
+  <si>
+    <t>Useful concrete example of how transparency ethics becomes a product-design requirement.</t>
+  </si>
+  <si>
+    <t>Deepfakes; disclosure; generative-AI product design</t>
+  </si>
+  <si>
+    <t>Should people always know when they are interacting with AI or seeing AI-generated content?</t>
+  </si>
+  <si>
+    <t>Article 50 applies from 2 August 2026.</t>
+  </si>
+  <si>
+    <t>General-purpose AI obligations</t>
+  </si>
+  <si>
+    <t>Guidelines for providers of general-purpose AI models</t>
+  </si>
+  <si>
+    <t>Clarifies obligations for providers of general-purpose AI models and the Commission's enforcement role.</t>
+  </si>
+  <si>
+    <t>Gives readers a current compliance perspective on frontier and general-purpose models rather than generic AI regulation.</t>
+  </si>
+  <si>
+    <t>GPAI governance; provider responsibilities; seminar discussion</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>What extra duties should apply to powerful general-purpose models?</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-gpai-providers</t>
+  </si>
+  <si>
+    <t>Commission enforcement powers apply from 2 August 2026.</t>
+  </si>
+  <si>
+    <t>Read/skim</t>
+  </si>
+  <si>
+    <t>India AI governance</t>
+  </si>
+  <si>
+    <t>IndiaAI / MeitY</t>
+  </si>
+  <si>
+    <t>National governance guidance</t>
+  </si>
+  <si>
+    <t>Sets out principles and recommendations around fairness, accountability, safety, inclusivity and trustworthy AI in India.</t>
+  </si>
+  <si>
+    <t>Adds an India-specific governance perspective and prevents the reading list from being US/EU-centric.</t>
+  </si>
+  <si>
+    <t>India case study; policy comparison; local context</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>How should responsible AI governance reflect India's scale, diversity and public-interest priorities?</t>
+  </si>
+  <si>
+    <t>Released 5 Nov 2025 under the IndiaAI Mission.</t>
+  </si>
+  <si>
+    <t>AI safety capacity</t>
+  </si>
+  <si>
+    <t>Safe &amp; Trusted AI Working Group</t>
+  </si>
+  <si>
+    <t>India AI Impact Summit</t>
+  </si>
+  <si>
+    <t>Policy / working-group output</t>
+  </si>
+  <si>
+    <t>Focuses on AI safety capacity, evaluation, governance and incorporating Global South perspectives into international AI safety frameworks.</t>
+  </si>
+  <si>
+    <t>Useful for understanding how safety debates are being localized beyond US/EU institutions.</t>
+  </si>
+  <si>
+    <t>India 2026 update; global governance; discussion prompt</t>
+  </si>
+  <si>
+    <t>India / Global South</t>
+  </si>
+  <si>
+    <t>Who gets to define acceptable AI risk and safety standards globally?</t>
+  </si>
+  <si>
+    <t>https://impact.indiaai.gov.in/working-groups/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>2026-relevant IndiaAI Impact Summit initiative.</t>
+  </si>
+  <si>
+    <t>Risk management framework</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1)</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>Risk-management framework</t>
+  </si>
+  <si>
+    <t>Identifies GenAI-specific risks and actions across the AI lifecycle, aligned with Govern, Map, Measure and Manage.</t>
+  </si>
+  <si>
+    <t>One of the most practical sources for converting ethical concerns into operational risk controls.</t>
+  </si>
+  <si>
+    <t>Risk register; deployment checklist; governance design</t>
+  </si>
+  <si>
+    <t>United States / cross-sector</t>
+  </si>
+  <si>
+    <t>How can an organization operationalize trustworthy GenAI rather than merely state principles?</t>
+  </si>
+  <si>
+    <t>https://www.nist.gov/publications/artificial-intelligence-risk-management-framework-generative-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>Companion to NIST AI RMF 1.0.</t>
+  </si>
+  <si>
+    <t>Human-rights-centered AI ethics</t>
+  </si>
+  <si>
+    <t>Recommendation on the Ethics of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>UNESCO</t>
+  </si>
+  <si>
+    <t>International ethics standard</t>
+  </si>
+  <si>
+    <t>Defines principles including proportionality, do-no-harm, safety, privacy, fairness, transparency, accountability, sustainability and human oversight.</t>
+  </si>
+  <si>
+    <t>Provides a normative foundation for almost every later AI ethics topic.</t>
+  </si>
+  <si>
+    <t>Foundations lecture; ethics framework; compare policies</t>
+  </si>
+  <si>
+    <t>What values should guide the design and deployment of AI systems?</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
+  </si>
+  <si>
+    <t>Global UNESCO recommendation; remains foundational in 2026.</t>
+  </si>
+  <si>
+    <t>Trustworthy AI principles</t>
+  </si>
+  <si>
+    <t>OECD AI Principles</t>
+  </si>
+  <si>
+    <t>OECD</t>
+  </si>
+  <si>
+    <t>International policy principles</t>
+  </si>
+  <si>
+    <t>Principles for innovative and trustworthy AI, covering human rights, fairness, transparency, robustness, security and accountability.</t>
+  </si>
+  <si>
+    <t>Concise policy baseline that is easy to compare against NIST, UNESCO, EU and national frameworks.</t>
+  </si>
+  <si>
+    <t>Framework comparison; policy lecture; exam preparation</t>
+  </si>
+  <si>
+    <t>What minimum principles should trustworthy AI systems satisfy across countries?</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/ai-principles</t>
+  </si>
+  <si>
+    <t>Initially adopted 2019; updated May 2024.</t>
+  </si>
+  <si>
+    <t>International AI treaty</t>
+  </si>
+  <si>
+    <t>Framework Convention on Artificial Intelligence and Human Rights, Democracy and the Rule of Law</t>
+  </si>
+  <si>
+    <t>Council of Europe</t>
+  </si>
+  <si>
+    <t>International treaty</t>
+  </si>
+  <si>
+    <t>Official / legally binding framework</t>
+  </si>
+  <si>
+    <t>Addresses human rights, democratic processes, autonomy, transparency, accountability, equality and privacy across the AI lifecycle.</t>
+  </si>
+  <si>
+    <t>Shows the transition from voluntary ethics to treaty-based human-rights obligations.</t>
+  </si>
+  <si>
+    <t>Human-rights module; legal governance; global policy</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>How should AI development be constrained when it may affect fundamental rights and democratic institutions?</t>
+  </si>
+  <si>
+    <t>https://www.coe.int/en/web/artificial-intelligence/the-framework-convention-on-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>First international legally binding treaty in this field; opened for signature 5 Sept 2024.</t>
+  </si>
+  <si>
+    <t>Developer risk reporting</t>
+  </si>
+  <si>
+    <t>How are AI developers managing risks? Insights from the Hiroshima AI Process reporting framework</t>
+  </si>
+  <si>
+    <t>International governance report</t>
+  </si>
+  <si>
+    <t>Official / multi-stakeholder</t>
+  </si>
+  <si>
+    <t>Analyzes how organizations report risk identification, safety, governance, content authentication and accountability practices.</t>
+  </si>
+  <si>
+    <t>Gives concrete examples of how frontier developers operationalize risk management, not just what principles say.</t>
+  </si>
+  <si>
+    <t>Industry governance; transparency; comparative analysis</t>
+  </si>
+  <si>
+    <t>G7 / global</t>
+  </si>
+  <si>
+    <t>Can voluntary transparency meaningfully improve accountability for advanced AI developers?</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/ai-publications/how-are-ai-developers-managing-risks-insights-from-responses-to-the-reporting-framework-of-the-hiroshima-ai-process-code-of-conduct</t>
+  </si>
+  <si>
+    <t>Reporting framework launched in 2025.</t>
+  </si>
+  <si>
+    <t>Comprehensive LLM ethics</t>
+  </si>
+  <si>
+    <t>Deconstructing the ethics of large language models from long-standing issues to new-emerging dilemmas</t>
+  </si>
+  <si>
+    <t>Deng et al.</t>
+  </si>
+  <si>
+    <t>Survey / review</t>
+  </si>
+  <si>
+    <t>Peer-reviewed</t>
+  </si>
+  <si>
+    <t>Surveys copyright, systematic bias, privacy, truthfulness, social norms and emerging ethical challenges of LLMs.</t>
+  </si>
+  <si>
+    <t>Good single-paper orientation before readers enter specialized literatures.</t>
+  </si>
+  <si>
+    <t>Literature review starting point; seminar reading</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Which LLM ethical risks are old problems amplified by scale, and which are genuinely new?</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s43681-025-00797-3</t>
+  </si>
+  <si>
+    <t>Published in AI and Ethics.</t>
+  </si>
+  <si>
+    <t>Bias evaluation and mitigation</t>
+  </si>
+  <si>
+    <t>Bias and Fairness in Large Language Models: A Survey</t>
+  </si>
+  <si>
+    <t>Gallegos et al.</t>
+  </si>
+  <si>
+    <t>Survey</t>
+  </si>
+  <si>
+    <t>Research / arXiv</t>
+  </si>
+  <si>
+    <t>Organizes social bias harms, evaluation metrics, datasets and mitigation techniques for LLMs.</t>
+  </si>
+  <si>
+    <t>Provides a technical taxonomy that makes 'AI bias' measurable rather than purely rhetorical.</t>
+  </si>
+  <si>
+    <t>Bias lecture; evaluation design; related work</t>
+  </si>
+  <si>
+    <t>How should fairness be defined and measured for generative language systems?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2309.00770</t>
+  </si>
+  <si>
+    <t>Still a useful technical survey in 2026.</t>
+  </si>
+  <si>
+    <t>Hallucination taxonomy</t>
+  </si>
+  <si>
+    <t>A Survey on Hallucination in Large Language Models</t>
+  </si>
+  <si>
+    <t>ACM Computing Surveys</t>
+  </si>
+  <si>
+    <t>Reviews hallucination principles, taxonomies, causes, evaluation, detection and mitigation in LLMs.</t>
+  </si>
+  <si>
+    <t>Helps distinguish factual reliability problems from broader moral or social harms.</t>
+  </si>
+  <si>
+    <t>Truthfulness; reliability; high-stakes deployment</t>
+  </si>
+  <si>
+    <t>When is an incorrect LLM output merely an error, and when does it become an ethical harm?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3703155</t>
+  </si>
+  <si>
+    <t>High-value technical survey.</t>
+  </si>
+  <si>
+    <t>Training-data leakage</t>
+  </si>
+  <si>
+    <t>New Privacy Risks for Large Language Models</t>
+  </si>
+  <si>
+    <t>Research paper</t>
+  </si>
+  <si>
+    <t>Preprint / current research</t>
+  </si>
+  <si>
+    <t>Examines data extraction and memorization risks, connecting privacy leakage with copyright and training-data provenance concerns.</t>
+  </si>
+  <si>
+    <t>Useful 2026 update showing privacy risk is not limited to classic membership inference.</t>
+  </si>
+  <si>
+    <t>Privacy section; training data; model memorization</t>
+  </si>
+  <si>
+    <t>What does a model owe people whose private or copyrighted data it can reproduce?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2509.14278v2</t>
+  </si>
+  <si>
+    <t>Version available Jan 2026.</t>
+  </si>
+  <si>
+    <t>Privacy threat landscape</t>
+  </si>
+  <si>
+    <t>SoK: The Privacy Paradox of Large Language Models</t>
+  </si>
+  <si>
+    <t>Systematization of knowledge</t>
+  </si>
+  <si>
+    <t>Preprint / research</t>
+  </si>
+  <si>
+    <t>Systematizes training-data extraction, reconstruction, inference-time privacy and protection mechanisms.</t>
+  </si>
+  <si>
+    <t>Gives readers a map of privacy attack surfaces instead of isolated examples.</t>
+  </si>
+  <si>
+    <t>Security/privacy module; research gap identification</t>
+  </si>
+  <si>
+    <t>Can LLM utility and strong privacy guarantees be achieved simultaneously?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2506.12699v2</t>
+  </si>
+  <si>
+    <t>Useful bridge between AI ethics and security.</t>
+  </si>
+  <si>
+    <t>Empirical privacy evaluation</t>
+  </si>
+  <si>
+    <t>Privacy Auditing of Large Language Models</t>
+  </si>
+  <si>
+    <t>Develops stronger privacy auditing techniques and more effective canaries for estimating empirical leakage.</t>
+  </si>
+  <si>
+    <t>Shows readers how privacy claims can be tested rather than assumed.</t>
+  </si>
+  <si>
+    <t>Methodology; model audit; technical assignment</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>How should developers demonstrate that a language model is not leaking training data?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2503.06808v1</t>
+  </si>
+  <si>
+    <t>Technical privacy-auditing work.</t>
+  </si>
+  <si>
+    <t>Reference as needed</t>
+  </si>
+  <si>
+    <t>Agent memory and contextual leakage</t>
+  </si>
+  <si>
+    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory</t>
+  </si>
+  <si>
+    <t>Security research</t>
+  </si>
+  <si>
+    <t>Studies privacy leakage from inference-time contextual memory in LLM agents, beyond training-data privacy.</t>
+  </si>
+  <si>
+    <t>Important for 2026 because persistent AI assistants and agents create a new privacy attack surface.</t>
+  </si>
+  <si>
+    <t>Agentic AI; memory privacy; security discussion</t>
+  </si>
+  <si>
+    <t>Research / agents</t>
+  </si>
+  <si>
+    <t>What privacy risks appear when AI systems remember and act on user context over time?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2604.23711v1</t>
+  </si>
+  <si>
+    <t>2026 agent-memory privacy paper.</t>
+  </si>
+  <si>
+    <t>Persuasion landscape</t>
+  </si>
+  <si>
+    <t>Research survey</t>
+  </si>
+  <si>
+    <t>Reviews empirical evidence on automated, personalized and interactive LLM persuasion and its effects on attitudes and behavior.</t>
+  </si>
+  <si>
+    <t>A direct entry point into one of the most important newer AI-ethics issues.</t>
+  </si>
+  <si>
+    <t>Manipulation lecture; social influence; governance</t>
+  </si>
+  <si>
+    <t>When does helpful persuasion become manipulation or undue influence?</t>
+  </si>
+  <si>
+    <t>Updated Apr 2026.</t>
+  </si>
+  <si>
+    <t>Human vs AI persuasion</t>
+  </si>
+  <si>
+    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders</t>
+  </si>
+  <si>
+    <t>Schoenegger et al.</t>
+  </si>
+  <si>
+    <t>Large-scale experiment</t>
+  </si>
+  <si>
+    <t>Compares a frontier LLM with incentivized human persuaders in interactive settings and measures compliance with correct and incorrect persuasion.</t>
+  </si>
+  <si>
+    <t>Provides concrete empirical evidence that persuasive capability can create both benefits and harms.</t>
+  </si>
+  <si>
+    <t>Case study; empirical evidence; class discussion</t>
+  </si>
+  <si>
+    <t>Should systems with human-level or greater persuasive power face special safeguards?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2505.09662</t>
+  </si>
+  <si>
+    <t>Preregistered, large-scale incentivized experiment.</t>
+  </si>
+  <si>
+    <t>Harmful influence evaluation</t>
+  </si>
+  <si>
+    <t>Evaluating Language Models for Harmful Manipulation</t>
+  </si>
+  <si>
+    <t>Akbulut et al.</t>
+  </si>
+  <si>
+    <t>Human-subject evaluation</t>
+  </si>
+  <si>
+    <t>Research / preprint</t>
+  </si>
+  <si>
+    <t>Introduces a framework for measuring harmful manipulation across public policy, finance and health with participants from multiple countries.</t>
+  </si>
+  <si>
+    <t>Shows how manipulation can be operationalized and evaluated across consequential domains.</t>
+  </si>
+  <si>
+    <t>Evaluation design; high-stakes AI; cross-country analysis</t>
+  </si>
+  <si>
+    <t>US / UK / India</t>
+  </si>
+  <si>
+    <t>How can harmful manipulation be measured before deployment?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2603.25326</t>
+  </si>
+  <si>
+    <t>Includes 10,101 participants across three locales.</t>
+  </si>
+  <si>
+    <t>Sycophancy to strategic deception</t>
+  </si>
+  <si>
+    <t>From Sycophancy to Deception: A Unified Taxonomy for Misleading LLM Behavior</t>
+  </si>
+  <si>
+    <t>Taxonomy / research</t>
+  </si>
+  <si>
+    <t>Unifies hallucination, omission, pragmatic distortion, sycophancy and strategic deception under a common taxonomy of misleading behavior.</t>
+  </si>
+  <si>
+    <t>Helps readers avoid treating all misleading model outputs as the same failure mode.</t>
+  </si>
+  <si>
+    <t>Conceptual framework; deception; research taxonomy</t>
+  </si>
+  <si>
+    <t>Does intent or goal-directedness change how ethically serious misleading AI behavior is?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2604.04788</t>
+  </si>
+  <si>
+    <t>Current 2026 taxonomy.</t>
+  </si>
+  <si>
+    <t>Sycophancy</t>
+  </si>
+  <si>
+    <t>Sycophancy in Large Language Models: Causes and Mitigations</t>
+  </si>
+  <si>
+    <t>Lars Malmqvist</t>
+  </si>
+  <si>
+    <t>Technical survey</t>
+  </si>
+  <si>
+    <t>Surveys excessive agreement with users, causes, measurement and mitigation, and links sycophancy to hallucination and bias.</t>
+  </si>
+  <si>
+    <t>Useful for discussing why 'agreeable' assistants can become epistemically unsafe.</t>
+  </si>
+  <si>
+    <t>Alignment; user trust; truthfulness</t>
+  </si>
+  <si>
+    <t>Should an assistant prioritize user satisfaction or epistemic honesty when they conflict?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2411.15287</t>
+  </si>
+  <si>
+    <t>Technical survey.</t>
+  </si>
+  <si>
+    <t>Emotional support</t>
+  </si>
+  <si>
+    <t>Huang, Stodolska &amp; Sultana</t>
+  </si>
+  <si>
+    <t>Qualitative HCI research</t>
+  </si>
+  <si>
+    <t>Analyzes how emotional support is co-constructed with AI companions and tensions such as support vs dependency and validation vs delusion.</t>
+  </si>
+  <si>
+    <t>Provides nuanced evidence beyond simplistic claims that AI companions are either beneficial or harmful.</t>
+  </si>
+  <si>
+    <t>HCI ethics; mental-health-adjacent discussion; companionship</t>
+  </si>
+  <si>
+    <t>How should AI offer emotional support without reinforcing dependency or harmful beliefs?</t>
+  </si>
+  <si>
+    <t>2026 HCI-focused research.</t>
+  </si>
+  <si>
+    <t>Companion-app design</t>
+  </si>
+  <si>
+    <t>Empirical audit</t>
+  </si>
+  <si>
+    <t>Audits popular AI companion apps for dark patterns, anthropomorphism, stereotypes, erotica and technical issues.</t>
+  </si>
+  <si>
+    <t>Connects ethical risk to actual interface and monetization design choices, not only model behavior.</t>
+  </si>
+  <si>
+    <t>Product ethics; dark patterns; companion AI</t>
+  </si>
+  <si>
+    <t>EU / UK market</t>
+  </si>
+  <si>
+    <t>Can product incentives push AI companions toward manipulative engagement?</t>
+  </si>
+  <si>
+    <t>Version updated Aug 2026.</t>
+  </si>
+  <si>
+    <t>Emotional dependence</t>
+  </si>
+  <si>
+    <t>Shi et al.</t>
+  </si>
+  <si>
+    <t>Perspective / evidence synthesis</t>
+  </si>
+  <si>
+    <t>Argues that emotional dependence can emerge incidentally in general-purpose AI use and may alter future preferences for human vs AI support.</t>
+  </si>
+  <si>
+    <t>Highlights cumulative interaction effects that one-shot safety evaluations can miss.</t>
+  </si>
+  <si>
+    <t>Long-term interaction ethics; product policy; research gaps</t>
+  </si>
+  <si>
+    <t>Should general-purpose assistants be evaluated for long-term relational effects, not just single-turn harms?</t>
+  </si>
+  <si>
+    <t>Includes synthesis of longitudinal evidence.</t>
+  </si>
+  <si>
+    <t>Identity and parasocial interaction</t>
+  </si>
+  <si>
+    <t>Negotiating Digital Identities with AI Companions</t>
+  </si>
+  <si>
+    <t>HCI / computational social science</t>
+  </si>
+  <si>
+    <t>Studies identity construction and negotiation in AI-companion communities using large-scale online discussions.</t>
+  </si>
+  <si>
+    <t>Useful for understanding anthropomorphism and dependence as social processes rather than merely UI bugs.</t>
+  </si>
+  <si>
+    <t>HCI seminar; identity; anthropomorphism</t>
+  </si>
+  <si>
+    <t>How do AI companions reshape users' identities, expectations and social relationships?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2601.12181v1</t>
+  </si>
+  <si>
+    <t>Analyzes 22,374 online discussions.</t>
+  </si>
+  <si>
+    <t>Governance of autonomous agents</t>
+  </si>
+  <si>
+    <t>Raji &amp; Bashir</t>
+  </si>
+  <si>
+    <t>Systematic review</t>
+  </si>
+  <si>
+    <t>Reviews governance priorities, mechanisms and stakeholder roles for AI systems that autonomously plan and execute tasks.</t>
+  </si>
+  <si>
+    <t>Important 2026 bridge from chatbot ethics to systems that can act in the world.</t>
+  </si>
+  <si>
+    <t>Agentic AI governance; research agenda; seminar</t>
+  </si>
+  <si>
+    <t>How should accountability change when AI can plan, call tools and execute actions autonomously?</t>
+  </si>
+  <si>
+    <t>Published Jul 2026.</t>
+  </si>
+  <si>
+    <t>Security and governance practice</t>
+  </si>
+  <si>
+    <t>State of Agentic AI Security and Governance</t>
+  </si>
+  <si>
+    <t>OWASP GenAI Security Project</t>
+  </si>
+  <si>
+    <t>Security / governance report</t>
+  </si>
+  <si>
+    <t>Practitioner standard</t>
+  </si>
+  <si>
+    <t>Covers governance and security issues for autonomous AI systems, including controls, oversight and operational risk.</t>
+  </si>
+  <si>
+    <t>Gives practitioners a deployment-oriented complement to academic governance work.</t>
+  </si>
+  <si>
+    <t>Agent security; enterprise governance; checklist design</t>
+  </si>
+  <si>
+    <t>What controls are necessary when agents receive tools, permissions and persistent access?</t>
+  </si>
+  <si>
+    <t>https://genai.owasp.org/resource/state-of-agentic-ai-security-and-governance/</t>
+  </si>
+  <si>
+    <t>Practitioner-focused resource.</t>
+  </si>
+  <si>
+    <t>AI in education ethics</t>
+  </si>
+  <si>
+    <t>AI and the future of education: Disruptions, dilemmas and directions</t>
+  </si>
+  <si>
+    <t>Policy / anthology</t>
+  </si>
+  <si>
+    <t>Official / expert collection</t>
+  </si>
+  <si>
+    <t>Explores philosophical, ethical and pedagogical dilemmas created by AI in education and human-machine co-creation.</t>
+  </si>
+  <si>
+    <t>Useful domain case study showing how general AI-ethics principles change in a real institution such as education.</t>
+  </si>
+  <si>
+    <t>Education case study; classroom discussion; policy</t>
+  </si>
+  <si>
+    <t>How should education preserve human agency, fairness and learning integrity in an AI-rich environment?</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/articles/ai-and-future-education-disruptions-dilemmas-and-directions</t>
+  </si>
+  <si>
+    <t>Published Jan 2026.</t>
+  </si>
+  <si>
+    <t>Scale, data and social harms</t>
+  </si>
+  <si>
+    <t>On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
+  </si>
+  <si>
+    <t>Bender et al.</t>
+  </si>
+  <si>
+    <t>FAccT research paper</t>
+  </si>
+  <si>
+    <t>Raises concerns about environmental cost, training-data scale, bias, documentation and the gap between linguistic form and meaning.</t>
+  </si>
+  <si>
+    <t>Foundational critical reading that explains why ethics concerns were present before today's frontier LLMs.</t>
+  </si>
+  <si>
+    <t>Historical foundation; data ethics; critical perspective</t>
+  </si>
+  <si>
+    <t>Does scaling language models without understanding data and social context create predictable harms?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3442188.3445922</t>
+  </si>
+  <si>
+    <t>FAccT 2021; foundational.</t>
+  </si>
+  <si>
+    <t>Language-model harm taxonomy</t>
+  </si>
+  <si>
+    <t>Ethical and Social Risks of Harm from Language Models</t>
+  </si>
+  <si>
+    <t>Weidinger et al.</t>
+  </si>
+  <si>
+    <t>Risk taxonomy / research</t>
+  </si>
+  <si>
+    <t>Organizes harms around discrimination, information hazards, misinformation, malicious use, human-computer interaction and socioeconomic/environmental harms.</t>
+  </si>
+  <si>
+    <t>One of the clearest early taxonomies for turning 'LLM ethics' into categories of harm.</t>
+  </si>
+  <si>
+    <t>Foundations; risk taxonomy; related work</t>
+  </si>
+  <si>
+    <t>What types of harm can language models create, and through which pathways?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2112.04359</t>
+  </si>
+  <si>
+    <t>Published work originated from DeepMind research.</t>
+  </si>
+  <si>
+    <t>Foundation-model societal impact</t>
+  </si>
+  <si>
+    <t>On the Opportunities and Risks of Foundation Models</t>
+  </si>
+  <si>
+    <t>Bommasani et al.</t>
+  </si>
+  <si>
+    <t>Examines foundation models across capabilities, homogenization, adaptation, evaluation, robustness, security, fairness, misuse, law and societal impact.</t>
+  </si>
+  <si>
+    <t>Provides broad conceptual background for why one upstream model can propagate benefits and harms across many downstream systems.</t>
+  </si>
+  <si>
+    <t>Foundation models; societal impact; literature review</t>
+  </si>
+  <si>
+    <t>How does reliance on a small number of foundation models concentrate systemic risk?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2108.07258</t>
+  </si>
+  <si>
+    <t>Stanford CRFM foundational report.</t>
+  </si>
+  <si>
+    <t>New This Week — Automatically Discovered</t>
+  </si>
+  <si>
+    <t>Recent high-scoring discoveries from scholarly APIs and official policy pages.</t>
+  </si>
+  <si>
+    <t>Detected</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Importance Score</t>
+  </si>
+  <si>
+    <t>Why flagged</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>A Common Standard for AI Incident Accountability</t>
+  </si>
+  <si>
+    <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>Must Read Candidate</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, accountability, disclosure, reporting; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21907857</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21907857</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Automatically discovered; verify bibliographic details before formal citation.</t>
+  </si>
+  <si>
+    <t>Autonomous Decision Assurance Layer for AI-Driven Enterprise Analytics: Bridging Governance, Multi-Agent AI, and Executive Decision Intelligence in Saudi Vision 2030 Organizations</t>
+  </si>
+  <si>
+    <t>International Journal for Research in Applied Science and Engineering Technology</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.22214/ijraset.2026.84573</t>
+  </si>
+  <si>
+    <t>10.22214/ijraset.2026.84573</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21907856</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21907856</t>
+  </si>
+  <si>
+    <t>Sustainability and Environmental Ethics in Sanskrit Texts: A Geographical Perspective</t>
+  </si>
+  <si>
+    <t>Environment &amp; Labor</t>
+  </si>
+  <si>
+    <t>Prantik Gabeshana Patrika</t>
+  </si>
+  <si>
+    <t>journal-article</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: water, environment, sustainability; strong scholarly metadata source; impact signal: framework, guidelines, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.67841/pgp.260501082</t>
+  </si>
+  <si>
+    <t>10.67841/pgp.260501082</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>Validating the Virtue Ethics Measurement Scale Within an Open Distance e-Learning Higher Education Institution in South Africa: Students’ Perspectives of Generative AI Practices</t>
+  </si>
+  <si>
+    <t>Algorithms</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/a19080682</t>
+  </si>
+  <si>
+    <t>10.3390/a19080682</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>Examining the Impact of Social-Emotional Learning on Academic Achievement in African American Middle School Girls</t>
+  </si>
+  <si>
+    <t>Seton Hall University eRepository (Seton Hall University)</t>
+  </si>
+  <si>
+    <t>dissertation</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://openalex.org/W7160680247</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>Managing ESG and cyber risks in Kazakhstan’s low-carbon transition by aligning EU and Chinese standards through demoethics</t>
+  </si>
+  <si>
+    <t>Discover Sustainability</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, sustainability; impact signal: framework, standard, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s43621-026-04260-z</t>
+  </si>
+  <si>
+    <t>10.1007/s43621-026-04260-z</t>
+  </si>
+  <si>
+    <t>Digital personas of AI use in nursing education: a latent class analysis of learning behaviors and academic engagement</t>
+  </si>
+  <si>
+    <t>Frontiers in Medicine</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fmed.2026.1859093</t>
+  </si>
+  <si>
+    <t>10.3389/fmed.2026.1859093</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>Beyond Visual Evidence: Revealing and Mitigating Relational Privacy Leakage in Document MLLMs</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>matches Privacy: privacy, leakage, extraction; impact signal: benchmark, framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12911v1</t>
+  </si>
+  <si>
+    <t>10.1145/3767308.3835901</t>
+  </si>
+  <si>
+    <t>Performance, interaction, and ethical evaluation in the use of generative artificial intelligence in engineering education</t>
+  </si>
+  <si>
+    <t>Education and Information Technologies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, regulation, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10639-026-14112-y</t>
+  </si>
+  <si>
+    <t>10.1007/s10639-026-14112-y</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>How Personal and Cognitive Traits Influence AI Attitudes, Ethics, and Well-being: The Role of AI Autonomy and Criticality in Design</t>
+  </si>
+  <si>
+    <t>SN Computer Science</t>
+  </si>
+  <si>
+    <t>matches Persuasion &amp; Manipulation: influence, autonomy; impact signal: survey, framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s42979-026-05214-y</t>
+  </si>
+  <si>
+    <t>10.1007/s42979-026-05214-y</t>
+  </si>
+  <si>
+    <t>Ethics Suppression in AI Development: A Comparative Case Study of Responsible AI Under Competitive Pressure</t>
+  </si>
+  <si>
+    <t>International Journal of Applied Research in Business and Management</t>
+  </si>
+  <si>
+    <t>matches Foundations: ethics, responsible ai; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51137/wrp.ijarbm.869</t>
+  </si>
+  <si>
+    <t>10.51137/wrp.ijarbm.869</t>
+  </si>
+  <si>
+    <t>Which LLM Is Your Ideal Companion? Evaluating Emotional Companion Capabilities of LLMs Based on Adult Attachment Theory</t>
+  </si>
+  <si>
+    <t>matches Human-AI Relationships: companion, emotional support, attachment; impact signal: benchmark, evaluation; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13168v1</t>
+  </si>
+  <si>
+    <t>InFactPlanner: Planning Sustainable Geo-Distributed LLM Data Centers</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, carbon, sustainability; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12915v1</t>
+  </si>
+  <si>
+    <t>Legitimacy Criteria for Strategic Communication in the Age of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>The Proceedings of the World Conference on Social Sciences and Humanities.</t>
+  </si>
+  <si>
+    <t>conference-paper</t>
+  </si>
+  <si>
+    <t>matches Persuasion &amp; Manipulation: persuasion, manipulation, influence, behavioral influence; impact signal: framework, regulation, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.33422/shconf.v3i1.2047</t>
+  </si>
+  <si>
+    <t>10.33422/shconf.v3i1.2047</t>
+  </si>
+  <si>
+    <t>A carbon aware job scheduling framework for data center sustainability using deep learning training</t>
+  </si>
+  <si>
+    <t>Discover Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, environment, sustainability; strong scholarly metadata source; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s44163-026-02022-4</t>
+  </si>
+  <si>
+    <t>10.1007/s44163-026-02022-4</t>
+  </si>
+  <si>
+    <t>How electoral management bodies govern digital electoral systems: capacity, authority, and accountability</t>
+  </si>
+  <si>
+    <t>Frontiers in Political Science</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: systematic review, framework, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpos.2026.1877569</t>
+  </si>
+  <si>
+    <t>10.3389/fpos.2026.1877569</t>
+  </si>
+  <si>
+    <t>Leveraging strategic facilities management to achieve corporate ESG and sustainability: a literature review</t>
+  </si>
+  <si>
+    <t>Frontiers in Environmental Economics</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: environment, sustainability; impact signal: framework, governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/frevc.2026.1839120</t>
+  </si>
+  <si>
+    <t>10.3389/frevc.2026.1839120</t>
+  </si>
+  <si>
+    <t>Benchmarking Knowledge-Extraction Attack and Defense on Retrieval-Augmented Generation (RAG)</t>
+  </si>
+  <si>
+    <t>OpenAlex</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>matches Privacy: privacy, extraction; impact signal: benchmark, framework, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3770855.3817524</t>
+  </si>
+  <si>
+    <t>10.1145/3770855.3817524</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>Governing Agentic AI in FinTech</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11344v2</t>
+  </si>
+  <si>
+    <t>Toward Meaningful Transparency for AI Chatbots: Disclosing Persuasive Intent Reduces Persuasion</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, disclosure, provenance; impact signal: regulation, policy, randomized; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11794v1</t>
+  </si>
+  <si>
+    <t>Research on the Judicial Fairness Challenges and Legal Regulation of AI-Assisted Judgments in the Context of Digital Justice</t>
+  </si>
+  <si>
+    <t>Advanced Electromagnetics</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.7716/aem.v15i3.3403</t>
+  </si>
+  <si>
+    <t>10.7716/aem.v15i3.3403</t>
+  </si>
+  <si>
+    <t>The Correlation Between Exposure to English-Language Content on Instagram and Listening Comprehension among EFL Students at UIN Datokarama Palu</t>
+  </si>
+  <si>
+    <t>Journal of General Education and Humanities</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.58421/gehu.v5i4.1936</t>
+  </si>
+  <si>
+    <t>10.58421/gehu.v5i4.1936</t>
+  </si>
+  <si>
+    <t>Motivation to learn and teach home economics in higher education: Predictors and comparative analysis</t>
+  </si>
+  <si>
+    <t>Social Sciences &amp; Humanities Open</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ssaho.2026.103414</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssaho.2026.103414</t>
+  </si>
+  <si>
+    <t>AI literacy and subject specialization in pre-service teacher education: a mixed-methods study of dimensional profiles and perceived pedagogical challenges</t>
+  </si>
+  <si>
+    <t>Frontiers in Education</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1876627</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1876627</t>
+  </si>
+  <si>
+    <t>PENGARUH MUSIK AI TERHADAP PENINGKATAN MOTIVASI BELAJAR SISWA PADA MATA PELAJARAN IPS DI KELAS IV SD NEGERI 73 AMBON</t>
+  </si>
+  <si>
+    <t>SOCIAL : Jurnal Inovasi Pendidikan IPS</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51878/social.v6i3.14523</t>
+  </si>
+  <si>
+    <t>10.51878/social.v6i3.14523</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Physical Processing of Aquatic Gel Foods: From Protein Structure Regulation to Health, Sustainability, and Personalized Design</t>
+  </si>
+  <si>
+    <t>Comprehensive Reviews in Food Science and Food Safety</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, sustainability; strong scholarly metadata source; impact signal: regulation, standard, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/1541-4337.70601</t>
+  </si>
+  <si>
+    <t>10.1111/1541-4337.70601</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>ChatGPT and Large Language Models in Contemporary Nursing</t>
+  </si>
+  <si>
+    <t>Journal of Clinical Nursing</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/jocn.70490</t>
+  </si>
+  <si>
+    <t>10.1111/jocn.70490</t>
+  </si>
+  <si>
+    <t>Software Engineering for and with GUI Agent</t>
+  </si>
+  <si>
+    <t>arXiv (Cornell University)</t>
+  </si>
+  <si>
+    <t>preprint</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, evaluation, audit; impact signal: benchmark, framework, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arxiv.2608.09278</t>
+  </si>
+  <si>
+    <t>10.48550/arxiv.2608.09278</t>
+  </si>
+  <si>
+    <t>Banking Performance under the Lens of Earnings Management: A Theoretical and Bibliometric Systematic Review</t>
+  </si>
+  <si>
+    <t>Bulletin of Social Studies and Community Development</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, disclosure, reporting; impact signal: systematic review, framework, guidelines; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.61436/bsscd/v5i3.pp253-267</t>
+  </si>
+  <si>
+    <t>10.61436/bsscd/v5i3.pp253-267</t>
+  </si>
+  <si>
+    <t>Pedagogical prompting rather than technical mastery: Generative AI use by English and English-medium instruction teachers</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1901680</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1901680</t>
+  </si>
+  <si>
+    <t>Applied and Filtered: An End-to-End Algorithmic Fairness Audit of A Public Employment Agency</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: evaluation, audit; impact signal: evaluation, audit; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13022v1</t>
+  </si>
+  <si>
+    <t>Pre-service teachers' general pedagogical knowledge and pedagogical learning opportunities at entry into induction: comparing traditional and alternative teacher education programs</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: standard, longitudinal; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1790135</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1790135</t>
+  </si>
+  <si>
+    <t>Dysfunction of Zakat Village Governance in Papua: Fragmentation of Collaboration and Inequality of Amil Capacity</t>
+  </si>
+  <si>
+    <t>JURNAL ILMIAH GEMA PERENCANA</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, evaluation; strong scholarly metadata source; impact signal: framework, regulation, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.61860/jigp.v5i1.411</t>
+  </si>
+  <si>
+    <t>10.61860/jigp.v5i1.411</t>
+  </si>
+  <si>
+    <t>Human-centric AI governance in the European Union. Accountability, fundamental rights, and institutional resilience in public administration</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpos.2026.1928481</t>
+  </si>
+  <si>
+    <t>10.3389/fpos.2026.1928481</t>
+  </si>
+  <si>
+    <t>PENGARUH MODEL PEMBELAJARAN PROJECT BASED LEARNING DAN KEDISIPLINAN BELAJAR TERHADAP KESIAPAN KERJA SISWA PADA JURUSAN AKUNTANSI KEUANGAN LEMABAGA DI SMK NEGERI 1 PANGKEP</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; impact signal: survey; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51878/social.v6i3.14617</t>
+  </si>
+  <si>
+    <t>10.51878/social.v6i3.14617</t>
+  </si>
+  <si>
+    <t>Large Language Model-facilitated national review on the use of ecological tools and processes in Environmental Impact Statements (EIS) in the U.S. with demonstrated use cases for environmental planners, legal practitioners, and researchers</t>
+  </si>
+  <si>
+    <t>Springer Science and Business Media LLC</t>
+  </si>
+  <si>
+    <t>posted-content</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, environment, labor; strong scholarly metadata source; impact signal: benchmark, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.21203/rs.3.rs-10627892/v1</t>
+  </si>
+  <si>
+    <t>10.21203/rs.3.rs-10627892/v1</t>
+  </si>
+  <si>
+    <t>Optimization of Household Equipment and Instrumentation in an Effort to Save Electrical Energy in a Restaurant</t>
+  </si>
+  <si>
+    <t>International Journal Of Community Service</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, environment; strong scholarly metadata source; impact signal: survey, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51601/ijcs.v6i3.1022</t>
+  </si>
+  <si>
+    <t>10.51601/ijcs.v6i3.1022</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>From Single Chatbots to Governed Agent Ecosystems: An Agentic AI Pattern Catalogue and Orchestration Framework for Mission-Critical Hospital Information Management Systems</t>
+  </si>
+  <si>
+    <t>matches Agentic AI: agentic ai, autonomous agent, multi-agent; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.07627v1</t>
+  </si>
+  <si>
+    <t>10.38124/ijisrt/26jul830</t>
+  </si>
+  <si>
+    <t>Bias Smells in AI Software Development: Recognizing Potential Sources of Fairness Debt</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arxiv.2608.10248</t>
+  </si>
+  <si>
+    <t>10.48550/arxiv.2608.10248</t>
+  </si>
+  <si>
+    <t>Quantifying the Relationship Between Clinical Safety and Environmental Impact in Therapeutic LLMs</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, carbon, environment; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11830v1</t>
+  </si>
+  <si>
+    <t>Benchmark-Based Comparative Assessment of Publicly Benchmarked Indian Foundation Models: A Capability and Evaluation-Maturity Framework</t>
+  </si>
+  <si>
+    <t>matches India &amp; Global South: multilingual, india; impact signal: survey, benchmark, framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11891v1</t>
+  </si>
+  <si>
+    <t>Academic League of Artificial Intelligence - An Integrative Perspective of Teaching, Research, and Extension</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13447v1</t>
+  </si>
+  <si>
+    <t>Solar Exposure and Photoprotection Behaviors as Determinants of Acne Vulgaris Severity Among University Students in Andalusia-Spain</t>
+  </si>
+  <si>
+    <t>Ibn Sina Journal of Medical Science Health &amp; Pharmacy</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; impact signal: survey, framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.64440/ibnsina/sina0027</t>
+  </si>
+  <si>
+    <t>10.64440/ibnsina/sina0027</t>
+  </si>
+  <si>
+    <t>FSGR: Mitigating Token Frequency Bias for Fair SID-Based Generative Recommendation</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12845v1</t>
+  </si>
+  <si>
+    <t>HEPE — Complete 16-State AI Governance Space with Lyapunov Values (Hardware-Enforced Policy Engine)</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: policy, governance, audit; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21935563</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21935563</t>
+  </si>
+  <si>
+    <t>What Remains Ours to Think? Reclaiming Critical Thinking in AI‐Augmented Student Leadership Education</t>
+  </si>
+  <si>
+    <t>New Directions for Student Leadership</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/yd.70068</t>
+  </si>
+  <si>
+    <t>10.1002/yd.70068</t>
+  </si>
+  <si>
+    <t>Supervision in educational leadership: practices, challenges, and innovations in the UAE — a multi-level coupling analysis of the current and future</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: benchmark, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1862260</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1862260</t>
+  </si>
+  <si>
+    <t>Research ethics and publication policies in journals using the Korea Institute of Science and Technology Information (KISTI) academic publishing platform: a content analysis of 181 journals</t>
+  </si>
+  <si>
+    <t>Science Editing</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: accountability, disclosure; impact signal: guidelines, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.6087/kcse.403</t>
+  </si>
+  <si>
+    <t>10.6087/kcse.403</t>
+  </si>
+  <si>
+    <t>Striking a Balance between the Right to Privacy and Freedom of Expression: A Case Study of Women’s Digital Rights in Tanzania</t>
+  </si>
+  <si>
+    <t>East African Journal of Law and Ethics</t>
+  </si>
+  <si>
+    <t>matches Regulation: regulation, legal framework, standard; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.37284/eajle.9.3.5557</t>
+  </si>
+  <si>
+    <t>10.37284/eajle.9.3.5557</t>
+  </si>
+  <si>
+    <t>Evaluation of the CIPP Model in a Project-Based Basic Electronics Course: A Discriminant Validity and Common Method Bias Analysis</t>
+  </si>
+  <si>
+    <t>Educative: Jurnal Ilmiah Pendidikan</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.70437/educative.v4i2.2180</t>
+  </si>
+  <si>
+    <t>10.70437/educative.v4i2.2180</t>
+  </si>
+  <si>
+    <t>Review Queue — Human-in-the-loop Curation</t>
+  </si>
+  <si>
+    <t>Promote only sources that are genuinely useful. Automatic discovery is intentionally not identical to automatic curation.</t>
+  </si>
+  <si>
+    <t>Topic Map — What to Read for Each AI / LLM Ethics Question</t>
+  </si>
+  <si>
+    <t>Theme-level map generated from the current curated library.</t>
+  </si>
+  <si>
+    <t>Sources in library</t>
+  </si>
+  <si>
+    <t>2026-heavy?</t>
+  </si>
+  <si>
+    <t>Start with</t>
+  </si>
+  <si>
+    <t>Then read</t>
+  </si>
+  <si>
+    <t>Typical reader question</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Recommendation on the Ethics of Artificial Intelligence; On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1); Guidelines for providers of general-purpose AI models</t>
+  </si>
+  <si>
+    <t>An Evaluation of AI Companion Apps; Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
+  </si>
+  <si>
+    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders; Evaluating Language Models for Harmful Manipulation</t>
+  </si>
+  <si>
+    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory; SoK: The Privacy Paradox of Large Language Models</t>
+  </si>
+  <si>
+    <t>2026-Only View</t>
+  </si>
+  <si>
+    <t>Current-year curated items.</t>
+  </si>
+  <si>
+    <t>Policy, Governance &amp; Regulation</t>
+  </si>
+  <si>
+    <t>Curated governance, standards, transparency, law and human-rights sources.</t>
+  </si>
+  <si>
+    <t>Source Configuration</t>
+  </si>
+  <si>
+    <t>Edit config/sources.yaml in the repository to change the automation. This sheet is a readable mirror.</t>
+  </si>
+  <si>
+    <t>Endpoint / URL</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Authority</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>https://export.arxiv.org/api/query</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Fresh preprints</t>
+  </si>
+  <si>
+    <t>3-second delay between repeated calls</t>
+  </si>
+  <si>
+    <t>https://api.openalex.org/works</t>
+  </si>
+  <si>
+    <t>Broad scholarly discovery</t>
+  </si>
+  <si>
+    <t>OPENALEX_API_KEY optional</t>
+  </si>
+  <si>
+    <t>Crossref</t>
+  </si>
+  <si>
+    <t>https://api.crossref.org/works</t>
+  </si>
+  <si>
+    <t>Published DOI metadata</t>
+  </si>
+  <si>
+    <t>CONTACT_EMAIL recommended</t>
+  </si>
+  <si>
+    <t>NIST Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Official page watch</t>
+  </si>
+  <si>
+    <t>https://www.nist.gov/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>Policy/news link discovery</t>
+  </si>
+  <si>
+    <t>First scan bootstraps without flooding</t>
+  </si>
+  <si>
+    <t>European Commission AI Act</t>
+  </si>
+  <si>
+    <t>OECD.AI Wonk</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/wonk</t>
+  </si>
+  <si>
+    <t>UNESCO Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>IndiaAI Safe &amp; Trusted AI</t>
+  </si>
+  <si>
+    <t>https://indiaai.gov.in/hub/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>Automation Update Log</t>
+  </si>
+  <si>
+    <t>Every run records discovery and deduplication counts.</t>
+  </si>
+  <si>
+    <t>New This Week</t>
+  </si>
+  <si>
+    <t>Review Queue</t>
+  </si>
+  <si>
+    <t>Auto-promoted</t>
+  </si>
+  <si>
+    <t>2026-08-16T12:18:00+05:30</t>
+  </si>
+  <si>
+    <t>Initial build</t>
+  </si>
+  <si>
+    <t>Living tracker package initialized</t>
+  </si>
+  <si>
     <t>2026-08-16T07:19:28+00:00</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>scheduled/manual</t>
-  </si>
-  <si>
-    <t>Sources checked</t>
-  </si>
-  <si>
-    <t>Candidates fetched</t>
-  </si>
-  <si>
-    <t>New after dedupe</t>
-  </si>
-  <si>
-    <t>Errors / notes</t>
-  </si>
-  <si>
-    <t>Policy/IndiaAI Safe &amp; Trusted AI: HTTPError: 403 Client Error: Forbidden for url: https://indiaai.gov.in/hub/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>Start Here — 2026-aware AI &amp; LLM Ethics Reading Path</t>
-  </si>
-  <si>
-    <t>Use this sheet for a compact orientation. The automated discovery tabs are intentionally separate from the stable reading path.</t>
-  </si>
-  <si>
-    <t>Curated sources</t>
-  </si>
-  <si>
-    <t>2026 sources</t>
-  </si>
-  <si>
-    <t>Must Read</t>
-  </si>
-  <si>
-    <t>Official / institutional</t>
-  </si>
-  <si>
-    <t>Recommended 10-source reading path</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Read this</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Why now</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Source URL</t>
-  </si>
-  <si>
-    <t>Responsible AI | The 2026 AI Index Report</t>
-  </si>
-  <si>
-    <t>Current 2025–2026 evidence or governance update</t>
-  </si>
-  <si>
-    <t>https://hai.stanford.edu/ai-index/2026-ai-index-report/responsible-ai</t>
-  </si>
-  <si>
-    <t>AI Act | Shaping Europe's digital future</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/regulatory-framework-ai</t>
-  </si>
-  <si>
-    <t>Guidelines on transparency obligations for providers and deployers of AI systems</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-transparency-ai-generated-content</t>
-  </si>
-  <si>
-    <t>Persuasion with Large Language Models: A Survey of Empirical Studies</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2411.06837v2</t>
-  </si>
-  <si>
-    <t>Emotional Support with Conversational AI: Talking to Machines About Life</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2603.22618v1</t>
-  </si>
-  <si>
-    <t>An Evaluation of AI Companion Apps</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2605.08093v2</t>
-  </si>
-  <si>
-    <t>Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2606.04150</t>
-  </si>
-  <si>
-    <t>Towards Agentic AI Governance: A Preliminary Assessment</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2607.07612</t>
-  </si>
-  <si>
-    <t>The 2025 Foundation Model Transparency Index</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2512.10169</t>
-  </si>
-  <si>
-    <t>India AI Governance Guidelines: Empowering Ethical and Responsible AI</t>
-  </si>
-  <si>
-    <t>https://indiaai.gov.in/article/india-ai-governance-guidelines-empowering-ethical-and-responsible-ai</t>
-  </si>
-  <si>
-    <t>Ethics of Artificial Intelligence &amp; LLMs — Curated Reading Library</t>
-  </si>
-  <si>
-    <t>Stable curated sources. Automatically discovered items are triaged separately before promotion.</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Subtopic</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Author / Body</t>
-  </si>
-  <si>
-    <t>Source Type</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>What it covers</t>
-  </si>
-  <si>
-    <t>Why the reader benefits</t>
-  </si>
-  <si>
-    <t>Best use</t>
-  </si>
-  <si>
-    <t>2026 Relevance Score</t>
-  </si>
-  <si>
-    <t>Read Priority</t>
-  </si>
-  <si>
-    <t>Region / Scope</t>
-  </si>
-  <si>
-    <t>Key ethical question</t>
-  </si>
-  <si>
-    <t>Notes / status</t>
-  </si>
-  <si>
-    <t>Reader mode</t>
-  </si>
-  <si>
-    <t>Responsible AI state of the field</t>
-  </si>
-  <si>
-    <t>Stanford HAI / AI Index</t>
-  </si>
-  <si>
-    <t>Annual evidence report</t>
-  </si>
-  <si>
-    <t>Institutional / data-driven</t>
-  </si>
-  <si>
-    <t>Tracks AI incidents, safety evaluation, transparency, responsible-AI reporting, and the widening gap between capability and governance.</t>
-  </si>
-  <si>
-    <t>Best current snapshot for showing that AI capability is advancing faster than safety measurement and transparency.</t>
-  </si>
-  <si>
-    <t>Lecture opener; literature review motivation; 2026 statistics</t>
-  </si>
-  <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t>Are current evaluation and governance systems keeping pace with frontier AI capability?</t>
-  </si>
-  <si>
-    <t>2026 edition; strong source for current facts and figures.</t>
-  </si>
-  <si>
-    <t>Read closely</t>
-  </si>
-  <si>
-    <t>Foundation model transparency</t>
-  </si>
-  <si>
-    <t>Wan et al. / Stanford CRFM</t>
-  </si>
-  <si>
-    <t>Research report / index</t>
-  </si>
-  <si>
-    <t>Research report</t>
-  </si>
-  <si>
-    <t>Scores major foundation-model developers on disclosures covering data, compute, risk mitigation, usage and downstream impacts.</t>
-  </si>
-  <si>
-    <t>Lets readers move from vague calls for transparency to measurable disclosure dimensions and compare developers.</t>
-  </si>
-  <si>
-    <t>Transparency section; accountability case study; assignment</t>
-  </si>
-  <si>
-    <t>Global / industry</t>
-  </si>
-  <si>
-    <t>What information should frontier-model developers be required to disclose?</t>
-  </si>
-  <si>
-    <t>Average score fell from 58/100 in 2024 to 40/100 in 2025.</t>
-  </si>
-  <si>
-    <t>EU AI Act implementation</t>
-  </si>
-  <si>
-    <t>European Commission</t>
-  </si>
-  <si>
-    <t>Regulation / official guidance</t>
-  </si>
-  <si>
-    <t>Official</t>
-  </si>
-  <si>
-    <t>Official overview of the EU AI Act, risk-based obligations, implementation timeline, GPAI rules and transparency requirements.</t>
-  </si>
-  <si>
-    <t>Provides the clearest bridge between ethics principles and enforceable legal duties in 2026.</t>
-  </si>
-  <si>
-    <t>Regulation module; compliance discussion; policy comparison</t>
-  </si>
-  <si>
-    <t>European Union</t>
-  </si>
-  <si>
-    <t>When should ethical expectations become legal obligations?</t>
-  </si>
-  <si>
-    <t>General application date: 2 August 2026, with exceptions and phased provisions.</t>
-  </si>
-  <si>
-    <t>AI-generated content disclosure</t>
-  </si>
-  <si>
-    <t>Regulatory guidance</t>
-  </si>
-  <si>
-    <t>Explains Article 50 duties concerning user disclosure, machine-readable marking, AI-generated content and deepfakes.</t>
-  </si>
-  <si>
-    <t>Useful concrete example of how transparency ethics becomes a product-design requirement.</t>
-  </si>
-  <si>
-    <t>Deepfakes; disclosure; generative-AI product design</t>
-  </si>
-  <si>
-    <t>Should people always know when they are interacting with AI or seeing AI-generated content?</t>
-  </si>
-  <si>
-    <t>Article 50 applies from 2 August 2026.</t>
-  </si>
-  <si>
-    <t>General-purpose AI obligations</t>
-  </si>
-  <si>
-    <t>Guidelines for providers of general-purpose AI models</t>
-  </si>
-  <si>
-    <t>Clarifies obligations for providers of general-purpose AI models and the Commission's enforcement role.</t>
-  </si>
-  <si>
-    <t>Gives readers a current compliance perspective on frontier and general-purpose models rather than generic AI regulation.</t>
-  </si>
-  <si>
-    <t>GPAI governance; provider responsibilities; seminar discussion</t>
-  </si>
-  <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>What extra duties should apply to powerful general-purpose models?</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-gpai-providers</t>
-  </si>
-  <si>
-    <t>Commission enforcement powers apply from 2 August 2026.</t>
-  </si>
-  <si>
-    <t>Read/skim</t>
-  </si>
-  <si>
-    <t>India AI governance</t>
-  </si>
-  <si>
-    <t>IndiaAI / MeitY</t>
-  </si>
-  <si>
-    <t>National governance guidance</t>
-  </si>
-  <si>
-    <t>Sets out principles and recommendations around fairness, accountability, safety, inclusivity and trustworthy AI in India.</t>
-  </si>
-  <si>
-    <t>Adds an India-specific governance perspective and prevents the reading list from being US/EU-centric.</t>
-  </si>
-  <si>
-    <t>India case study; policy comparison; local context</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>How should responsible AI governance reflect India's scale, diversity and public-interest priorities?</t>
-  </si>
-  <si>
-    <t>Released 5 Nov 2025 under the IndiaAI Mission.</t>
-  </si>
-  <si>
-    <t>AI safety capacity</t>
-  </si>
-  <si>
-    <t>Safe &amp; Trusted AI Working Group</t>
-  </si>
-  <si>
-    <t>India AI Impact Summit</t>
-  </si>
-  <si>
-    <t>Policy / working-group output</t>
-  </si>
-  <si>
-    <t>Focuses on AI safety capacity, evaluation, governance and incorporating Global South perspectives into international AI safety frameworks.</t>
-  </si>
-  <si>
-    <t>Useful for understanding how safety debates are being localized beyond US/EU institutions.</t>
-  </si>
-  <si>
-    <t>India 2026 update; global governance; discussion prompt</t>
-  </si>
-  <si>
-    <t>India / Global South</t>
-  </si>
-  <si>
-    <t>Who gets to define acceptable AI risk and safety standards globally?</t>
-  </si>
-  <si>
-    <t>https://impact.indiaai.gov.in/working-groups/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>2026-relevant IndiaAI Impact Summit initiative.</t>
-  </si>
-  <si>
-    <t>Risk management framework</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1)</t>
-  </si>
-  <si>
-    <t>NIST</t>
-  </si>
-  <si>
-    <t>Risk-management framework</t>
-  </si>
-  <si>
-    <t>Identifies GenAI-specific risks and actions across the AI lifecycle, aligned with Govern, Map, Measure and Manage.</t>
-  </si>
-  <si>
-    <t>One of the most practical sources for converting ethical concerns into operational risk controls.</t>
-  </si>
-  <si>
-    <t>Risk register; deployment checklist; governance design</t>
-  </si>
-  <si>
-    <t>United States / cross-sector</t>
-  </si>
-  <si>
-    <t>How can an organization operationalize trustworthy GenAI rather than merely state principles?</t>
-  </si>
-  <si>
-    <t>https://www.nist.gov/publications/artificial-intelligence-risk-management-framework-generative-artificial-intelligence</t>
-  </si>
-  <si>
-    <t>Companion to NIST AI RMF 1.0.</t>
-  </si>
-  <si>
-    <t>Human-rights-centered AI ethics</t>
-  </si>
-  <si>
-    <t>Recommendation on the Ethics of Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>UNESCO</t>
-  </si>
-  <si>
-    <t>International ethics standard</t>
-  </si>
-  <si>
-    <t>Defines principles including proportionality, do-no-harm, safety, privacy, fairness, transparency, accountability, sustainability and human oversight.</t>
-  </si>
-  <si>
-    <t>Provides a normative foundation for almost every later AI ethics topic.</t>
-  </si>
-  <si>
-    <t>Foundations lecture; ethics framework; compare policies</t>
-  </si>
-  <si>
-    <t>What values should guide the design and deployment of AI systems?</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
-  </si>
-  <si>
-    <t>Global UNESCO recommendation; remains foundational in 2026.</t>
-  </si>
-  <si>
-    <t>Trustworthy AI principles</t>
-  </si>
-  <si>
-    <t>OECD AI Principles</t>
-  </si>
-  <si>
-    <t>OECD</t>
-  </si>
-  <si>
-    <t>International policy principles</t>
-  </si>
-  <si>
-    <t>Principles for innovative and trustworthy AI, covering human rights, fairness, transparency, robustness, security and accountability.</t>
-  </si>
-  <si>
-    <t>Concise policy baseline that is easy to compare against NIST, UNESCO, EU and national frameworks.</t>
-  </si>
-  <si>
-    <t>Framework comparison; policy lecture; exam preparation</t>
-  </si>
-  <si>
-    <t>What minimum principles should trustworthy AI systems satisfy across countries?</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/ai-principles</t>
-  </si>
-  <si>
-    <t>Initially adopted 2019; updated May 2024.</t>
-  </si>
-  <si>
-    <t>International AI treaty</t>
-  </si>
-  <si>
-    <t>Framework Convention on Artificial Intelligence and Human Rights, Democracy and the Rule of Law</t>
-  </si>
-  <si>
-    <t>Council of Europe</t>
-  </si>
-  <si>
-    <t>International treaty</t>
-  </si>
-  <si>
-    <t>Official / legally binding framework</t>
-  </si>
-  <si>
-    <t>Addresses human rights, democratic processes, autonomy, transparency, accountability, equality and privacy across the AI lifecycle.</t>
-  </si>
-  <si>
-    <t>Shows the transition from voluntary ethics to treaty-based human-rights obligations.</t>
-  </si>
-  <si>
-    <t>Human-rights module; legal governance; global policy</t>
-  </si>
-  <si>
-    <t>International</t>
-  </si>
-  <si>
-    <t>How should AI development be constrained when it may affect fundamental rights and democratic institutions?</t>
-  </si>
-  <si>
-    <t>https://www.coe.int/en/web/artificial-intelligence/the-framework-convention-on-artificial-intelligence</t>
-  </si>
-  <si>
-    <t>First international legally binding treaty in this field; opened for signature 5 Sept 2024.</t>
-  </si>
-  <si>
-    <t>Developer risk reporting</t>
-  </si>
-  <si>
-    <t>How are AI developers managing risks? Insights from the Hiroshima AI Process reporting framework</t>
-  </si>
-  <si>
-    <t>International governance report</t>
-  </si>
-  <si>
-    <t>Official / multi-stakeholder</t>
-  </si>
-  <si>
-    <t>Analyzes how organizations report risk identification, safety, governance, content authentication and accountability practices.</t>
-  </si>
-  <si>
-    <t>Gives concrete examples of how frontier developers operationalize risk management, not just what principles say.</t>
-  </si>
-  <si>
-    <t>Industry governance; transparency; comparative analysis</t>
-  </si>
-  <si>
-    <t>G7 / global</t>
-  </si>
-  <si>
-    <t>Can voluntary transparency meaningfully improve accountability for advanced AI developers?</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/ai-publications/how-are-ai-developers-managing-risks-insights-from-responses-to-the-reporting-framework-of-the-hiroshima-ai-process-code-of-conduct</t>
-  </si>
-  <si>
-    <t>Reporting framework launched in 2025.</t>
-  </si>
-  <si>
-    <t>Comprehensive LLM ethics</t>
-  </si>
-  <si>
-    <t>Deconstructing the ethics of large language models from long-standing issues to new-emerging dilemmas</t>
-  </si>
-  <si>
-    <t>Deng et al.</t>
-  </si>
-  <si>
-    <t>Survey / review</t>
-  </si>
-  <si>
-    <t>Peer-reviewed</t>
-  </si>
-  <si>
-    <t>Surveys copyright, systematic bias, privacy, truthfulness, social norms and emerging ethical challenges of LLMs.</t>
-  </si>
-  <si>
-    <t>Good single-paper orientation before readers enter specialized literatures.</t>
-  </si>
-  <si>
-    <t>Literature review starting point; seminar reading</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Which LLM ethical risks are old problems amplified by scale, and which are genuinely new?</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s43681-025-00797-3</t>
-  </si>
-  <si>
-    <t>Published in AI and Ethics.</t>
-  </si>
-  <si>
-    <t>Bias evaluation and mitigation</t>
-  </si>
-  <si>
-    <t>Bias and Fairness in Large Language Models: A Survey</t>
-  </si>
-  <si>
-    <t>Gallegos et al.</t>
-  </si>
-  <si>
-    <t>Survey</t>
-  </si>
-  <si>
-    <t>Research / arXiv</t>
-  </si>
-  <si>
-    <t>Organizes social bias harms, evaluation metrics, datasets and mitigation techniques for LLMs.</t>
-  </si>
-  <si>
-    <t>Provides a technical taxonomy that makes 'AI bias' measurable rather than purely rhetorical.</t>
-  </si>
-  <si>
-    <t>Bias lecture; evaluation design; related work</t>
-  </si>
-  <si>
-    <t>How should fairness be defined and measured for generative language systems?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2309.00770</t>
-  </si>
-  <si>
-    <t>Still a useful technical survey in 2026.</t>
-  </si>
-  <si>
-    <t>Hallucination taxonomy</t>
-  </si>
-  <si>
-    <t>A Survey on Hallucination in Large Language Models</t>
-  </si>
-  <si>
-    <t>ACM Computing Surveys</t>
-  </si>
-  <si>
-    <t>Reviews hallucination principles, taxonomies, causes, evaluation, detection and mitigation in LLMs.</t>
-  </si>
-  <si>
-    <t>Helps distinguish factual reliability problems from broader moral or social harms.</t>
-  </si>
-  <si>
-    <t>Truthfulness; reliability; high-stakes deployment</t>
-  </si>
-  <si>
-    <t>When is an incorrect LLM output merely an error, and when does it become an ethical harm?</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3703155</t>
-  </si>
-  <si>
-    <t>High-value technical survey.</t>
-  </si>
-  <si>
-    <t>Training-data leakage</t>
-  </si>
-  <si>
-    <t>New Privacy Risks for Large Language Models</t>
-  </si>
-  <si>
-    <t>Research paper</t>
-  </si>
-  <si>
-    <t>Preprint / current research</t>
-  </si>
-  <si>
-    <t>Examines data extraction and memorization risks, connecting privacy leakage with copyright and training-data provenance concerns.</t>
-  </si>
-  <si>
-    <t>Useful 2026 update showing privacy risk is not limited to classic membership inference.</t>
-  </si>
-  <si>
-    <t>Privacy section; training data; model memorization</t>
-  </si>
-  <si>
-    <t>What does a model owe people whose private or copyrighted data it can reproduce?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2509.14278v2</t>
-  </si>
-  <si>
-    <t>Version available Jan 2026.</t>
-  </si>
-  <si>
-    <t>Privacy threat landscape</t>
-  </si>
-  <si>
-    <t>SoK: The Privacy Paradox of Large Language Models</t>
-  </si>
-  <si>
-    <t>Systematization of knowledge</t>
-  </si>
-  <si>
-    <t>Preprint / research</t>
-  </si>
-  <si>
-    <t>Systematizes training-data extraction, reconstruction, inference-time privacy and protection mechanisms.</t>
-  </si>
-  <si>
-    <t>Gives readers a map of privacy attack surfaces instead of isolated examples.</t>
-  </si>
-  <si>
-    <t>Security/privacy module; research gap identification</t>
-  </si>
-  <si>
-    <t>Can LLM utility and strong privacy guarantees be achieved simultaneously?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2506.12699v2</t>
-  </si>
-  <si>
-    <t>Useful bridge between AI ethics and security.</t>
-  </si>
-  <si>
-    <t>Empirical privacy evaluation</t>
-  </si>
-  <si>
-    <t>Privacy Auditing of Large Language Models</t>
-  </si>
-  <si>
-    <t>Develops stronger privacy auditing techniques and more effective canaries for estimating empirical leakage.</t>
-  </si>
-  <si>
-    <t>Shows readers how privacy claims can be tested rather than assumed.</t>
-  </si>
-  <si>
-    <t>Methodology; model audit; technical assignment</t>
-  </si>
-  <si>
-    <t>Specialist</t>
-  </si>
-  <si>
-    <t>How should developers demonstrate that a language model is not leaking training data?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2503.06808v1</t>
-  </si>
-  <si>
-    <t>Technical privacy-auditing work.</t>
-  </si>
-  <si>
-    <t>Reference as needed</t>
-  </si>
-  <si>
-    <t>Agent memory and contextual leakage</t>
-  </si>
-  <si>
-    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory</t>
-  </si>
-  <si>
-    <t>Security research</t>
-  </si>
-  <si>
-    <t>Studies privacy leakage from inference-time contextual memory in LLM agents, beyond training-data privacy.</t>
-  </si>
-  <si>
-    <t>Important for 2026 because persistent AI assistants and agents create a new privacy attack surface.</t>
-  </si>
-  <si>
-    <t>Agentic AI; memory privacy; security discussion</t>
-  </si>
-  <si>
-    <t>Research / agents</t>
-  </si>
-  <si>
-    <t>What privacy risks appear when AI systems remember and act on user context over time?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2604.23711v1</t>
-  </si>
-  <si>
-    <t>2026 agent-memory privacy paper.</t>
-  </si>
-  <si>
-    <t>Persuasion landscape</t>
-  </si>
-  <si>
-    <t>Research survey</t>
-  </si>
-  <si>
-    <t>Reviews empirical evidence on automated, personalized and interactive LLM persuasion and its effects on attitudes and behavior.</t>
-  </si>
-  <si>
-    <t>A direct entry point into one of the most important newer AI-ethics issues.</t>
-  </si>
-  <si>
-    <t>Manipulation lecture; social influence; governance</t>
-  </si>
-  <si>
-    <t>When does helpful persuasion become manipulation or undue influence?</t>
-  </si>
-  <si>
-    <t>Updated Apr 2026.</t>
-  </si>
-  <si>
-    <t>Human vs AI persuasion</t>
-  </si>
-  <si>
-    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders</t>
-  </si>
-  <si>
-    <t>Schoenegger et al.</t>
-  </si>
-  <si>
-    <t>Large-scale experiment</t>
-  </si>
-  <si>
-    <t>Compares a frontier LLM with incentivized human persuaders in interactive settings and measures compliance with correct and incorrect persuasion.</t>
-  </si>
-  <si>
-    <t>Provides concrete empirical evidence that persuasive capability can create both benefits and harms.</t>
-  </si>
-  <si>
-    <t>Case study; empirical evidence; class discussion</t>
-  </si>
-  <si>
-    <t>Should systems with human-level or greater persuasive power face special safeguards?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2505.09662</t>
-  </si>
-  <si>
-    <t>Preregistered, large-scale incentivized experiment.</t>
-  </si>
-  <si>
-    <t>Harmful influence evaluation</t>
-  </si>
-  <si>
-    <t>Evaluating Language Models for Harmful Manipulation</t>
-  </si>
-  <si>
-    <t>Akbulut et al.</t>
-  </si>
-  <si>
-    <t>Human-subject evaluation</t>
-  </si>
-  <si>
-    <t>Research / preprint</t>
-  </si>
-  <si>
-    <t>Introduces a framework for measuring harmful manipulation across public policy, finance and health with participants from multiple countries.</t>
-  </si>
-  <si>
-    <t>Shows how manipulation can be operationalized and evaluated across consequential domains.</t>
-  </si>
-  <si>
-    <t>Evaluation design; high-stakes AI; cross-country analysis</t>
-  </si>
-  <si>
-    <t>US / UK / India</t>
-  </si>
-  <si>
-    <t>How can harmful manipulation be measured before deployment?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2603.25326</t>
-  </si>
-  <si>
-    <t>Includes 10,101 participants across three locales.</t>
-  </si>
-  <si>
-    <t>Sycophancy to strategic deception</t>
-  </si>
-  <si>
-    <t>From Sycophancy to Deception: A Unified Taxonomy for Misleading LLM Behavior</t>
-  </si>
-  <si>
-    <t>Taxonomy / research</t>
-  </si>
-  <si>
-    <t>Unifies hallucination, omission, pragmatic distortion, sycophancy and strategic deception under a common taxonomy of misleading behavior.</t>
-  </si>
-  <si>
-    <t>Helps readers avoid treating all misleading model outputs as the same failure mode.</t>
-  </si>
-  <si>
-    <t>Conceptual framework; deception; research taxonomy</t>
-  </si>
-  <si>
-    <t>Does intent or goal-directedness change how ethically serious misleading AI behavior is?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2604.04788</t>
-  </si>
-  <si>
-    <t>Current 2026 taxonomy.</t>
-  </si>
-  <si>
-    <t>Sycophancy</t>
-  </si>
-  <si>
-    <t>Sycophancy in Large Language Models: Causes and Mitigations</t>
-  </si>
-  <si>
-    <t>Lars Malmqvist</t>
-  </si>
-  <si>
-    <t>Technical survey</t>
-  </si>
-  <si>
-    <t>Surveys excessive agreement with users, causes, measurement and mitigation, and links sycophancy to hallucination and bias.</t>
-  </si>
-  <si>
-    <t>Useful for discussing why 'agreeable' assistants can become epistemically unsafe.</t>
-  </si>
-  <si>
-    <t>Alignment; user trust; truthfulness</t>
-  </si>
-  <si>
-    <t>Should an assistant prioritize user satisfaction or epistemic honesty when they conflict?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2411.15287</t>
-  </si>
-  <si>
-    <t>Technical survey.</t>
-  </si>
-  <si>
-    <t>Emotional support</t>
-  </si>
-  <si>
-    <t>Huang, Stodolska &amp; Sultana</t>
-  </si>
-  <si>
-    <t>Qualitative HCI research</t>
-  </si>
-  <si>
-    <t>Analyzes how emotional support is co-constructed with AI companions and tensions such as support vs dependency and validation vs delusion.</t>
-  </si>
-  <si>
-    <t>Provides nuanced evidence beyond simplistic claims that AI companions are either beneficial or harmful.</t>
-  </si>
-  <si>
-    <t>HCI ethics; mental-health-adjacent discussion; companionship</t>
-  </si>
-  <si>
-    <t>How should AI offer emotional support without reinforcing dependency or harmful beliefs?</t>
-  </si>
-  <si>
-    <t>2026 HCI-focused research.</t>
-  </si>
-  <si>
-    <t>Companion-app design</t>
-  </si>
-  <si>
-    <t>Empirical audit</t>
-  </si>
-  <si>
-    <t>Audits popular AI companion apps for dark patterns, anthropomorphism, stereotypes, erotica and technical issues.</t>
-  </si>
-  <si>
-    <t>Connects ethical risk to actual interface and monetization design choices, not only model behavior.</t>
-  </si>
-  <si>
-    <t>Product ethics; dark patterns; companion AI</t>
-  </si>
-  <si>
-    <t>EU / UK market</t>
-  </si>
-  <si>
-    <t>Can product incentives push AI companions toward manipulative engagement?</t>
-  </si>
-  <si>
-    <t>Version updated Aug 2026.</t>
-  </si>
-  <si>
-    <t>Emotional dependence</t>
-  </si>
-  <si>
-    <t>Shi et al.</t>
-  </si>
-  <si>
-    <t>Perspective / evidence synthesis</t>
-  </si>
-  <si>
-    <t>Argues that emotional dependence can emerge incidentally in general-purpose AI use and may alter future preferences for human vs AI support.</t>
-  </si>
-  <si>
-    <t>Highlights cumulative interaction effects that one-shot safety evaluations can miss.</t>
-  </si>
-  <si>
-    <t>Long-term interaction ethics; product policy; research gaps</t>
-  </si>
-  <si>
-    <t>Should general-purpose assistants be evaluated for long-term relational effects, not just single-turn harms?</t>
-  </si>
-  <si>
-    <t>Includes synthesis of longitudinal evidence.</t>
-  </si>
-  <si>
-    <t>Identity and parasocial interaction</t>
-  </si>
-  <si>
-    <t>Negotiating Digital Identities with AI Companions</t>
-  </si>
-  <si>
-    <t>HCI / computational social science</t>
-  </si>
-  <si>
-    <t>Studies identity construction and negotiation in AI-companion communities using large-scale online discussions.</t>
-  </si>
-  <si>
-    <t>Useful for understanding anthropomorphism and dependence as social processes rather than merely UI bugs.</t>
-  </si>
-  <si>
-    <t>HCI seminar; identity; anthropomorphism</t>
-  </si>
-  <si>
-    <t>How do AI companions reshape users' identities, expectations and social relationships?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2601.12181v1</t>
-  </si>
-  <si>
-    <t>Analyzes 22,374 online discussions.</t>
-  </si>
-  <si>
-    <t>Governance of autonomous agents</t>
-  </si>
-  <si>
-    <t>Raji &amp; Bashir</t>
-  </si>
-  <si>
-    <t>Systematic review</t>
-  </si>
-  <si>
-    <t>Reviews governance priorities, mechanisms and stakeholder roles for AI systems that autonomously plan and execute tasks.</t>
-  </si>
-  <si>
-    <t>Important 2026 bridge from chatbot ethics to systems that can act in the world.</t>
-  </si>
-  <si>
-    <t>Agentic AI governance; research agenda; seminar</t>
-  </si>
-  <si>
-    <t>How should accountability change when AI can plan, call tools and execute actions autonomously?</t>
-  </si>
-  <si>
-    <t>Published Jul 2026.</t>
-  </si>
-  <si>
-    <t>Security and governance practice</t>
-  </si>
-  <si>
-    <t>State of Agentic AI Security and Governance</t>
-  </si>
-  <si>
-    <t>OWASP GenAI Security Project</t>
-  </si>
-  <si>
-    <t>Security / governance report</t>
-  </si>
-  <si>
-    <t>Practitioner standard</t>
-  </si>
-  <si>
-    <t>Covers governance and security issues for autonomous AI systems, including controls, oversight and operational risk.</t>
-  </si>
-  <si>
-    <t>Gives practitioners a deployment-oriented complement to academic governance work.</t>
-  </si>
-  <si>
-    <t>Agent security; enterprise governance; checklist design</t>
-  </si>
-  <si>
-    <t>What controls are necessary when agents receive tools, permissions and persistent access?</t>
-  </si>
-  <si>
-    <t>https://genai.owasp.org/resource/state-of-agentic-ai-security-and-governance/</t>
-  </si>
-  <si>
-    <t>Practitioner-focused resource.</t>
-  </si>
-  <si>
-    <t>AI in education ethics</t>
-  </si>
-  <si>
-    <t>AI and the future of education: Disruptions, dilemmas and directions</t>
-  </si>
-  <si>
-    <t>Policy / anthology</t>
-  </si>
-  <si>
-    <t>Official / expert collection</t>
-  </si>
-  <si>
-    <t>Explores philosophical, ethical and pedagogical dilemmas created by AI in education and human-machine co-creation.</t>
-  </si>
-  <si>
-    <t>Useful domain case study showing how general AI-ethics principles change in a real institution such as education.</t>
-  </si>
-  <si>
-    <t>Education case study; classroom discussion; policy</t>
-  </si>
-  <si>
-    <t>How should education preserve human agency, fairness and learning integrity in an AI-rich environment?</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/articles/ai-and-future-education-disruptions-dilemmas-and-directions</t>
-  </si>
-  <si>
-    <t>Published Jan 2026.</t>
-  </si>
-  <si>
-    <t>Scale, data and social harms</t>
-  </si>
-  <si>
-    <t>On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
-  </si>
-  <si>
-    <t>Bender et al.</t>
-  </si>
-  <si>
-    <t>FAccT research paper</t>
-  </si>
-  <si>
-    <t>Raises concerns about environmental cost, training-data scale, bias, documentation and the gap between linguistic form and meaning.</t>
-  </si>
-  <si>
-    <t>Foundational critical reading that explains why ethics concerns were present before today's frontier LLMs.</t>
-  </si>
-  <si>
-    <t>Historical foundation; data ethics; critical perspective</t>
-  </si>
-  <si>
-    <t>Does scaling language models without understanding data and social context create predictable harms?</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3442188.3445922</t>
-  </si>
-  <si>
-    <t>FAccT 2021; foundational.</t>
-  </si>
-  <si>
-    <t>Language-model harm taxonomy</t>
-  </si>
-  <si>
-    <t>Ethical and Social Risks of Harm from Language Models</t>
-  </si>
-  <si>
-    <t>Weidinger et al.</t>
-  </si>
-  <si>
-    <t>Risk taxonomy / research</t>
-  </si>
-  <si>
-    <t>Organizes harms around discrimination, information hazards, misinformation, malicious use, human-computer interaction and socioeconomic/environmental harms.</t>
-  </si>
-  <si>
-    <t>One of the clearest early taxonomies for turning 'LLM ethics' into categories of harm.</t>
-  </si>
-  <si>
-    <t>Foundations; risk taxonomy; related work</t>
-  </si>
-  <si>
-    <t>What types of harm can language models create, and through which pathways?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2112.04359</t>
-  </si>
-  <si>
-    <t>Published work originated from DeepMind research.</t>
-  </si>
-  <si>
-    <t>Foundation-model societal impact</t>
-  </si>
-  <si>
-    <t>On the Opportunities and Risks of Foundation Models</t>
-  </si>
-  <si>
-    <t>Bommasani et al.</t>
-  </si>
-  <si>
-    <t>Examines foundation models across capabilities, homogenization, adaptation, evaluation, robustness, security, fairness, misuse, law and societal impact.</t>
-  </si>
-  <si>
-    <t>Provides broad conceptual background for why one upstream model can propagate benefits and harms across many downstream systems.</t>
-  </si>
-  <si>
-    <t>Foundation models; societal impact; literature review</t>
-  </si>
-  <si>
-    <t>How does reliance on a small number of foundation models concentrate systemic risk?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2108.07258</t>
-  </si>
-  <si>
-    <t>Stanford CRFM foundational report.</t>
-  </si>
-  <si>
-    <t>New This Week — Automatically Discovered</t>
-  </si>
-  <si>
-    <t>Recent high-scoring discoveries from scholarly APIs and official policy pages.</t>
-  </si>
-  <si>
-    <t>Detected</t>
-  </si>
-  <si>
-    <t>Published</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Importance Score</t>
-  </si>
-  <si>
-    <t>Why flagged</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>DOI</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>2026-08-16</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>A Common Standard for AI Incident Accountability</t>
-  </si>
-  <si>
-    <t>Zenodo (CERN European Organization for Nuclear Research)</t>
-  </si>
-  <si>
-    <t>article</t>
-  </si>
-  <si>
-    <t>Must Read Candidate</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, accountability, disclosure, reporting; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21907857</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21907857</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Automatically discovered; verify bibliographic details before formal citation.</t>
-  </si>
-  <si>
-    <t>Autonomous Decision Assurance Layer for AI-Driven Enterprise Analytics: Bridging Governance, Multi-Agent AI, and Executive Decision Intelligence in Saudi Vision 2030 Organizations</t>
-  </si>
-  <si>
-    <t>International Journal for Research in Applied Science and Engineering Technology</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.22214/ijraset.2026.84573</t>
-  </si>
-  <si>
-    <t>10.22214/ijraset.2026.84573</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21907856</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21907856</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>Validating the Virtue Ethics Measurement Scale Within an Open Distance e-Learning Higher Education Institution in South Africa: Students’ Perspectives of Generative AI Practices</t>
-  </si>
-  <si>
-    <t>Algorithms</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3390/a19080682</t>
-  </si>
-  <si>
-    <t>10.3390/a19080682</t>
-  </si>
-  <si>
-    <t>2026-08-15</t>
-  </si>
-  <si>
-    <t>Examining the Impact of Social-Emotional Learning on Academic Achievement in African American Middle School Girls</t>
-  </si>
-  <si>
-    <t>Seton Hall University eRepository (Seton Hall University)</t>
-  </si>
-  <si>
-    <t>dissertation</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://openalex.org/W7160680247</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>Managing ESG and cyber risks in Kazakhstan’s low-carbon transition by aligning EU and Chinese standards through demoethics</t>
-  </si>
-  <si>
-    <t>Environment &amp; Labor</t>
-  </si>
-  <si>
-    <t>Discover Sustainability</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, sustainability; impact signal: framework, standard, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s43621-026-04260-z</t>
-  </si>
-  <si>
-    <t>10.1007/s43621-026-04260-z</t>
-  </si>
-  <si>
-    <t>Digital personas of AI use in nursing education: a latent class analysis of learning behaviors and academic engagement</t>
-  </si>
-  <si>
-    <t>Frontiers in Medicine</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fmed.2026.1859093</t>
-  </si>
-  <si>
-    <t>10.3389/fmed.2026.1859093</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>Beyond Visual Evidence: Revealing and Mitigating Relational Privacy Leakage in Document MLLMs</t>
-  </si>
-  <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>matches Privacy: privacy, leakage, extraction; impact signal: benchmark, framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12911v1</t>
-  </si>
-  <si>
-    <t>10.1145/3767308.3835901</t>
-  </si>
-  <si>
-    <t>Performance, interaction, and ethical evaluation in the use of generative artificial intelligence in engineering education</t>
-  </si>
-  <si>
-    <t>Education and Information Technologies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, regulation, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10639-026-14112-y</t>
-  </si>
-  <si>
-    <t>10.1007/s10639-026-14112-y</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>How Personal and Cognitive Traits Influence AI Attitudes, Ethics, and Well-being: The Role of AI Autonomy and Criticality in Design</t>
-  </si>
-  <si>
-    <t>SN Computer Science</t>
-  </si>
-  <si>
-    <t>matches Persuasion &amp; Manipulation: influence, autonomy; impact signal: survey, framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s42979-026-05214-y</t>
-  </si>
-  <si>
-    <t>10.1007/s42979-026-05214-y</t>
-  </si>
-  <si>
-    <t>Ethics Suppression in AI Development: A Comparative Case Study of Responsible AI Under Competitive Pressure</t>
-  </si>
-  <si>
-    <t>International Journal of Applied Research in Business and Management</t>
-  </si>
-  <si>
-    <t>matches Foundations: ethics, responsible ai; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51137/wrp.ijarbm.869</t>
-  </si>
-  <si>
-    <t>10.51137/wrp.ijarbm.869</t>
-  </si>
-  <si>
-    <t>Which LLM Is Your Ideal Companion? Evaluating Emotional Companion Capabilities of LLMs Based on Adult Attachment Theory</t>
-  </si>
-  <si>
-    <t>matches Human-AI Relationships: companion, emotional support, attachment; impact signal: benchmark, evaluation; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13168v1</t>
-  </si>
-  <si>
-    <t>InFactPlanner: Planning Sustainable Geo-Distributed LLM Data Centers</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, carbon, sustainability; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12915v1</t>
-  </si>
-  <si>
-    <t>Legitimacy Criteria for Strategic Communication in the Age of Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>The Proceedings of the World Conference on Social Sciences and Humanities.</t>
-  </si>
-  <si>
-    <t>conference-paper</t>
-  </si>
-  <si>
-    <t>matches Persuasion &amp; Manipulation: persuasion, manipulation, influence, behavioral influence; impact signal: framework, regulation, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.33422/shconf.v3i1.2047</t>
-  </si>
-  <si>
-    <t>10.33422/shconf.v3i1.2047</t>
-  </si>
-  <si>
-    <t>A carbon aware job scheduling framework for data center sustainability using deep learning training</t>
-  </si>
-  <si>
-    <t>Discover Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>journal-article</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, environment, sustainability; strong scholarly metadata source; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s44163-026-02022-4</t>
-  </si>
-  <si>
-    <t>10.1007/s44163-026-02022-4</t>
-  </si>
-  <si>
-    <t>How electoral management bodies govern digital electoral systems: capacity, authority, and accountability</t>
-  </si>
-  <si>
-    <t>Frontiers in Political Science</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: systematic review, framework, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpos.2026.1877569</t>
-  </si>
-  <si>
-    <t>10.3389/fpos.2026.1877569</t>
-  </si>
-  <si>
-    <t>Leveraging strategic facilities management to achieve corporate ESG and sustainability: a literature review</t>
-  </si>
-  <si>
-    <t>Frontiers in Environmental Economics</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: environment, sustainability; impact signal: framework, governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/frevc.2026.1839120</t>
-  </si>
-  <si>
-    <t>10.3389/frevc.2026.1839120</t>
-  </si>
-  <si>
-    <t>Benchmarking Knowledge-Extraction Attack and Defense on Retrieval-Augmented Generation (RAG)</t>
-  </si>
-  <si>
-    <t>OpenAlex</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>matches Privacy: privacy, extraction; impact signal: benchmark, framework, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3770855.3817524</t>
-  </si>
-  <si>
-    <t>10.1145/3770855.3817524</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>Governing Agentic AI in FinTech</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11344v2</t>
-  </si>
-  <si>
-    <t>Toward Meaningful Transparency for AI Chatbots: Disclosing Persuasive Intent Reduces Persuasion</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, disclosure, provenance; impact signal: regulation, policy, randomized; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11794v1</t>
-  </si>
-  <si>
-    <t>Research on the Judicial Fairness Challenges and Legal Regulation of AI-Assisted Judgments in the Context of Digital Justice</t>
-  </si>
-  <si>
-    <t>Advanced Electromagnetics</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.7716/aem.v15i3.3403</t>
-  </si>
-  <si>
-    <t>10.7716/aem.v15i3.3403</t>
-  </si>
-  <si>
-    <t>The Correlation Between Exposure to English-Language Content on Instagram and Listening Comprehension among EFL Students at UIN Datokarama Palu</t>
-  </si>
-  <si>
-    <t>Journal of General Education and Humanities</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.58421/gehu.v5i4.1936</t>
-  </si>
-  <si>
-    <t>10.58421/gehu.v5i4.1936</t>
-  </si>
-  <si>
-    <t>Motivation to learn and teach home economics in higher education: Predictors and comparative analysis</t>
-  </si>
-  <si>
-    <t>Social Sciences &amp; Humanities Open</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.ssaho.2026.103414</t>
-  </si>
-  <si>
-    <t>10.1016/j.ssaho.2026.103414</t>
-  </si>
-  <si>
-    <t>AI literacy and subject specialization in pre-service teacher education: a mixed-methods study of dimensional profiles and perceived pedagogical challenges</t>
-  </si>
-  <si>
-    <t>Frontiers in Education</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1876627</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1876627</t>
-  </si>
-  <si>
-    <t>PENGARUH MUSIK AI TERHADAP PENINGKATAN MOTIVASI BELAJAR SISWA PADA MATA PELAJARAN IPS DI KELAS IV SD NEGERI 73 AMBON</t>
-  </si>
-  <si>
-    <t>SOCIAL : Jurnal Inovasi Pendidikan IPS</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51878/social.v6i3.14523</t>
-  </si>
-  <si>
-    <t>10.51878/social.v6i3.14523</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>Physical Processing of Aquatic Gel Foods: From Protein Structure Regulation to Health, Sustainability, and Personalized Design</t>
-  </si>
-  <si>
-    <t>Comprehensive Reviews in Food Science and Food Safety</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, sustainability; strong scholarly metadata source; impact signal: regulation, standard, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/1541-4337.70601</t>
-  </si>
-  <si>
-    <t>10.1111/1541-4337.70601</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>ChatGPT and Large Language Models in Contemporary Nursing</t>
-  </si>
-  <si>
-    <t>Journal of Clinical Nursing</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/jocn.70490</t>
-  </si>
-  <si>
-    <t>10.1111/jocn.70490</t>
-  </si>
-  <si>
-    <t>Software Engineering for and with GUI Agent</t>
-  </si>
-  <si>
-    <t>arXiv (Cornell University)</t>
-  </si>
-  <si>
-    <t>preprint</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, evaluation, audit; impact signal: benchmark, framework, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.48550/arxiv.2608.09278</t>
-  </si>
-  <si>
-    <t>10.48550/arxiv.2608.09278</t>
-  </si>
-  <si>
-    <t>Banking Performance under the Lens of Earnings Management: A Theoretical and Bibliometric Systematic Review</t>
-  </si>
-  <si>
-    <t>Bulletin of Social Studies and Community Development</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, disclosure, reporting; impact signal: systematic review, framework, guidelines; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.61436/bsscd/v5i3.pp253-267</t>
-  </si>
-  <si>
-    <t>10.61436/bsscd/v5i3.pp253-267</t>
-  </si>
-  <si>
-    <t>Pedagogical prompting rather than technical mastery: Generative AI use by English and English-medium instruction teachers</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1901680</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1901680</t>
-  </si>
-  <si>
-    <t>Applied and Filtered: An End-to-End Algorithmic Fairness Audit of A Public Employment Agency</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: evaluation, audit; impact signal: evaluation, audit; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13022v1</t>
-  </si>
-  <si>
-    <t>Pre-service teachers' general pedagogical knowledge and pedagogical learning opportunities at entry into induction: comparing traditional and alternative teacher education programs</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: standard, longitudinal; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1790135</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1790135</t>
-  </si>
-  <si>
-    <t>Dysfunction of Zakat Village Governance in Papua: Fragmentation of Collaboration and Inequality of Amil Capacity</t>
-  </si>
-  <si>
-    <t>JURNAL ILMIAH GEMA PERENCANA</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, evaluation; strong scholarly metadata source; impact signal: framework, regulation, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.61860/jigp.v5i1.411</t>
-  </si>
-  <si>
-    <t>10.61860/jigp.v5i1.411</t>
-  </si>
-  <si>
-    <t>Human-centric AI governance in the European Union. Accountability, fundamental rights, and institutional resilience in public administration</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpos.2026.1928481</t>
-  </si>
-  <si>
-    <t>10.3389/fpos.2026.1928481</t>
-  </si>
-  <si>
-    <t>PENGARUH MODEL PEMBELAJARAN PROJECT BASED LEARNING DAN KEDISIPLINAN BELAJAR TERHADAP KESIAPAN KERJA SISWA PADA JURUSAN AKUNTANSI KEUANGAN LEMABAGA DI SMK NEGERI 1 PANGKEP</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; impact signal: survey; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51878/social.v6i3.14617</t>
-  </si>
-  <si>
-    <t>10.51878/social.v6i3.14617</t>
-  </si>
-  <si>
-    <t>Large Language Model-facilitated national review on the use of ecological tools and processes in Environmental Impact Statements (EIS) in the U.S. with demonstrated use cases for environmental planners, legal practitioners, and researchers</t>
-  </si>
-  <si>
-    <t>Springer Science and Business Media LLC</t>
-  </si>
-  <si>
-    <t>posted-content</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, environment, labor; strong scholarly metadata source; impact signal: benchmark, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.21203/rs.3.rs-10627892/v1</t>
-  </si>
-  <si>
-    <t>10.21203/rs.3.rs-10627892/v1</t>
-  </si>
-  <si>
-    <t>Optimization of Household Equipment and Instrumentation in an Effort to Save Electrical Energy in a Restaurant</t>
-  </si>
-  <si>
-    <t>International Journal Of Community Service</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, environment; strong scholarly metadata source; impact signal: survey, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51601/ijcs.v6i3.1022</t>
-  </si>
-  <si>
-    <t>10.51601/ijcs.v6i3.1022</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>From Single Chatbots to Governed Agent Ecosystems: An Agentic AI Pattern Catalogue and Orchestration Framework for Mission-Critical Hospital Information Management Systems</t>
-  </si>
-  <si>
-    <t>matches Agentic AI: agentic ai, autonomous agent, multi-agent; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.07627v1</t>
-  </si>
-  <si>
-    <t>10.38124/ijisrt/26jul830</t>
-  </si>
-  <si>
-    <t>Bias Smells in AI Software Development: Recognizing Potential Sources of Fairness Debt</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.48550/arxiv.2608.10248</t>
-  </si>
-  <si>
-    <t>10.48550/arxiv.2608.10248</t>
-  </si>
-  <si>
-    <t>Quantifying the Relationship Between Clinical Safety and Environmental Impact in Therapeutic LLMs</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, carbon, environment; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11830v1</t>
-  </si>
-  <si>
-    <t>Benchmark-Based Comparative Assessment of Publicly Benchmarked Indian Foundation Models: A Capability and Evaluation-Maturity Framework</t>
-  </si>
-  <si>
-    <t>matches India &amp; Global South: multilingual, india; impact signal: survey, benchmark, framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11891v1</t>
-  </si>
-  <si>
-    <t>Academic League of Artificial Intelligence - An Integrative Perspective of Teaching, Research, and Extension</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13447v1</t>
-  </si>
-  <si>
-    <t>Solar Exposure and Photoprotection Behaviors as Determinants of Acne Vulgaris Severity Among University Students in Andalusia-Spain</t>
-  </si>
-  <si>
-    <t>Ibn Sina Journal of Medical Science Health &amp; Pharmacy</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; impact signal: survey, framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.64440/ibnsina/sina0027</t>
-  </si>
-  <si>
-    <t>10.64440/ibnsina/sina0027</t>
-  </si>
-  <si>
-    <t>FSGR: Mitigating Token Frequency Bias for Fair SID-Based Generative Recommendation</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12845v1</t>
-  </si>
-  <si>
-    <t>HEPE — Complete 16-State AI Governance Space with Lyapunov Values (Hardware-Enforced Policy Engine)</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: policy, governance, audit; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21935563</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21935563</t>
-  </si>
-  <si>
-    <t>What Remains Ours to Think? Reclaiming Critical Thinking in AI‐Augmented Student Leadership Education</t>
-  </si>
-  <si>
-    <t>New Directions for Student Leadership</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/yd.70068</t>
-  </si>
-  <si>
-    <t>10.1002/yd.70068</t>
-  </si>
-  <si>
-    <t>Supervision in educational leadership: practices, challenges, and innovations in the UAE — a multi-level coupling analysis of the current and future</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: benchmark, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1862260</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1862260</t>
-  </si>
-  <si>
-    <t>Research ethics and publication policies in journals using the Korea Institute of Science and Technology Information (KISTI) academic publishing platform: a content analysis of 181 journals</t>
-  </si>
-  <si>
-    <t>Science Editing</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: accountability, disclosure; impact signal: guidelines, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.6087/kcse.403</t>
-  </si>
-  <si>
-    <t>10.6087/kcse.403</t>
-  </si>
-  <si>
-    <t>Striking a Balance between the Right to Privacy and Freedom of Expression: A Case Study of Women’s Digital Rights in Tanzania</t>
-  </si>
-  <si>
-    <t>East African Journal of Law and Ethics</t>
-  </si>
-  <si>
-    <t>matches Regulation: regulation, legal framework, standard; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.37284/eajle.9.3.5557</t>
-  </si>
-  <si>
-    <t>10.37284/eajle.9.3.5557</t>
-  </si>
-  <si>
-    <t>Evaluation of the CIPP Model in a Project-Based Basic Electronics Course: A Discriminant Validity and Common Method Bias Analysis</t>
-  </si>
-  <si>
-    <t>Educative: Jurnal Ilmiah Pendidikan</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.70437/educative.v4i2.2180</t>
-  </si>
-  <si>
-    <t>10.70437/educative.v4i2.2180</t>
-  </si>
-  <si>
-    <t>Review Queue — Human-in-the-loop Curation</t>
-  </si>
-  <si>
-    <t>Promote only sources that are genuinely useful. Automatic discovery is intentionally not identical to automatic curation.</t>
-  </si>
-  <si>
-    <t>Topic Map — What to Read for Each AI / LLM Ethics Question</t>
-  </si>
-  <si>
-    <t>Theme-level map generated from the current curated library.</t>
-  </si>
-  <si>
-    <t>Sources in library</t>
-  </si>
-  <si>
-    <t>2026-heavy?</t>
-  </si>
-  <si>
-    <t>Start with</t>
-  </si>
-  <si>
-    <t>Then read</t>
-  </si>
-  <si>
-    <t>Typical reader question</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Recommendation on the Ethics of Artificial Intelligence; On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1); Guidelines for providers of general-purpose AI models</t>
-  </si>
-  <si>
-    <t>An Evaluation of AI Companion Apps; Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
-  </si>
-  <si>
-    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders; Evaluating Language Models for Harmful Manipulation</t>
-  </si>
-  <si>
-    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory; SoK: The Privacy Paradox of Large Language Models</t>
-  </si>
-  <si>
-    <t>2026-Only View</t>
-  </si>
-  <si>
-    <t>Current-year curated items.</t>
-  </si>
-  <si>
-    <t>Policy, Governance &amp; Regulation</t>
-  </si>
-  <si>
-    <t>Curated governance, standards, transparency, law and human-rights sources.</t>
-  </si>
-  <si>
-    <t>Source Configuration</t>
-  </si>
-  <si>
-    <t>Edit config/sources.yaml in the repository to change the automation. This sheet is a readable mirror.</t>
-  </si>
-  <si>
-    <t>Endpoint / URL</t>
-  </si>
-  <si>
-    <t>Enabled</t>
-  </si>
-  <si>
-    <t>Authority</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>https://export.arxiv.org/api/query</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Fresh preprints</t>
-  </si>
-  <si>
-    <t>3-second delay between repeated calls</t>
-  </si>
-  <si>
-    <t>https://api.openalex.org/works</t>
-  </si>
-  <si>
-    <t>Broad scholarly discovery</t>
-  </si>
-  <si>
-    <t>OPENALEX_API_KEY optional</t>
-  </si>
-  <si>
-    <t>Crossref</t>
-  </si>
-  <si>
-    <t>https://api.crossref.org/works</t>
-  </si>
-  <si>
-    <t>Published DOI metadata</t>
-  </si>
-  <si>
-    <t>CONTACT_EMAIL recommended</t>
-  </si>
-  <si>
-    <t>NIST Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Official page watch</t>
-  </si>
-  <si>
-    <t>https://www.nist.gov/artificial-intelligence</t>
-  </si>
-  <si>
-    <t>Policy/news link discovery</t>
-  </si>
-  <si>
-    <t>First scan bootstraps without flooding</t>
-  </si>
-  <si>
-    <t>European Commission AI Act</t>
-  </si>
-  <si>
-    <t>OECD.AI Wonk</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/wonk</t>
-  </si>
-  <si>
-    <t>UNESCO Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/artificial-intelligence</t>
-  </si>
-  <si>
-    <t>IndiaAI Safe &amp; Trusted AI</t>
-  </si>
-  <si>
-    <t>https://indiaai.gov.in/hub/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>Automation Update Log</t>
-  </si>
-  <si>
-    <t>Every run records discovery and deduplication counts.</t>
-  </si>
-  <si>
-    <t>New This Week</t>
-  </si>
-  <si>
-    <t>Review Queue</t>
-  </si>
-  <si>
-    <t>Auto-promoted</t>
-  </si>
-  <si>
-    <t>2026-08-16T12:18:00+05:30</t>
-  </si>
-  <si>
-    <t>Initial build</t>
-  </si>
-  <si>
-    <t>Living tracker package initialized</t>
   </si>
   <si>
     <t>Automation Guide</t>
@@ -3067,10 +3085,10 @@
         <v>17</v>
       </c>
       <c r="C5" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" s="4">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3148,7 +3166,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3257,7 +3275,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="22.7109375" customWidth="1"/>
@@ -3267,7 +3285,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>721</v>
+        <v>726</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3280,7 +3298,7 @@
     </row>
     <row r="2" spans="1:9" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>722</v>
+        <v>727</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3308,13 +3326,13 @@
         <v>31</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>32</v>
@@ -3322,10 +3340,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>726</v>
+        <v>731</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>727</v>
+        <v>732</v>
       </c>
       <c r="C5" s="7">
         <v>8</v>
@@ -3346,12 +3364,12 @@
         <v>0</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>728</v>
+        <v>733</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
-        <v>26</v>
+        <v>734</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>28</v>
@@ -3375,6 +3393,35 @@
         <v>0</v>
       </c>
       <c r="I6" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7">
+        <v>28</v>
+      </c>
+      <c r="D7" s="7">
+        <v>635</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="7">
+        <v>51</v>
+      </c>
+      <c r="G7" s="7">
+        <v>51</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3402,7 +3449,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3412,7 +3459,7 @@
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3425,16 +3472,16 @@
         <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>428</v>
@@ -3445,19 +3492,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3465,19 +3512,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3485,19 +3532,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>746</v>
+        <v>752</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3505,19 +3552,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>747</v>
+        <v>753</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>748</v>
+        <v>754</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>749</v>
+        <v>755</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>751</v>
+        <v>757</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3525,19 +3572,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>752</v>
+        <v>758</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>753</v>
+        <v>759</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>754</v>
+        <v>760</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>750</v>
+        <v>756</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>755</v>
+        <v>761</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3545,19 +3592,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>757</v>
+        <v>763</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>758</v>
+        <v>764</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>759</v>
+        <v>765</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>760</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -5989,7 +6036,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="13.7109375" customWidth="1"/>
@@ -6209,34 +6256,34 @@
         <v>429</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>448</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>449</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G8" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>434</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>438</v>
@@ -6250,19 +6297,19 @@
         <v>429</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="G9" s="7">
         <v>93</v>
@@ -6276,7 +6323,9 @@
       <c r="J9" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="K9" s="7"/>
+      <c r="K9" s="7" t="s">
+        <v>459</v>
+      </c>
       <c r="L9" s="7" t="s">
         <v>438</v>
       </c>
@@ -6289,35 +6338,33 @@
         <v>429</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>462</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="G10" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>434</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K10" s="7" t="s">
         <v>465</v>
       </c>
+      <c r="K10" s="7"/>
       <c r="L10" s="7" t="s">
         <v>438</v>
       </c>
@@ -6330,25 +6377,25 @@
         <v>429</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>19</v>
+        <v>448</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>433</v>
       </c>
       <c r="G11" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>469</v>
@@ -6371,25 +6418,25 @@
         <v>429</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G12" s="7">
+        <v>89</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G12" s="7">
-        <v>87</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>468</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>475</v>
@@ -6412,34 +6459,34 @@
         <v>429</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G13" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>438</v>
@@ -6453,13 +6500,13 @@
         <v>429</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>484</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>485</v>
@@ -6468,10 +6515,10 @@
         <v>433</v>
       </c>
       <c r="G14" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>486</v>
@@ -6494,16 +6541,16 @@
         <v>429</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>447</v>
+        <v>489</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>433</v>
@@ -6512,16 +6559,16 @@
         <v>84</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>438</v>
@@ -6535,33 +6582,35 @@
         <v>429</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G16" s="7">
+        <v>84</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G16" s="7">
-        <v>83</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>468</v>
-      </c>
       <c r="I16" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="K16" s="7"/>
+        <v>498</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>499</v>
+      </c>
       <c r="L16" s="7" t="s">
         <v>438</v>
       </c>
@@ -6574,16 +6623,16 @@
         <v>429</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>461</v>
+        <v>11</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>252</v>
@@ -6592,13 +6641,13 @@
         <v>83</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7" t="s">
@@ -6613,35 +6662,33 @@
         <v>429</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>13</v>
+        <v>448</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>502</v>
+        <v>252</v>
       </c>
       <c r="G18" s="7">
         <v>83</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="K18" s="7" t="s">
         <v>505</v>
       </c>
+      <c r="K18" s="7"/>
       <c r="L18" s="7" t="s">
         <v>438</v>
       </c>
@@ -6654,13 +6701,13 @@
         <v>429</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>506</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>461</v>
+        <v>13</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>507</v>
@@ -6669,10 +6716,10 @@
         <v>508</v>
       </c>
       <c r="G19" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>509</v>
@@ -6695,25 +6742,25 @@
         <v>429</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>472</v>
+        <v>429</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>512</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>10</v>
+        <v>448</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>513</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G20" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>514</v>
@@ -6736,13 +6783,13 @@
         <v>429</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>517</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>461</v>
+        <v>10</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>518</v>
@@ -6754,7 +6801,7 @@
         <v>81</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>519</v>
@@ -6777,34 +6824,34 @@
         <v>429</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>522</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>12</v>
+        <v>448</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>523</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>502</v>
+        <v>433</v>
       </c>
       <c r="G22" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H22" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="J22" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="K22" s="7" t="s">
         <v>526</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>527</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>438</v>
@@ -6818,25 +6865,25 @@
         <v>429</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>474</v>
-      </c>
       <c r="F23" s="7" t="s">
-        <v>252</v>
+        <v>508</v>
       </c>
       <c r="G23" s="7">
         <v>79</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>530</v>
@@ -6844,7 +6891,9 @@
       <c r="J23" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="K23" s="7"/>
+      <c r="K23" s="7" t="s">
+        <v>532</v>
+      </c>
       <c r="L23" s="7" t="s">
         <v>438</v>
       </c>
@@ -6857,16 +6906,16 @@
         <v>429</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>430</v>
+        <v>533</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>252</v>
@@ -6875,13 +6924,13 @@
         <v>79</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7" t="s">
@@ -6896,35 +6945,33 @@
         <v>429</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>536</v>
+        <v>480</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G25" s="7">
         <v>79</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="K25" s="7" t="s">
         <v>539</v>
       </c>
+      <c r="K25" s="7"/>
       <c r="L25" s="7" t="s">
         <v>438</v>
       </c>
@@ -6937,25 +6984,25 @@
         <v>429</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>540</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>541</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G26" s="7">
         <v>79</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>542</v>
@@ -6978,7 +7025,7 @@
         <v>429</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>430</v>
+        <v>460</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>545</v>
@@ -6990,13 +7037,13 @@
         <v>546</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G27" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>547</v>
@@ -7019,7 +7066,7 @@
         <v>429</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>550</v>
@@ -7034,19 +7081,19 @@
         <v>433</v>
       </c>
       <c r="G28" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>469</v>
+        <v>552</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>438</v>
@@ -7060,28 +7107,28 @@
         <v>429</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G29" s="7">
         <v>77</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>556</v>
+        <v>475</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>557</v>
@@ -7101,34 +7148,34 @@
         <v>429</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>561</v>
-      </c>
       <c r="F30" s="7" t="s">
-        <v>508</v>
+        <v>450</v>
       </c>
       <c r="G30" s="7">
         <v>77</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I30" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>564</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>438</v>
@@ -7142,34 +7189,34 @@
         <v>429</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G31" s="7">
+        <v>77</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="G31" s="7">
-        <v>76</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="J31" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="7" t="s">
         <v>569</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>570</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>438</v>
@@ -7183,34 +7230,34 @@
         <v>429</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>483</v>
+        <v>570</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>571</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>572</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>573</v>
+        <v>433</v>
       </c>
       <c r="G32" s="7">
         <v>76</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I32" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="7" t="s">
         <v>575</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>576</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>438</v>
@@ -7224,34 +7271,34 @@
         <v>429</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>578</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>579</v>
       </c>
       <c r="G33" s="7">
         <v>76</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I33" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="7" t="s">
         <v>581</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>582</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>438</v>
@@ -7265,34 +7312,34 @@
         <v>429</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="7" t="s">
         <v>583</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>551</v>
-      </c>
       <c r="F34" s="7" t="s">
-        <v>433</v>
+        <v>584</v>
       </c>
       <c r="G34" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>438</v>
@@ -7306,33 +7353,35 @@
         <v>429</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>474</v>
+        <v>556</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>252</v>
+        <v>433</v>
       </c>
       <c r="G35" s="7">
         <v>75</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="K35" s="7"/>
+        <v>590</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>591</v>
+      </c>
       <c r="L35" s="7" t="s">
         <v>438</v>
       </c>
@@ -7345,35 +7394,33 @@
         <v>429</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>551</v>
+        <v>480</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G36" s="7">
         <v>75</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>592</v>
-      </c>
-      <c r="K36" s="7" t="s">
-        <v>593</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="K36" s="7"/>
       <c r="L36" s="7" t="s">
         <v>438</v>
       </c>
@@ -7386,25 +7433,25 @@
         <v>429</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>595</v>
+        <v>556</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G37" s="7">
         <v>75</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>596</v>
@@ -7427,7 +7474,7 @@
         <v>429</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>599</v>
@@ -7436,25 +7483,25 @@
         <v>10</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>513</v>
+        <v>600</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G38" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L38" s="7" t="s">
         <v>438</v>
@@ -7468,34 +7515,34 @@
         <v>429</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>555</v>
+        <v>518</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G39" s="7">
         <v>74</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>438</v>
@@ -7509,34 +7556,34 @@
         <v>429</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>608</v>
+        <v>560</v>
       </c>
       <c r="F40" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G40" s="7">
+        <v>74</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="I40" s="7" t="s">
         <v>609</v>
       </c>
-      <c r="G40" s="7">
-        <v>73</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="I40" s="7" t="s">
+      <c r="J40" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="J40" s="8" t="s">
+      <c r="K40" s="7" t="s">
         <v>611</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>612</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>438</v>
@@ -7550,25 +7597,25 @@
         <v>429</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E41" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>614</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>508</v>
       </c>
       <c r="G41" s="7">
         <v>73</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>615</v>
@@ -7591,25 +7638,25 @@
         <v>429</v>
       </c>
       <c r="B42" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C42" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="D42" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>619</v>
       </c>
-      <c r="D42" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>474</v>
-      </c>
       <c r="F42" s="7" t="s">
-        <v>252</v>
+        <v>450</v>
       </c>
       <c r="G42" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>620</v>
@@ -7632,34 +7679,34 @@
         <v>429</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>483</v>
+        <v>623</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>573</v>
+        <v>252</v>
       </c>
       <c r="G43" s="7">
         <v>72</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>438</v>
@@ -7673,33 +7720,35 @@
         <v>429</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>430</v>
+        <v>489</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>461</v>
+        <v>18</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>474</v>
+        <v>577</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>252</v>
+        <v>578</v>
       </c>
       <c r="G44" s="7">
         <v>72</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="K44" s="7"/>
+        <v>630</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>631</v>
+      </c>
       <c r="L44" s="7" t="s">
         <v>438</v>
       </c>
@@ -7715,13 +7764,13 @@
         <v>430</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>15</v>
+        <v>448</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>252</v>
@@ -7730,13 +7779,13 @@
         <v>72</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
@@ -7751,16 +7800,16 @@
         <v>429</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>252</v>
@@ -7769,13 +7818,13 @@
         <v>72</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7" t="s">
@@ -7790,35 +7839,33 @@
         <v>429</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="D47" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>637</v>
+        <v>480</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G47" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="K47" s="7" t="s">
         <v>640</v>
       </c>
+      <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
         <v>438</v>
       </c>
@@ -7831,33 +7878,35 @@
         <v>429</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>641</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>474</v>
+        <v>642</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>252</v>
+        <v>433</v>
       </c>
       <c r="G48" s="7">
         <v>71</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="K48" s="7"/>
+        <v>644</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>645</v>
+      </c>
       <c r="L48" s="7" t="s">
         <v>438</v>
       </c>
@@ -7870,35 +7919,33 @@
         <v>429</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>573</v>
+        <v>252</v>
       </c>
       <c r="G49" s="7">
         <v>71</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>647</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="K49" s="7"/>
       <c r="L49" s="7" t="s">
         <v>438</v>
       </c>
@@ -7911,34 +7958,34 @@
         <v>429</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>649</v>
+        <v>577</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>433</v>
+        <v>578</v>
       </c>
       <c r="G50" s="7">
         <v>71</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>438</v>
@@ -7952,16 +7999,16 @@
         <v>429</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D51" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>551</v>
+        <v>654</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>433</v>
@@ -7970,16 +8017,16 @@
         <v>71</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>653</v>
+        <v>589</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>438</v>
@@ -7993,16 +8040,16 @@
         <v>429</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>657</v>
+        <v>556</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>433</v>
@@ -8011,7 +8058,7 @@
         <v>71</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>658</v>
@@ -8034,13 +8081,13 @@
         <v>429</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C53" s="7" t="s">
         <v>661</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>662</v>
@@ -8052,7 +8099,7 @@
         <v>71</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>663</v>
@@ -8075,25 +8122,25 @@
         <v>429</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>666</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>667</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G54" s="7">
         <v>71</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>668</v>
@@ -8111,13 +8158,54 @@
         <v>439</v>
       </c>
     </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>672</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G55" s="7">
+        <v>71</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>439</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M54"/>
+  <autoFilter ref="A4:M55"/>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G54">
+  <conditionalFormatting sqref="G5:G55">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -8180,6 +8268,7 @@
     <hyperlink ref="J52" r:id="rId48"/>
     <hyperlink ref="J53" r:id="rId49"/>
     <hyperlink ref="J54" r:id="rId50"/>
+    <hyperlink ref="J55" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8187,7 +8276,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="13.7109375" customWidth="1"/>
@@ -8206,7 +8295,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8223,7 +8312,7 @@
     </row>
     <row r="2" spans="1:13" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8407,34 +8496,34 @@
         <v>429</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>448</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>19</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>449</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G8" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>434</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>438</v>
@@ -8448,19 +8537,19 @@
         <v>429</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>456</v>
+        <v>433</v>
       </c>
       <c r="G9" s="7">
         <v>93</v>
@@ -8474,7 +8563,9 @@
       <c r="J9" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="K9" s="7"/>
+      <c r="K9" s="7" t="s">
+        <v>459</v>
+      </c>
       <c r="L9" s="7" t="s">
         <v>438</v>
       </c>
@@ -8487,35 +8578,33 @@
         <v>429</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>461</v>
+        <v>19</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>462</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="G10" s="7">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>434</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>464</v>
-      </c>
-      <c r="K10" s="7" t="s">
         <v>465</v>
       </c>
+      <c r="K10" s="7"/>
       <c r="L10" s="7" t="s">
         <v>438</v>
       </c>
@@ -8528,25 +8617,25 @@
         <v>429</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>19</v>
+        <v>448</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>433</v>
       </c>
       <c r="G11" s="7">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>468</v>
+        <v>434</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>469</v>
@@ -8569,25 +8658,25 @@
         <v>429</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="D12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="F12" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G12" s="7">
+        <v>89</v>
+      </c>
+      <c r="H12" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G12" s="7">
-        <v>87</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>468</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>475</v>
@@ -8610,34 +8699,34 @@
         <v>429</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G13" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>438</v>
@@ -8651,34 +8740,34 @@
         <v>429</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>433</v>
       </c>
       <c r="G14" s="7">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L14" s="7" t="s">
         <v>438</v>
@@ -8692,16 +8781,16 @@
         <v>429</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>433</v>
@@ -8710,16 +8799,16 @@
         <v>84</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>438</v>
@@ -8733,33 +8822,35 @@
         <v>429</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G16" s="7">
+        <v>84</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="K16" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>474</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="G16" s="7">
-        <v>83</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>496</v>
-      </c>
-      <c r="K16" s="7"/>
       <c r="L16" s="7" t="s">
         <v>438</v>
       </c>
@@ -8772,16 +8863,16 @@
         <v>429</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>461</v>
+        <v>11</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>252</v>
@@ -8790,13 +8881,13 @@
         <v>83</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="7" t="s">
@@ -8811,35 +8902,33 @@
         <v>429</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>13</v>
+        <v>448</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>502</v>
+        <v>252</v>
       </c>
       <c r="G18" s="7">
         <v>83</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>504</v>
-      </c>
-      <c r="K18" s="7" t="s">
         <v>505</v>
       </c>
+      <c r="K18" s="7"/>
       <c r="L18" s="7" t="s">
         <v>438</v>
       </c>
@@ -8852,13 +8941,13 @@
         <v>429</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>506</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>461</v>
+        <v>13</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>507</v>
@@ -8867,10 +8956,10 @@
         <v>508</v>
       </c>
       <c r="G19" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>509</v>
@@ -8893,34 +8982,34 @@
         <v>429</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G20" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L20" s="7" t="s">
         <v>438</v>
@@ -8934,16 +9023,16 @@
         <v>429</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>10</v>
+        <v>448</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>433</v>
@@ -8952,16 +9041,16 @@
         <v>81</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="L21" s="7" t="s">
         <v>438</v>
@@ -8975,34 +9064,34 @@
         <v>429</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>540</v>
+        <v>517</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>541</v>
+        <v>518</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G22" s="7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>524</v>
+        <v>474</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>542</v>
+        <v>519</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>544</v>
+        <v>521</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>438</v>
@@ -9016,34 +9105,34 @@
         <v>429</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>522</v>
+        <v>545</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>523</v>
+        <v>546</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>502</v>
+        <v>450</v>
       </c>
       <c r="G23" s="7">
         <v>79</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>525</v>
+        <v>547</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>526</v>
+        <v>548</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>527</v>
+        <v>549</v>
       </c>
       <c r="L23" s="7" t="s">
         <v>438</v>
@@ -9057,25 +9146,25 @@
         <v>429</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>528</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>529</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>474</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>252</v>
+        <v>508</v>
       </c>
       <c r="G24" s="7">
         <v>79</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>530</v>
@@ -9083,7 +9172,9 @@
       <c r="J24" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="K24" s="7"/>
+      <c r="K24" s="7" t="s">
+        <v>532</v>
+      </c>
       <c r="L24" s="7" t="s">
         <v>438</v>
       </c>
@@ -9096,16 +9187,16 @@
         <v>429</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>430</v>
+        <v>533</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>252</v>
@@ -9114,13 +9205,13 @@
         <v>79</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="7" t="s">
@@ -9135,35 +9226,33 @@
         <v>429</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>472</v>
+        <v>430</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>536</v>
+        <v>480</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G26" s="7">
         <v>79</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="K26" s="7" t="s">
         <v>539</v>
       </c>
+      <c r="K26" s="7"/>
       <c r="L26" s="7" t="s">
         <v>438</v>
       </c>
@@ -9176,34 +9265,34 @@
         <v>429</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>430</v>
+        <v>478</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>433</v>
       </c>
       <c r="G27" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="L27" s="7" t="s">
         <v>438</v>
@@ -9217,7 +9306,7 @@
         <v>429</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>550</v>
@@ -9232,19 +9321,19 @@
         <v>433</v>
       </c>
       <c r="G28" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>469</v>
+        <v>552</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L28" s="7" t="s">
         <v>438</v>
@@ -9258,28 +9347,28 @@
         <v>429</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G29" s="7">
         <v>77</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>556</v>
+        <v>475</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>557</v>
@@ -9299,34 +9388,34 @@
         <v>429</v>
       </c>
       <c r="B30" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="D30" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>561</v>
-      </c>
       <c r="F30" s="7" t="s">
-        <v>508</v>
+        <v>450</v>
       </c>
       <c r="G30" s="7">
         <v>77</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I30" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="J30" s="8" t="s">
         <v>562</v>
       </c>
-      <c r="J30" s="8" t="s">
+      <c r="K30" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>564</v>
       </c>
       <c r="L30" s="7" t="s">
         <v>438</v>
@@ -9340,34 +9429,34 @@
         <v>429</v>
       </c>
       <c r="B31" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="D31" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E31" s="7" t="s">
+      <c r="F31" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="G31" s="7">
+        <v>77</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="G31" s="7">
-        <v>76</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="J31" s="8" t="s">
         <v>568</v>
       </c>
-      <c r="J31" s="8" t="s">
+      <c r="K31" s="7" t="s">
         <v>569</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>570</v>
       </c>
       <c r="L31" s="7" t="s">
         <v>438</v>
@@ -9381,34 +9470,34 @@
         <v>429</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>483</v>
+        <v>570</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>571</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>572</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>573</v>
+        <v>433</v>
       </c>
       <c r="G32" s="7">
         <v>76</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I32" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="J32" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="J32" s="8" t="s">
+      <c r="K32" s="7" t="s">
         <v>575</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>576</v>
       </c>
       <c r="L32" s="7" t="s">
         <v>438</v>
@@ -9422,34 +9511,34 @@
         <v>429</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E33" s="7" t="s">
+      <c r="F33" s="7" t="s">
         <v>578</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>579</v>
       </c>
       <c r="G33" s="7">
         <v>76</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I33" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="J33" s="8" t="s">
         <v>580</v>
       </c>
-      <c r="J33" s="8" t="s">
+      <c r="K33" s="7" t="s">
         <v>581</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>582</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>438</v>
@@ -9463,34 +9552,34 @@
         <v>429</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>433</v>
+        <v>584</v>
       </c>
       <c r="G34" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="L34" s="7" t="s">
         <v>438</v>
@@ -9504,16 +9593,16 @@
         <v>429</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="D35" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>433</v>
@@ -9522,16 +9611,16 @@
         <v>75</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="K35" s="7" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="L35" s="7" t="s">
         <v>438</v>
@@ -9545,34 +9634,34 @@
         <v>429</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>595</v>
+        <v>556</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G36" s="7">
         <v>75</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="L36" s="7" t="s">
         <v>438</v>
@@ -9586,33 +9675,35 @@
         <v>429</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="D37" s="7" t="s">
         <v>10</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>474</v>
+        <v>600</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>252</v>
+        <v>450</v>
       </c>
       <c r="G37" s="7">
         <v>75</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>589</v>
-      </c>
-      <c r="K37" s="7"/>
+        <v>602</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>603</v>
+      </c>
       <c r="L37" s="7" t="s">
         <v>438</v>
       </c>
@@ -9625,35 +9716,33 @@
         <v>429</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>555</v>
+        <v>480</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>508</v>
+        <v>252</v>
       </c>
       <c r="G38" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>605</v>
-      </c>
-      <c r="K38" s="7" t="s">
-        <v>606</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="K38" s="7"/>
       <c r="L38" s="7" t="s">
         <v>438</v>
       </c>
@@ -9666,34 +9755,34 @@
         <v>429</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>513</v>
+        <v>560</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="G39" s="7">
         <v>74</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="L39" s="7" t="s">
         <v>438</v>
@@ -9707,34 +9796,34 @@
         <v>429</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C40" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G40" s="7">
+        <v>74</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="K40" s="7" t="s">
         <v>607</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="G40" s="7">
-        <v>73</v>
-      </c>
-      <c r="H40" s="7" t="s">
-        <v>524</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>611</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>612</v>
       </c>
       <c r="L40" s="7" t="s">
         <v>438</v>
@@ -9748,25 +9837,25 @@
         <v>429</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>429</v>
+        <v>460</v>
       </c>
       <c r="C41" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>613</v>
       </c>
-      <c r="D41" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E41" s="7" t="s">
+      <c r="F41" s="7" t="s">
         <v>614</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>508</v>
       </c>
       <c r="G41" s="7">
         <v>73</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>615</v>
@@ -9789,33 +9878,35 @@
         <v>429</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>474</v>
+        <v>619</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>252</v>
+        <v>450</v>
       </c>
       <c r="G42" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="J42" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="K42" s="7"/>
+        <v>621</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>622</v>
+      </c>
       <c r="L42" s="7" t="s">
         <v>438</v>
       </c>
@@ -9828,35 +9919,33 @@
         <v>429</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>483</v>
+        <v>430</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>18</v>
+        <v>448</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>573</v>
+        <v>252</v>
       </c>
       <c r="G43" s="7">
         <v>72</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>625</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>626</v>
-      </c>
+        <v>634</v>
+      </c>
+      <c r="K43" s="7"/>
       <c r="L43" s="7" t="s">
         <v>438</v>
       </c>
@@ -9869,33 +9958,35 @@
         <v>429</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>430</v>
+        <v>489</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>474</v>
+        <v>577</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>252</v>
+        <v>578</v>
       </c>
       <c r="G44" s="7">
         <v>72</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I44" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="J44" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="K44" s="7" t="s">
         <v>631</v>
       </c>
-      <c r="J44" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="K44" s="7"/>
       <c r="L44" s="7" t="s">
         <v>438</v>
       </c>
@@ -9908,16 +9999,16 @@
         <v>429</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>618</v>
+        <v>430</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>619</v>
+        <v>635</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>252</v>
@@ -9926,17 +10017,15 @@
         <v>72</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>622</v>
-      </c>
+        <v>637</v>
+      </c>
+      <c r="K45" s="7"/>
       <c r="L45" s="7" t="s">
         <v>438</v>
       </c>
@@ -9949,16 +10038,16 @@
         <v>429</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>472</v>
+        <v>623</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>252</v>
@@ -9967,15 +10056,17 @@
         <v>72</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="K46" s="7"/>
+        <v>626</v>
+      </c>
+      <c r="K46" s="7" t="s">
+        <v>627</v>
+      </c>
       <c r="L46" s="7" t="s">
         <v>438</v>
       </c>
@@ -9988,35 +10079,33 @@
         <v>429</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>572</v>
+        <v>480</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>573</v>
+        <v>252</v>
       </c>
       <c r="G47" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="K47" s="7" t="s">
-        <v>647</v>
-      </c>
+        <v>640</v>
+      </c>
+      <c r="K47" s="7"/>
       <c r="L47" s="7" t="s">
         <v>438</v>
       </c>
@@ -10029,34 +10118,34 @@
         <v>429</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>649</v>
+        <v>577</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>433</v>
+        <v>578</v>
       </c>
       <c r="G48" s="7">
         <v>71</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>584</v>
+        <v>650</v>
       </c>
       <c r="J48" s="8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>438</v>
@@ -10070,16 +10159,16 @@
         <v>429</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="D49" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
       <c r="F49" s="7" t="s">
         <v>433</v>
@@ -10088,16 +10177,16 @@
         <v>71</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>638</v>
+        <v>589</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="L49" s="7" t="s">
         <v>438</v>
@@ -10111,34 +10200,34 @@
         <v>429</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>429</v>
+        <v>478</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>666</v>
+        <v>641</v>
       </c>
       <c r="D50" s="7" t="s">
         <v>19</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>667</v>
+        <v>642</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>508</v>
+        <v>433</v>
       </c>
       <c r="G50" s="7">
         <v>71</v>
       </c>
       <c r="H50" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>668</v>
+        <v>643</v>
       </c>
       <c r="J50" s="8" t="s">
-        <v>669</v>
+        <v>644</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>670</v>
+        <v>645</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>438</v>
@@ -10152,33 +10241,35 @@
         <v>429</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>472</v>
+        <v>429</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>641</v>
+        <v>671</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>474</v>
+        <v>672</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>252</v>
+        <v>450</v>
       </c>
       <c r="G51" s="7">
         <v>71</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>642</v>
+        <v>673</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>643</v>
-      </c>
-      <c r="K51" s="7"/>
+        <v>674</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>675</v>
+      </c>
       <c r="L51" s="7" t="s">
         <v>438</v>
       </c>
@@ -10191,35 +10282,33 @@
         <v>429</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>551</v>
+        <v>480</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>433</v>
+        <v>252</v>
       </c>
       <c r="G52" s="7">
         <v>71</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="K52" s="7" t="s">
-        <v>655</v>
-      </c>
+        <v>648</v>
+      </c>
+      <c r="K52" s="7"/>
       <c r="L52" s="7" t="s">
         <v>438</v>
       </c>
@@ -10232,16 +10321,16 @@
         <v>429</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>657</v>
+        <v>556</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>433</v>
@@ -10250,7 +10339,7 @@
         <v>71</v>
       </c>
       <c r="H53" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>658</v>
@@ -10273,13 +10362,13 @@
         <v>429</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="C54" s="7" t="s">
         <v>661</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>662</v>
@@ -10291,7 +10380,7 @@
         <v>71</v>
       </c>
       <c r="H54" s="7" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>663</v>
@@ -10309,13 +10398,54 @@
         <v>439</v>
       </c>
     </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>667</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="G55" s="7">
+        <v>71</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="J55" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="K55" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>439</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:M54"/>
+  <autoFilter ref="A4:M55"/>
   <mergeCells count="2">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G54">
+  <conditionalFormatting sqref="G5:G55">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -10378,6 +10508,7 @@
     <hyperlink ref="J52" r:id="rId48"/>
     <hyperlink ref="J53" r:id="rId49"/>
     <hyperlink ref="J54" r:id="rId50"/>
+    <hyperlink ref="J55" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10396,7 +10527,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10406,7 +10537,7 @@
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10419,19 +10550,19 @@
         <v>7</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10442,7 +10573,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>62</v>
@@ -10462,7 +10593,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>220</v>
@@ -10480,7 +10611,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>380</v>
@@ -10498,7 +10629,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>208</v>
@@ -10516,13 +10647,13 @@
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>400</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>406</v>
@@ -10536,13 +10667,13 @@
         <v>4</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>47</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>93</v>
@@ -10556,7 +10687,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>231</v>
@@ -10574,7 +10705,7 @@
         <v>1</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>185</v>
@@ -10592,13 +10723,13 @@
         <v>4</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>56</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>333</v>
@@ -10612,7 +10743,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>66</v>
@@ -10632,13 +10763,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>54</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>685</v>
+        <v>690</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>284</v>
@@ -10652,13 +10783,13 @@
         <v>4</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>240</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>686</v>
+        <v>691</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>246</v>
@@ -10672,7 +10803,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>50</v>
@@ -10690,7 +10821,7 @@
         <v>2</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>52</v>
@@ -10710,7 +10841,7 @@
         <v>2</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>309</v>
@@ -10756,7 +10887,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>687</v>
+        <v>692</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10778,7 +10909,7 @@
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11860,7 +11991,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11882,7 +12013,7 @@
     </row>
     <row r="2" spans="1:18" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12781,7 +12912,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>691</v>
+        <v>696</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12792,7 +12923,7 @@
     </row>
     <row r="2" spans="1:7" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12809,16 +12940,16 @@
         <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>428</v>
@@ -12826,186 +12957,186 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="7" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E5" s="7">
         <v>76</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="7" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E6" s="7">
         <v>84</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="7" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E7" s="7">
         <v>88</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="7" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E8" s="7">
         <v>100</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="7" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E9" s="7">
         <v>100</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>715</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>710</v>
-      </c>
       <c r="C10" s="8" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E10" s="7">
         <v>98</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="7" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>718</v>
+        <v>723</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E11" s="7">
         <v>98</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="7" t="s">
-        <v>719</v>
+        <v>724</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>720</v>
+        <v>725</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="E12" s="7">
         <v>98</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/AI_LLM_Ethics_Living_Tracker.xlsx
+++ b/AI_LLM_Ethics_Living_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2970" uniqueCount="851">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="852">
   <si>
     <t>AI &amp; LLM Ethics — Living Literature Dashboard</t>
   </si>
@@ -111,2383 +111,2386 @@
     <t>Run time</t>
   </si>
   <si>
+    <t>2026-08-16T10:48:23+00:00</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>scheduled/manual</t>
+  </si>
+  <si>
+    <t>Sources checked</t>
+  </si>
+  <si>
+    <t>Candidates fetched</t>
+  </si>
+  <si>
+    <t>New after dedupe</t>
+  </si>
+  <si>
+    <t>Errors / notes</t>
+  </si>
+  <si>
+    <t>Completed without recorded source errors</t>
+  </si>
+  <si>
+    <t>Start Here — 2026-aware AI &amp; LLM Ethics Reading Path</t>
+  </si>
+  <si>
+    <t>Use this sheet for a compact orientation. The automated discovery tabs are intentionally separate from the stable reading path.</t>
+  </si>
+  <si>
+    <t>Curated sources</t>
+  </si>
+  <si>
+    <t>2026 sources</t>
+  </si>
+  <si>
+    <t>Must Read</t>
+  </si>
+  <si>
+    <t>Official / institutional</t>
+  </si>
+  <si>
+    <t>Recommended 10-source reading path</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Read this</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Why now</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Source URL</t>
+  </si>
+  <si>
+    <t>Responsible AI | The 2026 AI Index Report</t>
+  </si>
+  <si>
+    <t>Current 2025–2026 evidence or governance update</t>
+  </si>
+  <si>
+    <t>https://hai.stanford.edu/ai-index/2026-ai-index-report/responsible-ai</t>
+  </si>
+  <si>
+    <t>AI Act | Shaping Europe's digital future</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/regulatory-framework-ai</t>
+  </si>
+  <si>
+    <t>Guidelines on transparency obligations for providers and deployers of AI systems</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-transparency-ai-generated-content</t>
+  </si>
+  <si>
+    <t>Persuasion with Large Language Models: A Survey of Empirical Studies</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2411.06837v2</t>
+  </si>
+  <si>
+    <t>Emotional Support with Conversational AI: Talking to Machines About Life</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2603.22618v1</t>
+  </si>
+  <si>
+    <t>An Evaluation of AI Companion Apps</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2605.08093v2</t>
+  </si>
+  <si>
+    <t>Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2606.04150</t>
+  </si>
+  <si>
+    <t>Towards Agentic AI Governance: A Preliminary Assessment</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2607.07612</t>
+  </si>
+  <si>
+    <t>The 2025 Foundation Model Transparency Index</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2512.10169</t>
+  </si>
+  <si>
+    <t>India AI Governance Guidelines: Empowering Ethical and Responsible AI</t>
+  </si>
+  <si>
+    <t>https://indiaai.gov.in/article/india-ai-governance-guidelines-empowering-ethical-and-responsible-ai</t>
+  </si>
+  <si>
+    <t>Ethics of Artificial Intelligence &amp; LLMs — Curated Reading Library</t>
+  </si>
+  <si>
+    <t>Stable curated sources. Automatically discovered items are triaged separately before promotion.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Subtopic</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Author / Body</t>
+  </si>
+  <si>
+    <t>Source Type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>What it covers</t>
+  </si>
+  <si>
+    <t>Why the reader benefits</t>
+  </si>
+  <si>
+    <t>Best use</t>
+  </si>
+  <si>
+    <t>2026 Relevance Score</t>
+  </si>
+  <si>
+    <t>Read Priority</t>
+  </si>
+  <si>
+    <t>Region / Scope</t>
+  </si>
+  <si>
+    <t>Key ethical question</t>
+  </si>
+  <si>
+    <t>Notes / status</t>
+  </si>
+  <si>
+    <t>Reader mode</t>
+  </si>
+  <si>
+    <t>Responsible AI state of the field</t>
+  </si>
+  <si>
+    <t>Stanford HAI / AI Index</t>
+  </si>
+  <si>
+    <t>Annual evidence report</t>
+  </si>
+  <si>
+    <t>Institutional / data-driven</t>
+  </si>
+  <si>
+    <t>Tracks AI incidents, safety evaluation, transparency, responsible-AI reporting, and the widening gap between capability and governance.</t>
+  </si>
+  <si>
+    <t>Best current snapshot for showing that AI capability is advancing faster than safety measurement and transparency.</t>
+  </si>
+  <si>
+    <t>Lecture opener; literature review motivation; 2026 statistics</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Are current evaluation and governance systems keeping pace with frontier AI capability?</t>
+  </si>
+  <si>
+    <t>2026 edition; strong source for current facts and figures.</t>
+  </si>
+  <si>
+    <t>Read closely</t>
+  </si>
+  <si>
+    <t>Foundation model transparency</t>
+  </si>
+  <si>
+    <t>Wan et al. / Stanford CRFM</t>
+  </si>
+  <si>
+    <t>Research report / index</t>
+  </si>
+  <si>
+    <t>Research report</t>
+  </si>
+  <si>
+    <t>Scores major foundation-model developers on disclosures covering data, compute, risk mitigation, usage and downstream impacts.</t>
+  </si>
+  <si>
+    <t>Lets readers move from vague calls for transparency to measurable disclosure dimensions and compare developers.</t>
+  </si>
+  <si>
+    <t>Transparency section; accountability case study; assignment</t>
+  </si>
+  <si>
+    <t>Global / industry</t>
+  </si>
+  <si>
+    <t>What information should frontier-model developers be required to disclose?</t>
+  </si>
+  <si>
+    <t>Average score fell from 58/100 in 2024 to 40/100 in 2025.</t>
+  </si>
+  <si>
+    <t>EU AI Act implementation</t>
+  </si>
+  <si>
+    <t>European Commission</t>
+  </si>
+  <si>
+    <t>Regulation / official guidance</t>
+  </si>
+  <si>
+    <t>Official</t>
+  </si>
+  <si>
+    <t>Official overview of the EU AI Act, risk-based obligations, implementation timeline, GPAI rules and transparency requirements.</t>
+  </si>
+  <si>
+    <t>Provides the clearest bridge between ethics principles and enforceable legal duties in 2026.</t>
+  </si>
+  <si>
+    <t>Regulation module; compliance discussion; policy comparison</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>When should ethical expectations become legal obligations?</t>
+  </si>
+  <si>
+    <t>General application date: 2 August 2026, with exceptions and phased provisions.</t>
+  </si>
+  <si>
+    <t>AI-generated content disclosure</t>
+  </si>
+  <si>
+    <t>Regulatory guidance</t>
+  </si>
+  <si>
+    <t>Explains Article 50 duties concerning user disclosure, machine-readable marking, AI-generated content and deepfakes.</t>
+  </si>
+  <si>
+    <t>Useful concrete example of how transparency ethics becomes a product-design requirement.</t>
+  </si>
+  <si>
+    <t>Deepfakes; disclosure; generative-AI product design</t>
+  </si>
+  <si>
+    <t>Should people always know when they are interacting with AI or seeing AI-generated content?</t>
+  </si>
+  <si>
+    <t>Article 50 applies from 2 August 2026.</t>
+  </si>
+  <si>
+    <t>General-purpose AI obligations</t>
+  </si>
+  <si>
+    <t>Guidelines for providers of general-purpose AI models</t>
+  </si>
+  <si>
+    <t>Clarifies obligations for providers of general-purpose AI models and the Commission's enforcement role.</t>
+  </si>
+  <si>
+    <t>Gives readers a current compliance perspective on frontier and general-purpose models rather than generic AI regulation.</t>
+  </si>
+  <si>
+    <t>GPAI governance; provider responsibilities; seminar discussion</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>What extra duties should apply to powerful general-purpose models?</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-gpai-providers</t>
+  </si>
+  <si>
+    <t>Commission enforcement powers apply from 2 August 2026.</t>
+  </si>
+  <si>
+    <t>Read/skim</t>
+  </si>
+  <si>
+    <t>India AI governance</t>
+  </si>
+  <si>
+    <t>IndiaAI / MeitY</t>
+  </si>
+  <si>
+    <t>National governance guidance</t>
+  </si>
+  <si>
+    <t>Sets out principles and recommendations around fairness, accountability, safety, inclusivity and trustworthy AI in India.</t>
+  </si>
+  <si>
+    <t>Adds an India-specific governance perspective and prevents the reading list from being US/EU-centric.</t>
+  </si>
+  <si>
+    <t>India case study; policy comparison; local context</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>How should responsible AI governance reflect India's scale, diversity and public-interest priorities?</t>
+  </si>
+  <si>
+    <t>Released 5 Nov 2025 under the IndiaAI Mission.</t>
+  </si>
+  <si>
+    <t>AI safety capacity</t>
+  </si>
+  <si>
+    <t>Safe &amp; Trusted AI Working Group</t>
+  </si>
+  <si>
+    <t>India AI Impact Summit</t>
+  </si>
+  <si>
+    <t>Policy / working-group output</t>
+  </si>
+  <si>
+    <t>Focuses on AI safety capacity, evaluation, governance and incorporating Global South perspectives into international AI safety frameworks.</t>
+  </si>
+  <si>
+    <t>Useful for understanding how safety debates are being localized beyond US/EU institutions.</t>
+  </si>
+  <si>
+    <t>India 2026 update; global governance; discussion prompt</t>
+  </si>
+  <si>
+    <t>India / Global South</t>
+  </si>
+  <si>
+    <t>Who gets to define acceptable AI risk and safety standards globally?</t>
+  </si>
+  <si>
+    <t>https://impact.indiaai.gov.in/working-groups/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>2026-relevant IndiaAI Impact Summit initiative.</t>
+  </si>
+  <si>
+    <t>Risk management framework</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1)</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>Risk-management framework</t>
+  </si>
+  <si>
+    <t>Identifies GenAI-specific risks and actions across the AI lifecycle, aligned with Govern, Map, Measure and Manage.</t>
+  </si>
+  <si>
+    <t>One of the most practical sources for converting ethical concerns into operational risk controls.</t>
+  </si>
+  <si>
+    <t>Risk register; deployment checklist; governance design</t>
+  </si>
+  <si>
+    <t>United States / cross-sector</t>
+  </si>
+  <si>
+    <t>How can an organization operationalize trustworthy GenAI rather than merely state principles?</t>
+  </si>
+  <si>
+    <t>https://www.nist.gov/publications/artificial-intelligence-risk-management-framework-generative-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>Companion to NIST AI RMF 1.0.</t>
+  </si>
+  <si>
+    <t>Human-rights-centered AI ethics</t>
+  </si>
+  <si>
+    <t>Recommendation on the Ethics of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>UNESCO</t>
+  </si>
+  <si>
+    <t>International ethics standard</t>
+  </si>
+  <si>
+    <t>Defines principles including proportionality, do-no-harm, safety, privacy, fairness, transparency, accountability, sustainability and human oversight.</t>
+  </si>
+  <si>
+    <t>Provides a normative foundation for almost every later AI ethics topic.</t>
+  </si>
+  <si>
+    <t>Foundations lecture; ethics framework; compare policies</t>
+  </si>
+  <si>
+    <t>What values should guide the design and deployment of AI systems?</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
+  </si>
+  <si>
+    <t>Global UNESCO recommendation; remains foundational in 2026.</t>
+  </si>
+  <si>
+    <t>Trustworthy AI principles</t>
+  </si>
+  <si>
+    <t>OECD AI Principles</t>
+  </si>
+  <si>
+    <t>OECD</t>
+  </si>
+  <si>
+    <t>International policy principles</t>
+  </si>
+  <si>
+    <t>Principles for innovative and trustworthy AI, covering human rights, fairness, transparency, robustness, security and accountability.</t>
+  </si>
+  <si>
+    <t>Concise policy baseline that is easy to compare against NIST, UNESCO, EU and national frameworks.</t>
+  </si>
+  <si>
+    <t>Framework comparison; policy lecture; exam preparation</t>
+  </si>
+  <si>
+    <t>What minimum principles should trustworthy AI systems satisfy across countries?</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/ai-principles</t>
+  </si>
+  <si>
+    <t>Initially adopted 2019; updated May 2024.</t>
+  </si>
+  <si>
+    <t>International AI treaty</t>
+  </si>
+  <si>
+    <t>Framework Convention on Artificial Intelligence and Human Rights, Democracy and the Rule of Law</t>
+  </si>
+  <si>
+    <t>Council of Europe</t>
+  </si>
+  <si>
+    <t>International treaty</t>
+  </si>
+  <si>
+    <t>Official / legally binding framework</t>
+  </si>
+  <si>
+    <t>Addresses human rights, democratic processes, autonomy, transparency, accountability, equality and privacy across the AI lifecycle.</t>
+  </si>
+  <si>
+    <t>Shows the transition from voluntary ethics to treaty-based human-rights obligations.</t>
+  </si>
+  <si>
+    <t>Human-rights module; legal governance; global policy</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>How should AI development be constrained when it may affect fundamental rights and democratic institutions?</t>
+  </si>
+  <si>
+    <t>https://www.coe.int/en/web/artificial-intelligence/the-framework-convention-on-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>First international legally binding treaty in this field; opened for signature 5 Sept 2024.</t>
+  </si>
+  <si>
+    <t>Developer risk reporting</t>
+  </si>
+  <si>
+    <t>How are AI developers managing risks? Insights from the Hiroshima AI Process reporting framework</t>
+  </si>
+  <si>
+    <t>International governance report</t>
+  </si>
+  <si>
+    <t>Official / multi-stakeholder</t>
+  </si>
+  <si>
+    <t>Analyzes how organizations report risk identification, safety, governance, content authentication and accountability practices.</t>
+  </si>
+  <si>
+    <t>Gives concrete examples of how frontier developers operationalize risk management, not just what principles say.</t>
+  </si>
+  <si>
+    <t>Industry governance; transparency; comparative analysis</t>
+  </si>
+  <si>
+    <t>G7 / global</t>
+  </si>
+  <si>
+    <t>Can voluntary transparency meaningfully improve accountability for advanced AI developers?</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/ai-publications/how-are-ai-developers-managing-risks-insights-from-responses-to-the-reporting-framework-of-the-hiroshima-ai-process-code-of-conduct</t>
+  </si>
+  <si>
+    <t>Reporting framework launched in 2025.</t>
+  </si>
+  <si>
+    <t>Comprehensive LLM ethics</t>
+  </si>
+  <si>
+    <t>Deconstructing the ethics of large language models from long-standing issues to new-emerging dilemmas</t>
+  </si>
+  <si>
+    <t>Deng et al.</t>
+  </si>
+  <si>
+    <t>Survey / review</t>
+  </si>
+  <si>
+    <t>Peer-reviewed</t>
+  </si>
+  <si>
+    <t>Surveys copyright, systematic bias, privacy, truthfulness, social norms and emerging ethical challenges of LLMs.</t>
+  </si>
+  <si>
+    <t>Good single-paper orientation before readers enter specialized literatures.</t>
+  </si>
+  <si>
+    <t>Literature review starting point; seminar reading</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Which LLM ethical risks are old problems amplified by scale, and which are genuinely new?</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s43681-025-00797-3</t>
+  </si>
+  <si>
+    <t>Published in AI and Ethics.</t>
+  </si>
+  <si>
+    <t>Bias evaluation and mitigation</t>
+  </si>
+  <si>
+    <t>Bias and Fairness in Large Language Models: A Survey</t>
+  </si>
+  <si>
+    <t>Gallegos et al.</t>
+  </si>
+  <si>
+    <t>Survey</t>
+  </si>
+  <si>
+    <t>Research / arXiv</t>
+  </si>
+  <si>
+    <t>Organizes social bias harms, evaluation metrics, datasets and mitigation techniques for LLMs.</t>
+  </si>
+  <si>
+    <t>Provides a technical taxonomy that makes 'AI bias' measurable rather than purely rhetorical.</t>
+  </si>
+  <si>
+    <t>Bias lecture; evaluation design; related work</t>
+  </si>
+  <si>
+    <t>How should fairness be defined and measured for generative language systems?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2309.00770</t>
+  </si>
+  <si>
+    <t>Still a useful technical survey in 2026.</t>
+  </si>
+  <si>
+    <t>Hallucination taxonomy</t>
+  </si>
+  <si>
+    <t>A Survey on Hallucination in Large Language Models</t>
+  </si>
+  <si>
+    <t>ACM Computing Surveys</t>
+  </si>
+  <si>
+    <t>Reviews hallucination principles, taxonomies, causes, evaluation, detection and mitigation in LLMs.</t>
+  </si>
+  <si>
+    <t>Helps distinguish factual reliability problems from broader moral or social harms.</t>
+  </si>
+  <si>
+    <t>Truthfulness; reliability; high-stakes deployment</t>
+  </si>
+  <si>
+    <t>When is an incorrect LLM output merely an error, and when does it become an ethical harm?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3703155</t>
+  </si>
+  <si>
+    <t>High-value technical survey.</t>
+  </si>
+  <si>
+    <t>Training-data leakage</t>
+  </si>
+  <si>
+    <t>New Privacy Risks for Large Language Models</t>
+  </si>
+  <si>
+    <t>Research paper</t>
+  </si>
+  <si>
+    <t>Preprint / current research</t>
+  </si>
+  <si>
+    <t>Examines data extraction and memorization risks, connecting privacy leakage with copyright and training-data provenance concerns.</t>
+  </si>
+  <si>
+    <t>Useful 2026 update showing privacy risk is not limited to classic membership inference.</t>
+  </si>
+  <si>
+    <t>Privacy section; training data; model memorization</t>
+  </si>
+  <si>
+    <t>What does a model owe people whose private or copyrighted data it can reproduce?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2509.14278v2</t>
+  </si>
+  <si>
+    <t>Version available Jan 2026.</t>
+  </si>
+  <si>
+    <t>Privacy threat landscape</t>
+  </si>
+  <si>
+    <t>SoK: The Privacy Paradox of Large Language Models</t>
+  </si>
+  <si>
+    <t>Systematization of knowledge</t>
+  </si>
+  <si>
+    <t>Preprint / research</t>
+  </si>
+  <si>
+    <t>Systematizes training-data extraction, reconstruction, inference-time privacy and protection mechanisms.</t>
+  </si>
+  <si>
+    <t>Gives readers a map of privacy attack surfaces instead of isolated examples.</t>
+  </si>
+  <si>
+    <t>Security/privacy module; research gap identification</t>
+  </si>
+  <si>
+    <t>Can LLM utility and strong privacy guarantees be achieved simultaneously?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2506.12699v2</t>
+  </si>
+  <si>
+    <t>Useful bridge between AI ethics and security.</t>
+  </si>
+  <si>
+    <t>Empirical privacy evaluation</t>
+  </si>
+  <si>
+    <t>Privacy Auditing of Large Language Models</t>
+  </si>
+  <si>
+    <t>Develops stronger privacy auditing techniques and more effective canaries for estimating empirical leakage.</t>
+  </si>
+  <si>
+    <t>Shows readers how privacy claims can be tested rather than assumed.</t>
+  </si>
+  <si>
+    <t>Methodology; model audit; technical assignment</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>How should developers demonstrate that a language model is not leaking training data?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2503.06808v1</t>
+  </si>
+  <si>
+    <t>Technical privacy-auditing work.</t>
+  </si>
+  <si>
+    <t>Reference as needed</t>
+  </si>
+  <si>
+    <t>Agent memory and contextual leakage</t>
+  </si>
+  <si>
+    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory</t>
+  </si>
+  <si>
+    <t>Security research</t>
+  </si>
+  <si>
+    <t>Studies privacy leakage from inference-time contextual memory in LLM agents, beyond training-data privacy.</t>
+  </si>
+  <si>
+    <t>Important for 2026 because persistent AI assistants and agents create a new privacy attack surface.</t>
+  </si>
+  <si>
+    <t>Agentic AI; memory privacy; security discussion</t>
+  </si>
+  <si>
+    <t>Research / agents</t>
+  </si>
+  <si>
+    <t>What privacy risks appear when AI systems remember and act on user context over time?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2604.23711v1</t>
+  </si>
+  <si>
+    <t>2026 agent-memory privacy paper.</t>
+  </si>
+  <si>
+    <t>Persuasion landscape</t>
+  </si>
+  <si>
+    <t>Research survey</t>
+  </si>
+  <si>
+    <t>Reviews empirical evidence on automated, personalized and interactive LLM persuasion and its effects on attitudes and behavior.</t>
+  </si>
+  <si>
+    <t>A direct entry point into one of the most important newer AI-ethics issues.</t>
+  </si>
+  <si>
+    <t>Manipulation lecture; social influence; governance</t>
+  </si>
+  <si>
+    <t>When does helpful persuasion become manipulation or undue influence?</t>
+  </si>
+  <si>
+    <t>Updated Apr 2026.</t>
+  </si>
+  <si>
+    <t>Human vs AI persuasion</t>
+  </si>
+  <si>
+    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders</t>
+  </si>
+  <si>
+    <t>Schoenegger et al.</t>
+  </si>
+  <si>
+    <t>Large-scale experiment</t>
+  </si>
+  <si>
+    <t>Compares a frontier LLM with incentivized human persuaders in interactive settings and measures compliance with correct and incorrect persuasion.</t>
+  </si>
+  <si>
+    <t>Provides concrete empirical evidence that persuasive capability can create both benefits and harms.</t>
+  </si>
+  <si>
+    <t>Case study; empirical evidence; class discussion</t>
+  </si>
+  <si>
+    <t>Should systems with human-level or greater persuasive power face special safeguards?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2505.09662</t>
+  </si>
+  <si>
+    <t>Preregistered, large-scale incentivized experiment.</t>
+  </si>
+  <si>
+    <t>Harmful influence evaluation</t>
+  </si>
+  <si>
+    <t>Evaluating Language Models for Harmful Manipulation</t>
+  </si>
+  <si>
+    <t>Akbulut et al.</t>
+  </si>
+  <si>
+    <t>Human-subject evaluation</t>
+  </si>
+  <si>
+    <t>Research / preprint</t>
+  </si>
+  <si>
+    <t>Introduces a framework for measuring harmful manipulation across public policy, finance and health with participants from multiple countries.</t>
+  </si>
+  <si>
+    <t>Shows how manipulation can be operationalized and evaluated across consequential domains.</t>
+  </si>
+  <si>
+    <t>Evaluation design; high-stakes AI; cross-country analysis</t>
+  </si>
+  <si>
+    <t>US / UK / India</t>
+  </si>
+  <si>
+    <t>How can harmful manipulation be measured before deployment?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2603.25326</t>
+  </si>
+  <si>
+    <t>Includes 10,101 participants across three locales.</t>
+  </si>
+  <si>
+    <t>Sycophancy to strategic deception</t>
+  </si>
+  <si>
+    <t>From Sycophancy to Deception: A Unified Taxonomy for Misleading LLM Behavior</t>
+  </si>
+  <si>
+    <t>Taxonomy / research</t>
+  </si>
+  <si>
+    <t>Unifies hallucination, omission, pragmatic distortion, sycophancy and strategic deception under a common taxonomy of misleading behavior.</t>
+  </si>
+  <si>
+    <t>Helps readers avoid treating all misleading model outputs as the same failure mode.</t>
+  </si>
+  <si>
+    <t>Conceptual framework; deception; research taxonomy</t>
+  </si>
+  <si>
+    <t>Does intent or goal-directedness change how ethically serious misleading AI behavior is?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2604.04788</t>
+  </si>
+  <si>
+    <t>Current 2026 taxonomy.</t>
+  </si>
+  <si>
+    <t>Sycophancy</t>
+  </si>
+  <si>
+    <t>Sycophancy in Large Language Models: Causes and Mitigations</t>
+  </si>
+  <si>
+    <t>Lars Malmqvist</t>
+  </si>
+  <si>
+    <t>Technical survey</t>
+  </si>
+  <si>
+    <t>Surveys excessive agreement with users, causes, measurement and mitigation, and links sycophancy to hallucination and bias.</t>
+  </si>
+  <si>
+    <t>Useful for discussing why 'agreeable' assistants can become epistemically unsafe.</t>
+  </si>
+  <si>
+    <t>Alignment; user trust; truthfulness</t>
+  </si>
+  <si>
+    <t>Should an assistant prioritize user satisfaction or epistemic honesty when they conflict?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2411.15287</t>
+  </si>
+  <si>
+    <t>Technical survey.</t>
+  </si>
+  <si>
+    <t>Emotional support</t>
+  </si>
+  <si>
+    <t>Huang, Stodolska &amp; Sultana</t>
+  </si>
+  <si>
+    <t>Qualitative HCI research</t>
+  </si>
+  <si>
+    <t>Analyzes how emotional support is co-constructed with AI companions and tensions such as support vs dependency and validation vs delusion.</t>
+  </si>
+  <si>
+    <t>Provides nuanced evidence beyond simplistic claims that AI companions are either beneficial or harmful.</t>
+  </si>
+  <si>
+    <t>HCI ethics; mental-health-adjacent discussion; companionship</t>
+  </si>
+  <si>
+    <t>How should AI offer emotional support without reinforcing dependency or harmful beliefs?</t>
+  </si>
+  <si>
+    <t>2026 HCI-focused research.</t>
+  </si>
+  <si>
+    <t>Companion-app design</t>
+  </si>
+  <si>
+    <t>Empirical audit</t>
+  </si>
+  <si>
+    <t>Audits popular AI companion apps for dark patterns, anthropomorphism, stereotypes, erotica and technical issues.</t>
+  </si>
+  <si>
+    <t>Connects ethical risk to actual interface and monetization design choices, not only model behavior.</t>
+  </si>
+  <si>
+    <t>Product ethics; dark patterns; companion AI</t>
+  </si>
+  <si>
+    <t>EU / UK market</t>
+  </si>
+  <si>
+    <t>Can product incentives push AI companions toward manipulative engagement?</t>
+  </si>
+  <si>
+    <t>Version updated Aug 2026.</t>
+  </si>
+  <si>
+    <t>Emotional dependence</t>
+  </si>
+  <si>
+    <t>Shi et al.</t>
+  </si>
+  <si>
+    <t>Perspective / evidence synthesis</t>
+  </si>
+  <si>
+    <t>Argues that emotional dependence can emerge incidentally in general-purpose AI use and may alter future preferences for human vs AI support.</t>
+  </si>
+  <si>
+    <t>Highlights cumulative interaction effects that one-shot safety evaluations can miss.</t>
+  </si>
+  <si>
+    <t>Long-term interaction ethics; product policy; research gaps</t>
+  </si>
+  <si>
+    <t>Should general-purpose assistants be evaluated for long-term relational effects, not just single-turn harms?</t>
+  </si>
+  <si>
+    <t>Includes synthesis of longitudinal evidence.</t>
+  </si>
+  <si>
+    <t>Identity and parasocial interaction</t>
+  </si>
+  <si>
+    <t>Negotiating Digital Identities with AI Companions</t>
+  </si>
+  <si>
+    <t>HCI / computational social science</t>
+  </si>
+  <si>
+    <t>Studies identity construction and negotiation in AI-companion communities using large-scale online discussions.</t>
+  </si>
+  <si>
+    <t>Useful for understanding anthropomorphism and dependence as social processes rather than merely UI bugs.</t>
+  </si>
+  <si>
+    <t>HCI seminar; identity; anthropomorphism</t>
+  </si>
+  <si>
+    <t>How do AI companions reshape users' identities, expectations and social relationships?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2601.12181v1</t>
+  </si>
+  <si>
+    <t>Analyzes 22,374 online discussions.</t>
+  </si>
+  <si>
+    <t>Governance of autonomous agents</t>
+  </si>
+  <si>
+    <t>Raji &amp; Bashir</t>
+  </si>
+  <si>
+    <t>Systematic review</t>
+  </si>
+  <si>
+    <t>Reviews governance priorities, mechanisms and stakeholder roles for AI systems that autonomously plan and execute tasks.</t>
+  </si>
+  <si>
+    <t>Important 2026 bridge from chatbot ethics to systems that can act in the world.</t>
+  </si>
+  <si>
+    <t>Agentic AI governance; research agenda; seminar</t>
+  </si>
+  <si>
+    <t>How should accountability change when AI can plan, call tools and execute actions autonomously?</t>
+  </si>
+  <si>
+    <t>Published Jul 2026.</t>
+  </si>
+  <si>
+    <t>Security and governance practice</t>
+  </si>
+  <si>
+    <t>State of Agentic AI Security and Governance</t>
+  </si>
+  <si>
+    <t>OWASP GenAI Security Project</t>
+  </si>
+  <si>
+    <t>Security / governance report</t>
+  </si>
+  <si>
+    <t>Practitioner standard</t>
+  </si>
+  <si>
+    <t>Covers governance and security issues for autonomous AI systems, including controls, oversight and operational risk.</t>
+  </si>
+  <si>
+    <t>Gives practitioners a deployment-oriented complement to academic governance work.</t>
+  </si>
+  <si>
+    <t>Agent security; enterprise governance; checklist design</t>
+  </si>
+  <si>
+    <t>What controls are necessary when agents receive tools, permissions and persistent access?</t>
+  </si>
+  <si>
+    <t>https://genai.owasp.org/resource/state-of-agentic-ai-security-and-governance/</t>
+  </si>
+  <si>
+    <t>Practitioner-focused resource.</t>
+  </si>
+  <si>
+    <t>AI in education ethics</t>
+  </si>
+  <si>
+    <t>AI and the future of education: Disruptions, dilemmas and directions</t>
+  </si>
+  <si>
+    <t>Policy / anthology</t>
+  </si>
+  <si>
+    <t>Official / expert collection</t>
+  </si>
+  <si>
+    <t>Explores philosophical, ethical and pedagogical dilemmas created by AI in education and human-machine co-creation.</t>
+  </si>
+  <si>
+    <t>Useful domain case study showing how general AI-ethics principles change in a real institution such as education.</t>
+  </si>
+  <si>
+    <t>Education case study; classroom discussion; policy</t>
+  </si>
+  <si>
+    <t>How should education preserve human agency, fairness and learning integrity in an AI-rich environment?</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/articles/ai-and-future-education-disruptions-dilemmas-and-directions</t>
+  </si>
+  <si>
+    <t>Published Jan 2026.</t>
+  </si>
+  <si>
+    <t>Scale, data and social harms</t>
+  </si>
+  <si>
+    <t>On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
+  </si>
+  <si>
+    <t>Bender et al.</t>
+  </si>
+  <si>
+    <t>FAccT research paper</t>
+  </si>
+  <si>
+    <t>Raises concerns about environmental cost, training-data scale, bias, documentation and the gap between linguistic form and meaning.</t>
+  </si>
+  <si>
+    <t>Foundational critical reading that explains why ethics concerns were present before today's frontier LLMs.</t>
+  </si>
+  <si>
+    <t>Historical foundation; data ethics; critical perspective</t>
+  </si>
+  <si>
+    <t>Does scaling language models without understanding data and social context create predictable harms?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3442188.3445922</t>
+  </si>
+  <si>
+    <t>FAccT 2021; foundational.</t>
+  </si>
+  <si>
+    <t>Language-model harm taxonomy</t>
+  </si>
+  <si>
+    <t>Ethical and Social Risks of Harm from Language Models</t>
+  </si>
+  <si>
+    <t>Weidinger et al.</t>
+  </si>
+  <si>
+    <t>Risk taxonomy / research</t>
+  </si>
+  <si>
+    <t>Organizes harms around discrimination, information hazards, misinformation, malicious use, human-computer interaction and socioeconomic/environmental harms.</t>
+  </si>
+  <si>
+    <t>One of the clearest early taxonomies for turning 'LLM ethics' into categories of harm.</t>
+  </si>
+  <si>
+    <t>Foundations; risk taxonomy; related work</t>
+  </si>
+  <si>
+    <t>What types of harm can language models create, and through which pathways?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2112.04359</t>
+  </si>
+  <si>
+    <t>Published work originated from DeepMind research.</t>
+  </si>
+  <si>
+    <t>Foundation-model societal impact</t>
+  </si>
+  <si>
+    <t>On the Opportunities and Risks of Foundation Models</t>
+  </si>
+  <si>
+    <t>Bommasani et al.</t>
+  </si>
+  <si>
+    <t>Examines foundation models across capabilities, homogenization, adaptation, evaluation, robustness, security, fairness, misuse, law and societal impact.</t>
+  </si>
+  <si>
+    <t>Provides broad conceptual background for why one upstream model can propagate benefits and harms across many downstream systems.</t>
+  </si>
+  <si>
+    <t>Foundation models; societal impact; literature review</t>
+  </si>
+  <si>
+    <t>How does reliance on a small number of foundation models concentrate systemic risk?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2108.07258</t>
+  </si>
+  <si>
+    <t>Stanford CRFM foundational report.</t>
+  </si>
+  <si>
+    <t>New This Week — Automatically Discovered</t>
+  </si>
+  <si>
+    <t>Recent high-scoring discoveries from scholarly APIs and official policy pages.</t>
+  </si>
+  <si>
+    <t>Detected</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Importance Score</t>
+  </si>
+  <si>
+    <t>Why flagged</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>A Common Standard for AI Incident Accountability</t>
+  </si>
+  <si>
+    <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>Must Read Candidate</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, accountability, disclosure, reporting; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21907857</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21907857</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Automatically discovered; verify bibliographic details before formal citation.</t>
+  </si>
+  <si>
+    <t>Autonomous Decision Assurance Layer for AI-Driven Enterprise Analytics: Bridging Governance, Multi-Agent AI, and Executive Decision Intelligence in Saudi Vision 2030 Organizations</t>
+  </si>
+  <si>
+    <t>International Journal for Research in Applied Science and Engineering Technology</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.22214/ijraset.2026.84573</t>
+  </si>
+  <si>
+    <t>10.22214/ijraset.2026.84573</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21907856</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21907856</t>
+  </si>
+  <si>
+    <t>Sustainability and Environmental Ethics in Sanskrit Texts: A Geographical Perspective</t>
+  </si>
+  <si>
+    <t>Environment &amp; Labor</t>
+  </si>
+  <si>
+    <t>Prantik Gabeshana Patrika</t>
+  </si>
+  <si>
+    <t>journal-article</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: water, environment, sustainability; strong scholarly metadata source; impact signal: framework, guidelines, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.67841/pgp.260501082</t>
+  </si>
+  <si>
+    <t>10.67841/pgp.260501082</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>Validating the Virtue Ethics Measurement Scale Within an Open Distance e-Learning Higher Education Institution in South Africa: Students’ Perspectives of Generative AI Practices</t>
+  </si>
+  <si>
+    <t>Algorithms</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/a19080682</t>
+  </si>
+  <si>
+    <t>10.3390/a19080682</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>Examining the Impact of Social-Emotional Learning on Academic Achievement in African American Middle School Girls</t>
+  </si>
+  <si>
+    <t>Seton Hall University eRepository (Seton Hall University)</t>
+  </si>
+  <si>
+    <t>dissertation</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://openalex.org/W7160680247</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>Managing ESG and cyber risks in Kazakhstan’s low-carbon transition by aligning EU and Chinese standards through demoethics</t>
+  </si>
+  <si>
+    <t>Discover Sustainability</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, sustainability; impact signal: framework, standard, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s43621-026-04260-z</t>
+  </si>
+  <si>
+    <t>10.1007/s43621-026-04260-z</t>
+  </si>
+  <si>
+    <t>A Framework for Protecting Students Privacy in Online and Offline Digital Footprints</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL JOURNAL OF COMPUTER SCIENCE AND MATHEMATICAL THEORY E-ISSN</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
+  </si>
+  <si>
+    <t>10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
+  </si>
+  <si>
+    <t>A Review of the TITAN Guideline: Advancing Transparency and Responsible Artificial Intelligence Use in Medical Research and Scholarly Publishing</t>
+  </si>
+  <si>
+    <t>Electronic Journal of Medical Research</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, accountability, reporting; impact signal: framework, guidelines, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.64813/ejmr.2026.126</t>
+  </si>
+  <si>
+    <t>10.64813/ejmr.2026.126</t>
+  </si>
+  <si>
+    <t>Digital personas of AI use in nursing education: a latent class analysis of learning behaviors and academic engagement</t>
+  </si>
+  <si>
+    <t>Frontiers in Medicine</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fmed.2026.1859093</t>
+  </si>
+  <si>
+    <t>10.3389/fmed.2026.1859093</t>
+  </si>
+  <si>
+    <t>Brazil's ENAMED and the Governance of AI-Supported Exam Preparation: A Conceptual Policy Analysis</t>
+  </si>
+  <si>
+    <t>International Journal For Multidisciplinary Research</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: standard, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.36948/ijfmr.2026.v08i04.84125</t>
+  </si>
+  <si>
+    <t>10.36948/ijfmr.2026.v08i04.84125</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>Beyond Visual Evidence: Revealing and Mitigating Relational Privacy Leakage in Document MLLMs</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>matches Privacy: privacy, leakage, extraction; impact signal: benchmark, framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12911v1</t>
+  </si>
+  <si>
+    <t>10.1145/3767308.3835901</t>
+  </si>
+  <si>
+    <t>Digital Transformation of the Indonesian Public Sector: A Systematic Review of Governance, Audit, and Service Innovation</t>
+  </si>
+  <si>
+    <t>F1000Research</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: systematic review, framework, guidelines; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.12688/f1000research.188727.1</t>
+  </si>
+  <si>
+    <t>10.12688/f1000research.188727.1</t>
+  </si>
+  <si>
+    <t>Performance, interaction, and ethical evaluation in the use of generative artificial intelligence in engineering education</t>
+  </si>
+  <si>
+    <t>Education and Information Technologies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, regulation, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10639-026-14112-y</t>
+  </si>
+  <si>
+    <t>10.1007/s10639-026-14112-y</t>
+  </si>
+  <si>
+    <t>Exploring student use of generative AI in higher education: A dual-institutional study</t>
+  </si>
+  <si>
+    <t>book-chapter</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10639-026-14100-2</t>
+  </si>
+  <si>
+    <t>10.1007/s10639-026-14100-2</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>How Personal and Cognitive Traits Influence AI Attitudes, Ethics, and Well-being: The Role of AI Autonomy and Criticality in Design</t>
+  </si>
+  <si>
+    <t>SN Computer Science</t>
+  </si>
+  <si>
+    <t>matches Persuasion &amp; Manipulation: influence, autonomy; impact signal: survey, framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s42979-026-05214-y</t>
+  </si>
+  <si>
+    <t>10.1007/s42979-026-05214-y</t>
+  </si>
+  <si>
+    <t>Ethics Suppression in AI Development: A Comparative Case Study of Responsible AI Under Competitive Pressure</t>
+  </si>
+  <si>
+    <t>International Journal of Applied Research in Business and Management</t>
+  </si>
+  <si>
+    <t>matches Foundations: ethics, responsible ai; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51137/wrp.ijarbm.869</t>
+  </si>
+  <si>
+    <t>10.51137/wrp.ijarbm.869</t>
+  </si>
+  <si>
+    <t>Generative AI in African Higher Education: A Systematic Review of Opportunities, Ethical Challenges, and Institutional Readiness</t>
+  </si>
+  <si>
+    <t>Journal of University Teaching and Learning Practice</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.53761/c682ye61</t>
+  </si>
+  <si>
+    <t>10.53761/c682ye61</t>
+  </si>
+  <si>
+    <t>Which LLM Is Your Ideal Companion? Evaluating Emotional Companion Capabilities of LLMs Based on Adult Attachment Theory</t>
+  </si>
+  <si>
+    <t>matches Human-AI Relationships: companion, emotional support, attachment; impact signal: benchmark, evaluation; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13168v1</t>
+  </si>
+  <si>
+    <t>InFactPlanner: Planning Sustainable Geo-Distributed LLM Data Centers</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, carbon, sustainability; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12915v1</t>
+  </si>
+  <si>
+    <t>Legitimacy Criteria for Strategic Communication in the Age of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>The Proceedings of the World Conference on Social Sciences and Humanities.</t>
+  </si>
+  <si>
+    <t>conference-paper</t>
+  </si>
+  <si>
+    <t>matches Persuasion &amp; Manipulation: persuasion, manipulation, influence, behavioral influence; impact signal: framework, regulation, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.33422/shconf.v3i1.2047</t>
+  </si>
+  <si>
+    <t>10.33422/shconf.v3i1.2047</t>
+  </si>
+  <si>
+    <t>A carbon aware job scheduling framework for data center sustainability using deep learning training</t>
+  </si>
+  <si>
+    <t>Discover Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, environment, sustainability; strong scholarly metadata source; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s44163-026-02022-4</t>
+  </si>
+  <si>
+    <t>10.1007/s44163-026-02022-4</t>
+  </si>
+  <si>
+    <t>How electoral management bodies govern digital electoral systems: capacity, authority, and accountability</t>
+  </si>
+  <si>
+    <t>Frontiers in Political Science</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: systematic review, framework, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpos.2026.1877569</t>
+  </si>
+  <si>
+    <t>10.3389/fpos.2026.1877569</t>
+  </si>
+  <si>
+    <t>Leveraging strategic facilities management to achieve corporate ESG and sustainability: a literature review</t>
+  </si>
+  <si>
+    <t>Frontiers in Environmental Economics</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: environment, sustainability; impact signal: framework, governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/frevc.2026.1839120</t>
+  </si>
+  <si>
+    <t>10.3389/frevc.2026.1839120</t>
+  </si>
+  <si>
+    <t>Effect of Artificial Intelligence (AI) Study Tools on the Study Behaviour of Pharmacology and Medical Students in Bauchi State, Nigeria</t>
+  </si>
+  <si>
+    <t>WORLD JOURNAL OF INNOVATION AND MODERN TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, guidelines, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.56201/wjimt.v10.no7.2026.pg351.366</t>
+  </si>
+  <si>
+    <t>10.56201/wjimt.v10.no7.2026.pg351.366</t>
+  </si>
+  <si>
+    <t>Analysis of PAI Students' Readiness for the Integration of Artificial Intelligence in Learning at Ahmad Dahlan University</t>
+  </si>
+  <si>
+    <t>EDUSOSHUM Journal of Islamic Education and Social Humanities</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.52366/edusoshum.v6i3.550</t>
+  </si>
+  <si>
+    <t>10.52366/edusoshum.v6i3.550</t>
+  </si>
+  <si>
+    <t>Beyond the Device: Reforming Higher Education and Teacher Education Curricula from ICT Literacy to AI Pedagogical Readiness in East Africa</t>
+  </si>
+  <si>
+    <t>East African Journal of Education Studies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.37284/eajes.9.3.5567</t>
+  </si>
+  <si>
+    <t>10.37284/eajes.9.3.5567</t>
+  </si>
+  <si>
+    <t>Acceptance of Generative AI for Supporting Innovative Learning in Vocational Education</t>
+  </si>
+  <si>
+    <t>World Journal of Education</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: survey, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5430/wje.v16n3p30</t>
+  </si>
+  <si>
+    <t>10.5430/wje.v16n3p30</t>
+  </si>
+  <si>
+    <t>Benchmarking Knowledge-Extraction Attack and Defense on Retrieval-Augmented Generation (RAG)</t>
+  </si>
+  <si>
+    <t>OpenAlex</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>matches Privacy: privacy, extraction; impact signal: benchmark, framework, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3770855.3817524</t>
+  </si>
+  <si>
+    <t>10.1145/3770855.3817524</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>Governing Agentic AI in FinTech</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11344v2</t>
+  </si>
+  <si>
+    <t>Toward Meaningful Transparency for AI Chatbots: Disclosing Persuasive Intent Reduces Persuasion</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, disclosure, provenance; impact signal: regulation, policy, randomized; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11794v1</t>
+  </si>
+  <si>
+    <t>Research on the Judicial Fairness Challenges and Legal Regulation of AI-Assisted Judgments in the Context of Digital Justice</t>
+  </si>
+  <si>
+    <t>Advanced Electromagnetics</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.7716/aem.v15i3.3403</t>
+  </si>
+  <si>
+    <t>10.7716/aem.v15i3.3403</t>
+  </si>
+  <si>
+    <t>The Correlation Between Exposure to English-Language Content on Instagram and Listening Comprehension among EFL Students at UIN Datokarama Palu</t>
+  </si>
+  <si>
+    <t>Journal of General Education and Humanities</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.58421/gehu.v5i4.1936</t>
+  </si>
+  <si>
+    <t>10.58421/gehu.v5i4.1936</t>
+  </si>
+  <si>
+    <t>Motivation to learn and teach home economics in higher education: Predictors and comparative analysis</t>
+  </si>
+  <si>
+    <t>Social Sciences &amp; Humanities Open</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ssaho.2026.103414</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssaho.2026.103414</t>
+  </si>
+  <si>
+    <t>The Impact of Artificial Intelligence on English Language Learning, Communication, and Linguistic Development: Opportunities and Challenges</t>
+  </si>
+  <si>
+    <t>Journal of Intelligent Decision Making and Information Science</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.59543/jidmis.v3.1938</t>
+  </si>
+  <si>
+    <t>10.59543/jidmis.v3.1938</t>
+  </si>
+  <si>
+    <t>AI literacy and subject specialization in pre-service teacher education: a mixed-methods study of dimensional profiles and perceived pedagogical challenges</t>
+  </si>
+  <si>
+    <t>Frontiers in Education</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1876627</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1876627</t>
+  </si>
+  <si>
+    <t>Development and pilot testing of multi-stakeholder questionnaires for assessing University 4.0 transformation in higher education institutions</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; impact signal: governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1908552</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1908552</t>
+  </si>
+  <si>
+    <t>PENGARUH MUSIK AI TERHADAP PENINGKATAN MOTIVASI BELAJAR SISWA PADA MATA PELAJARAN IPS DI KELAS IV SD NEGERI 73 AMBON</t>
+  </si>
+  <si>
+    <t>SOCIAL : Jurnal Inovasi Pendidikan IPS</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51878/social.v6i3.14523</t>
+  </si>
+  <si>
+    <t>10.51878/social.v6i3.14523</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Physical Processing of Aquatic Gel Foods: From Protein Structure Regulation to Health, Sustainability, and Personalized Design</t>
+  </si>
+  <si>
+    <t>Comprehensive Reviews in Food Science and Food Safety</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, sustainability; strong scholarly metadata source; impact signal: regulation, standard, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/1541-4337.70601</t>
+  </si>
+  <si>
+    <t>10.1111/1541-4337.70601</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>ChatGPT and Large Language Models in Contemporary Nursing</t>
+  </si>
+  <si>
+    <t>Journal of Clinical Nursing</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/jocn.70490</t>
+  </si>
+  <si>
+    <t>10.1111/jocn.70490</t>
+  </si>
+  <si>
+    <t>Software Engineering for and with GUI Agent</t>
+  </si>
+  <si>
+    <t>arXiv (Cornell University)</t>
+  </si>
+  <si>
+    <t>preprint</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, evaluation, audit; impact signal: benchmark, framework, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arxiv.2608.09278</t>
+  </si>
+  <si>
+    <t>10.48550/arxiv.2608.09278</t>
+  </si>
+  <si>
+    <t>Banking Performance under the Lens of Earnings Management: A Theoretical and Bibliometric Systematic Review</t>
+  </si>
+  <si>
+    <t>Bulletin of Social Studies and Community Development</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, disclosure, reporting; impact signal: systematic review, framework, guidelines; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.61436/bsscd/v5i3.pp253-267</t>
+  </si>
+  <si>
+    <t>10.61436/bsscd/v5i3.pp253-267</t>
+  </si>
+  <si>
+    <t>Pedagogical prompting rather than technical mastery: Generative AI use by English and English-medium instruction teachers</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1901680</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1901680</t>
+  </si>
+  <si>
+    <t>Applied and Filtered: An End-to-End Algorithmic Fairness Audit of A Public Employment Agency</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: evaluation, audit; impact signal: evaluation, audit; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13022v1</t>
+  </si>
+  <si>
+    <t>Pre-service teachers' general pedagogical knowledge and pedagogical learning opportunities at entry into induction: comparing traditional and alternative teacher education programs</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: standard, longitudinal; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1790135</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1790135</t>
+  </si>
+  <si>
+    <t>Policy Integration and Implementation Gaps in China’s Dual-Carbon Strategy: A Multi-Dimensional Analysis of Carbon Trading System, New Energy Vehicle Incentives, and Air Quality Policies</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon; impact signal: policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.59543/jidmis.v3.1782</t>
+  </si>
+  <si>
+    <t>10.59543/jidmis.v3.1782</t>
+  </si>
+  <si>
+    <t>Dysfunction of Zakat Village Governance in Papua: Fragmentation of Collaboration and Inequality of Amil Capacity</t>
+  </si>
+  <si>
+    <t>JURNAL ILMIAH GEMA PERENCANA</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, evaluation; strong scholarly metadata source; impact signal: framework, regulation, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.61860/jigp.v5i1.411</t>
+  </si>
+  <si>
+    <t>10.61860/jigp.v5i1.411</t>
+  </si>
+  <si>
+    <t>Human-centric AI governance in the European Union. Accountability, fundamental rights, and institutional resilience in public administration</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpos.2026.1928481</t>
+  </si>
+  <si>
+    <t>10.3389/fpos.2026.1928481</t>
+  </si>
+  <si>
+    <t>Delivering building demand flexibility for grid-interactive operation: from perception and cognition to decision, execution, and verification</t>
+  </si>
+  <si>
+    <t>Applied Energy</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon; impact signal: framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.apenergy.2026.128668</t>
+  </si>
+  <si>
+    <t>10.1016/j.apenergy.2026.128668</t>
+  </si>
+  <si>
+    <t>PENGARUH MODEL PEMBELAJARAN PROJECT BASED LEARNING DAN KEDISIPLINAN BELAJAR TERHADAP KESIAPAN KERJA SISWA PADA JURUSAN AKUNTANSI KEUANGAN LEMABAGA DI SMK NEGERI 1 PANGKEP</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; impact signal: survey; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51878/social.v6i3.14617</t>
+  </si>
+  <si>
+    <t>10.51878/social.v6i3.14617</t>
+  </si>
+  <si>
+    <t>Large Language Model-facilitated national review on the use of ecological tools and processes in Environmental Impact Statements (EIS) in the U.S. with demonstrated use cases for environmental planners, legal practitioners, and researchers</t>
+  </si>
+  <si>
+    <t>Springer Science and Business Media LLC</t>
+  </si>
+  <si>
+    <t>posted-content</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, environment, labor; strong scholarly metadata source; impact signal: benchmark, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.21203/rs.3.rs-10627892/v1</t>
+  </si>
+  <si>
+    <t>10.21203/rs.3.rs-10627892/v1</t>
+  </si>
+  <si>
+    <t>Optimization of Household Equipment and Instrumentation in an Effort to Save Electrical Energy in a Restaurant</t>
+  </si>
+  <si>
+    <t>International Journal Of Community Service</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, environment; strong scholarly metadata source; impact signal: survey, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51601/ijcs.v6i3.1022</t>
+  </si>
+  <si>
+    <t>10.51601/ijcs.v6i3.1022</t>
+  </si>
+  <si>
+    <t>Effect of Public Safety Center Video-Based Education on Emergency Response Attitudes Among High School Students</t>
+  </si>
+  <si>
+    <t>Jurnal Kegawatdaruratan Medis Indonesia</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.58545/jkmi.v5i2.827</t>
+  </si>
+  <si>
+    <t>10.58545/jkmi.v5i2.827</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>From Single Chatbots to Governed Agent Ecosystems: An Agentic AI Pattern Catalogue and Orchestration Framework for Mission-Critical Hospital Information Management Systems</t>
+  </si>
+  <si>
+    <t>matches Agentic AI: agentic ai, autonomous agent, multi-agent; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.07627v1</t>
+  </si>
+  <si>
+    <t>10.38124/ijisrt/26jul830</t>
+  </si>
+  <si>
+    <t>Bias Smells in AI Software Development: Recognizing Potential Sources of Fairness Debt</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arxiv.2608.10248</t>
+  </si>
+  <si>
+    <t>10.48550/arxiv.2608.10248</t>
+  </si>
+  <si>
+    <t>Quantifying the Relationship Between Clinical Safety and Environmental Impact in Therapeutic LLMs</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, carbon, environment; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11830v1</t>
+  </si>
+  <si>
+    <t>Benchmark-Based Comparative Assessment of Publicly Benchmarked Indian Foundation Models: A Capability and Evaluation-Maturity Framework</t>
+  </si>
+  <si>
+    <t>matches India &amp; Global South: multilingual, india; impact signal: survey, benchmark, framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11891v1</t>
+  </si>
+  <si>
+    <t>Academic League of Artificial Intelligence - An Integrative Perspective of Teaching, Research, and Extension</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13447v1</t>
+  </si>
+  <si>
+    <t>Educational Aspirations in Contemporary Indian Education: A Critical Conceptual Synthesis for Holistic Learner Development</t>
+  </si>
+  <si>
+    <t>Asian Journal of Education and Social Studies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: policy, longitudinal; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.9734/ajess/2026/v52i83261</t>
+  </si>
+  <si>
+    <t>10.9734/ajess/2026/v52i83261</t>
+  </si>
+  <si>
+    <t>Solar Exposure and Photoprotection Behaviors as Determinants of Acne Vulgaris Severity Among University Students in Andalusia-Spain</t>
+  </si>
+  <si>
+    <t>Ibn Sina Journal of Medical Science Health &amp; Pharmacy</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; impact signal: survey, framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.64440/ibnsina/sina0027</t>
+  </si>
+  <si>
+    <t>10.64440/ibnsina/sina0027</t>
+  </si>
+  <si>
+    <t>FSGR: Mitigating Token Frequency Bias for Fair SID-Based Generative Recommendation</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12845v1</t>
+  </si>
+  <si>
+    <t>HEPE — Complete 16-State AI Governance Space with Lyapunov Values (Hardware-Enforced Policy Engine)</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: policy, governance, audit; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21935563</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21935563</t>
+  </si>
+  <si>
+    <t>What Remains Ours to Think? Reclaiming Critical Thinking in AI‐Augmented Student Leadership Education</t>
+  </si>
+  <si>
+    <t>New Directions for Student Leadership</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/yd.70068</t>
+  </si>
+  <si>
+    <t>10.1002/yd.70068</t>
+  </si>
+  <si>
+    <t>Supervision in educational leadership: practices, challenges, and innovations in the UAE — a multi-level coupling analysis of the current and future</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: benchmark, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1862260</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1862260</t>
+  </si>
+  <si>
+    <t>Research ethics and publication policies in journals using the Korea Institute of Science and Technology Information (KISTI) academic publishing platform: a content analysis of 181 journals</t>
+  </si>
+  <si>
+    <t>Science Editing</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: accountability, disclosure; impact signal: guidelines, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.6087/kcse.403</t>
+  </si>
+  <si>
+    <t>10.6087/kcse.403</t>
+  </si>
+  <si>
+    <t>Striking a Balance between the Right to Privacy and Freedom of Expression: A Case Study of Women’s Digital Rights in Tanzania</t>
+  </si>
+  <si>
+    <t>East African Journal of Law and Ethics</t>
+  </si>
+  <si>
+    <t>matches Regulation: regulation, legal framework, standard; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.37284/eajle.9.3.5557</t>
+  </si>
+  <si>
+    <t>10.37284/eajle.9.3.5557</t>
+  </si>
+  <si>
+    <t>Evaluation of the CIPP Model in a Project-Based Basic Electronics Course: A Discriminant Validity and Common Method Bias Analysis</t>
+  </si>
+  <si>
+    <t>Educative: Jurnal Ilmiah Pendidikan</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.70437/educative.v4i2.2180</t>
+  </si>
+  <si>
+    <t>10.70437/educative.v4i2.2180</t>
+  </si>
+  <si>
+    <t>The effectiveness of the contextual teaching and learning model on mathematical literacy skills in terms of learning motivation</t>
+  </si>
+  <si>
+    <t>Union: Jurnal Ilmiah Pendidikan Matematika</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.30738/union.v14i2.22911</t>
+  </si>
+  <si>
+    <t>10.30738/union.v14i2.22911</t>
+  </si>
+  <si>
+    <t>Review Queue — Human-in-the-loop Curation</t>
+  </si>
+  <si>
+    <t>Promote only sources that are genuinely useful. Automatic discovery is intentionally not identical to automatic curation.</t>
+  </si>
+  <si>
+    <t>Topic Map — What to Read for Each AI / LLM Ethics Question</t>
+  </si>
+  <si>
+    <t>Theme-level map generated from the current curated library.</t>
+  </si>
+  <si>
+    <t>Sources in library</t>
+  </si>
+  <si>
+    <t>2026-heavy?</t>
+  </si>
+  <si>
+    <t>Start with</t>
+  </si>
+  <si>
+    <t>Then read</t>
+  </si>
+  <si>
+    <t>Typical reader question</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Recommendation on the Ethics of Artificial Intelligence; On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1); Guidelines for providers of general-purpose AI models</t>
+  </si>
+  <si>
+    <t>An Evaluation of AI Companion Apps; Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
+  </si>
+  <si>
+    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders; Evaluating Language Models for Harmful Manipulation</t>
+  </si>
+  <si>
+    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory; SoK: The Privacy Paradox of Large Language Models</t>
+  </si>
+  <si>
+    <t>2026-Only View</t>
+  </si>
+  <si>
+    <t>Current-year curated items.</t>
+  </si>
+  <si>
+    <t>Policy, Governance &amp; Regulation</t>
+  </si>
+  <si>
+    <t>Curated governance, standards, transparency, law and human-rights sources.</t>
+  </si>
+  <si>
+    <t>Source Configuration</t>
+  </si>
+  <si>
+    <t>Edit config/sources.yaml in the repository to change the automation. This sheet is a readable mirror.</t>
+  </si>
+  <si>
+    <t>Endpoint / URL</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Authority</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>https://export.arxiv.org/api/query</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Fresh preprints</t>
+  </si>
+  <si>
+    <t>3-second delay between repeated calls</t>
+  </si>
+  <si>
+    <t>https://api.openalex.org/works</t>
+  </si>
+  <si>
+    <t>Broad scholarly discovery</t>
+  </si>
+  <si>
+    <t>OPENALEX_API_KEY optional</t>
+  </si>
+  <si>
+    <t>Crossref</t>
+  </si>
+  <si>
+    <t>https://api.crossref.org/works</t>
+  </si>
+  <si>
+    <t>Published DOI metadata</t>
+  </si>
+  <si>
+    <t>CONTACT_EMAIL recommended</t>
+  </si>
+  <si>
+    <t>NIST Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Official page watch</t>
+  </si>
+  <si>
+    <t>https://www.nist.gov/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>Policy/news link discovery</t>
+  </si>
+  <si>
+    <t>First scan bootstraps without flooding</t>
+  </si>
+  <si>
+    <t>European Commission AI Act</t>
+  </si>
+  <si>
+    <t>OECD.AI Wonk</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/wonk</t>
+  </si>
+  <si>
+    <t>UNESCO Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>IndiaAI / MeitY — PIB Releases</t>
+  </si>
+  <si>
+    <t>https://www.pib.gov.in/AllRelease.aspx?MenuId=30&amp;lang=1&amp;reg=3</t>
+  </si>
+  <si>
+    <t>Automation Update Log</t>
+  </si>
+  <si>
+    <t>Every run records discovery and deduplication counts.</t>
+  </si>
+  <si>
+    <t>New This Week</t>
+  </si>
+  <si>
+    <t>Review Queue</t>
+  </si>
+  <si>
+    <t>Auto-promoted</t>
+  </si>
+  <si>
+    <t>2026-08-16T12:18:00+05:30</t>
+  </si>
+  <si>
+    <t>Initial build</t>
+  </si>
+  <si>
+    <t>Living tracker package initialized</t>
+  </si>
+  <si>
+    <t>2026-08-16T07:19:28+00:00</t>
+  </si>
+  <si>
+    <t>Policy/IndiaAI Safe &amp; Trusted AI: HTTPError: 403 Client Error: Forbidden for url: https://indiaai.gov.in/hub/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>2026-08-16T07:39:54+00:00</t>
+  </si>
+  <si>
     <t>2026-08-16T10:42:00+00:00</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>scheduled/manual</t>
-  </si>
-  <si>
-    <t>Sources checked</t>
-  </si>
-  <si>
-    <t>Candidates fetched</t>
-  </si>
-  <si>
-    <t>New after dedupe</t>
-  </si>
-  <si>
-    <t>Errors / notes</t>
-  </si>
-  <si>
-    <t>Completed without recorded source errors</t>
-  </si>
-  <si>
-    <t>Start Here — 2026-aware AI &amp; LLM Ethics Reading Path</t>
-  </si>
-  <si>
-    <t>Use this sheet for a compact orientation. The automated discovery tabs are intentionally separate from the stable reading path.</t>
-  </si>
-  <si>
-    <t>Curated sources</t>
-  </si>
-  <si>
-    <t>2026 sources</t>
-  </si>
-  <si>
-    <t>Must Read</t>
-  </si>
-  <si>
-    <t>Official / institutional</t>
-  </si>
-  <si>
-    <t>Recommended 10-source reading path</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Read this</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Why now</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Source URL</t>
-  </si>
-  <si>
-    <t>Responsible AI | The 2026 AI Index Report</t>
-  </si>
-  <si>
-    <t>Current 2025–2026 evidence or governance update</t>
-  </si>
-  <si>
-    <t>https://hai.stanford.edu/ai-index/2026-ai-index-report/responsible-ai</t>
-  </si>
-  <si>
-    <t>AI Act | Shaping Europe's digital future</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/regulatory-framework-ai</t>
-  </si>
-  <si>
-    <t>Guidelines on transparency obligations for providers and deployers of AI systems</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-transparency-ai-generated-content</t>
-  </si>
-  <si>
-    <t>Persuasion with Large Language Models: A Survey of Empirical Studies</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2411.06837v2</t>
-  </si>
-  <si>
-    <t>Emotional Support with Conversational AI: Talking to Machines About Life</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2603.22618v1</t>
-  </si>
-  <si>
-    <t>An Evaluation of AI Companion Apps</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2605.08093v2</t>
-  </si>
-  <si>
-    <t>Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2606.04150</t>
-  </si>
-  <si>
-    <t>Towards Agentic AI Governance: A Preliminary Assessment</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2607.07612</t>
-  </si>
-  <si>
-    <t>The 2025 Foundation Model Transparency Index</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2512.10169</t>
-  </si>
-  <si>
-    <t>India AI Governance Guidelines: Empowering Ethical and Responsible AI</t>
-  </si>
-  <si>
-    <t>https://indiaai.gov.in/article/india-ai-governance-guidelines-empowering-ethical-and-responsible-ai</t>
-  </si>
-  <si>
-    <t>Ethics of Artificial Intelligence &amp; LLMs — Curated Reading Library</t>
-  </si>
-  <si>
-    <t>Stable curated sources. Automatically discovered items are triaged separately before promotion.</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Subtopic</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Author / Body</t>
-  </si>
-  <si>
-    <t>Source Type</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>What it covers</t>
-  </si>
-  <si>
-    <t>Why the reader benefits</t>
-  </si>
-  <si>
-    <t>Best use</t>
-  </si>
-  <si>
-    <t>2026 Relevance Score</t>
-  </si>
-  <si>
-    <t>Read Priority</t>
-  </si>
-  <si>
-    <t>Region / Scope</t>
-  </si>
-  <si>
-    <t>Key ethical question</t>
-  </si>
-  <si>
-    <t>Notes / status</t>
-  </si>
-  <si>
-    <t>Reader mode</t>
-  </si>
-  <si>
-    <t>Responsible AI state of the field</t>
-  </si>
-  <si>
-    <t>Stanford HAI / AI Index</t>
-  </si>
-  <si>
-    <t>Annual evidence report</t>
-  </si>
-  <si>
-    <t>Institutional / data-driven</t>
-  </si>
-  <si>
-    <t>Tracks AI incidents, safety evaluation, transparency, responsible-AI reporting, and the widening gap between capability and governance.</t>
-  </si>
-  <si>
-    <t>Best current snapshot for showing that AI capability is advancing faster than safety measurement and transparency.</t>
-  </si>
-  <si>
-    <t>Lecture opener; literature review motivation; 2026 statistics</t>
-  </si>
-  <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t>Are current evaluation and governance systems keeping pace with frontier AI capability?</t>
-  </si>
-  <si>
-    <t>2026 edition; strong source for current facts and figures.</t>
-  </si>
-  <si>
-    <t>Read closely</t>
-  </si>
-  <si>
-    <t>Foundation model transparency</t>
-  </si>
-  <si>
-    <t>Wan et al. / Stanford CRFM</t>
-  </si>
-  <si>
-    <t>Research report / index</t>
-  </si>
-  <si>
-    <t>Research report</t>
-  </si>
-  <si>
-    <t>Scores major foundation-model developers on disclosures covering data, compute, risk mitigation, usage and downstream impacts.</t>
-  </si>
-  <si>
-    <t>Lets readers move from vague calls for transparency to measurable disclosure dimensions and compare developers.</t>
-  </si>
-  <si>
-    <t>Transparency section; accountability case study; assignment</t>
-  </si>
-  <si>
-    <t>Global / industry</t>
-  </si>
-  <si>
-    <t>What information should frontier-model developers be required to disclose?</t>
-  </si>
-  <si>
-    <t>Average score fell from 58/100 in 2024 to 40/100 in 2025.</t>
-  </si>
-  <si>
-    <t>EU AI Act implementation</t>
-  </si>
-  <si>
-    <t>European Commission</t>
-  </si>
-  <si>
-    <t>Regulation / official guidance</t>
-  </si>
-  <si>
-    <t>Official</t>
-  </si>
-  <si>
-    <t>Official overview of the EU AI Act, risk-based obligations, implementation timeline, GPAI rules and transparency requirements.</t>
-  </si>
-  <si>
-    <t>Provides the clearest bridge between ethics principles and enforceable legal duties in 2026.</t>
-  </si>
-  <si>
-    <t>Regulation module; compliance discussion; policy comparison</t>
-  </si>
-  <si>
-    <t>European Union</t>
-  </si>
-  <si>
-    <t>When should ethical expectations become legal obligations?</t>
-  </si>
-  <si>
-    <t>General application date: 2 August 2026, with exceptions and phased provisions.</t>
-  </si>
-  <si>
-    <t>AI-generated content disclosure</t>
-  </si>
-  <si>
-    <t>Regulatory guidance</t>
-  </si>
-  <si>
-    <t>Explains Article 50 duties concerning user disclosure, machine-readable marking, AI-generated content and deepfakes.</t>
-  </si>
-  <si>
-    <t>Useful concrete example of how transparency ethics becomes a product-design requirement.</t>
-  </si>
-  <si>
-    <t>Deepfakes; disclosure; generative-AI product design</t>
-  </si>
-  <si>
-    <t>Should people always know when they are interacting with AI or seeing AI-generated content?</t>
-  </si>
-  <si>
-    <t>Article 50 applies from 2 August 2026.</t>
-  </si>
-  <si>
-    <t>General-purpose AI obligations</t>
-  </si>
-  <si>
-    <t>Guidelines for providers of general-purpose AI models</t>
-  </si>
-  <si>
-    <t>Clarifies obligations for providers of general-purpose AI models and the Commission's enforcement role.</t>
-  </si>
-  <si>
-    <t>Gives readers a current compliance perspective on frontier and general-purpose models rather than generic AI regulation.</t>
-  </si>
-  <si>
-    <t>GPAI governance; provider responsibilities; seminar discussion</t>
-  </si>
-  <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>What extra duties should apply to powerful general-purpose models?</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-gpai-providers</t>
-  </si>
-  <si>
-    <t>Commission enforcement powers apply from 2 August 2026.</t>
-  </si>
-  <si>
-    <t>Read/skim</t>
-  </si>
-  <si>
-    <t>India AI governance</t>
-  </si>
-  <si>
-    <t>IndiaAI / MeitY</t>
-  </si>
-  <si>
-    <t>National governance guidance</t>
-  </si>
-  <si>
-    <t>Sets out principles and recommendations around fairness, accountability, safety, inclusivity and trustworthy AI in India.</t>
-  </si>
-  <si>
-    <t>Adds an India-specific governance perspective and prevents the reading list from being US/EU-centric.</t>
-  </si>
-  <si>
-    <t>India case study; policy comparison; local context</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>How should responsible AI governance reflect India's scale, diversity and public-interest priorities?</t>
-  </si>
-  <si>
-    <t>Released 5 Nov 2025 under the IndiaAI Mission.</t>
-  </si>
-  <si>
-    <t>AI safety capacity</t>
-  </si>
-  <si>
-    <t>Safe &amp; Trusted AI Working Group</t>
-  </si>
-  <si>
-    <t>India AI Impact Summit</t>
-  </si>
-  <si>
-    <t>Policy / working-group output</t>
-  </si>
-  <si>
-    <t>Focuses on AI safety capacity, evaluation, governance and incorporating Global South perspectives into international AI safety frameworks.</t>
-  </si>
-  <si>
-    <t>Useful for understanding how safety debates are being localized beyond US/EU institutions.</t>
-  </si>
-  <si>
-    <t>India 2026 update; global governance; discussion prompt</t>
-  </si>
-  <si>
-    <t>India / Global South</t>
-  </si>
-  <si>
-    <t>Who gets to define acceptable AI risk and safety standards globally?</t>
-  </si>
-  <si>
-    <t>https://impact.indiaai.gov.in/working-groups/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>2026-relevant IndiaAI Impact Summit initiative.</t>
-  </si>
-  <si>
-    <t>Risk management framework</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1)</t>
-  </si>
-  <si>
-    <t>NIST</t>
-  </si>
-  <si>
-    <t>Risk-management framework</t>
-  </si>
-  <si>
-    <t>Identifies GenAI-specific risks and actions across the AI lifecycle, aligned with Govern, Map, Measure and Manage.</t>
-  </si>
-  <si>
-    <t>One of the most practical sources for converting ethical concerns into operational risk controls.</t>
-  </si>
-  <si>
-    <t>Risk register; deployment checklist; governance design</t>
-  </si>
-  <si>
-    <t>United States / cross-sector</t>
-  </si>
-  <si>
-    <t>How can an organization operationalize trustworthy GenAI rather than merely state principles?</t>
-  </si>
-  <si>
-    <t>https://www.nist.gov/publications/artificial-intelligence-risk-management-framework-generative-artificial-intelligence</t>
-  </si>
-  <si>
-    <t>Companion to NIST AI RMF 1.0.</t>
-  </si>
-  <si>
-    <t>Human-rights-centered AI ethics</t>
-  </si>
-  <si>
-    <t>Recommendation on the Ethics of Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>UNESCO</t>
-  </si>
-  <si>
-    <t>International ethics standard</t>
-  </si>
-  <si>
-    <t>Defines principles including proportionality, do-no-harm, safety, privacy, fairness, transparency, accountability, sustainability and human oversight.</t>
-  </si>
-  <si>
-    <t>Provides a normative foundation for almost every later AI ethics topic.</t>
-  </si>
-  <si>
-    <t>Foundations lecture; ethics framework; compare policies</t>
-  </si>
-  <si>
-    <t>What values should guide the design and deployment of AI systems?</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
-  </si>
-  <si>
-    <t>Global UNESCO recommendation; remains foundational in 2026.</t>
-  </si>
-  <si>
-    <t>Trustworthy AI principles</t>
-  </si>
-  <si>
-    <t>OECD AI Principles</t>
-  </si>
-  <si>
-    <t>OECD</t>
-  </si>
-  <si>
-    <t>International policy principles</t>
-  </si>
-  <si>
-    <t>Principles for innovative and trustworthy AI, covering human rights, fairness, transparency, robustness, security and accountability.</t>
-  </si>
-  <si>
-    <t>Concise policy baseline that is easy to compare against NIST, UNESCO, EU and national frameworks.</t>
-  </si>
-  <si>
-    <t>Framework comparison; policy lecture; exam preparation</t>
-  </si>
-  <si>
-    <t>What minimum principles should trustworthy AI systems satisfy across countries?</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/ai-principles</t>
-  </si>
-  <si>
-    <t>Initially adopted 2019; updated May 2024.</t>
-  </si>
-  <si>
-    <t>International AI treaty</t>
-  </si>
-  <si>
-    <t>Framework Convention on Artificial Intelligence and Human Rights, Democracy and the Rule of Law</t>
-  </si>
-  <si>
-    <t>Council of Europe</t>
-  </si>
-  <si>
-    <t>International treaty</t>
-  </si>
-  <si>
-    <t>Official / legally binding framework</t>
-  </si>
-  <si>
-    <t>Addresses human rights, democratic processes, autonomy, transparency, accountability, equality and privacy across the AI lifecycle.</t>
-  </si>
-  <si>
-    <t>Shows the transition from voluntary ethics to treaty-based human-rights obligations.</t>
-  </si>
-  <si>
-    <t>Human-rights module; legal governance; global policy</t>
-  </si>
-  <si>
-    <t>International</t>
-  </si>
-  <si>
-    <t>How should AI development be constrained when it may affect fundamental rights and democratic institutions?</t>
-  </si>
-  <si>
-    <t>https://www.coe.int/en/web/artificial-intelligence/the-framework-convention-on-artificial-intelligence</t>
-  </si>
-  <si>
-    <t>First international legally binding treaty in this field; opened for signature 5 Sept 2024.</t>
-  </si>
-  <si>
-    <t>Developer risk reporting</t>
-  </si>
-  <si>
-    <t>How are AI developers managing risks? Insights from the Hiroshima AI Process reporting framework</t>
-  </si>
-  <si>
-    <t>International governance report</t>
-  </si>
-  <si>
-    <t>Official / multi-stakeholder</t>
-  </si>
-  <si>
-    <t>Analyzes how organizations report risk identification, safety, governance, content authentication and accountability practices.</t>
-  </si>
-  <si>
-    <t>Gives concrete examples of how frontier developers operationalize risk management, not just what principles say.</t>
-  </si>
-  <si>
-    <t>Industry governance; transparency; comparative analysis</t>
-  </si>
-  <si>
-    <t>G7 / global</t>
-  </si>
-  <si>
-    <t>Can voluntary transparency meaningfully improve accountability for advanced AI developers?</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/ai-publications/how-are-ai-developers-managing-risks-insights-from-responses-to-the-reporting-framework-of-the-hiroshima-ai-process-code-of-conduct</t>
-  </si>
-  <si>
-    <t>Reporting framework launched in 2025.</t>
-  </si>
-  <si>
-    <t>Comprehensive LLM ethics</t>
-  </si>
-  <si>
-    <t>Deconstructing the ethics of large language models from long-standing issues to new-emerging dilemmas</t>
-  </si>
-  <si>
-    <t>Deng et al.</t>
-  </si>
-  <si>
-    <t>Survey / review</t>
-  </si>
-  <si>
-    <t>Peer-reviewed</t>
-  </si>
-  <si>
-    <t>Surveys copyright, systematic bias, privacy, truthfulness, social norms and emerging ethical challenges of LLMs.</t>
-  </si>
-  <si>
-    <t>Good single-paper orientation before readers enter specialized literatures.</t>
-  </si>
-  <si>
-    <t>Literature review starting point; seminar reading</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Which LLM ethical risks are old problems amplified by scale, and which are genuinely new?</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s43681-025-00797-3</t>
-  </si>
-  <si>
-    <t>Published in AI and Ethics.</t>
-  </si>
-  <si>
-    <t>Bias evaluation and mitigation</t>
-  </si>
-  <si>
-    <t>Bias and Fairness in Large Language Models: A Survey</t>
-  </si>
-  <si>
-    <t>Gallegos et al.</t>
-  </si>
-  <si>
-    <t>Survey</t>
-  </si>
-  <si>
-    <t>Research / arXiv</t>
-  </si>
-  <si>
-    <t>Organizes social bias harms, evaluation metrics, datasets and mitigation techniques for LLMs.</t>
-  </si>
-  <si>
-    <t>Provides a technical taxonomy that makes 'AI bias' measurable rather than purely rhetorical.</t>
-  </si>
-  <si>
-    <t>Bias lecture; evaluation design; related work</t>
-  </si>
-  <si>
-    <t>How should fairness be defined and measured for generative language systems?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2309.00770</t>
-  </si>
-  <si>
-    <t>Still a useful technical survey in 2026.</t>
-  </si>
-  <si>
-    <t>Hallucination taxonomy</t>
-  </si>
-  <si>
-    <t>A Survey on Hallucination in Large Language Models</t>
-  </si>
-  <si>
-    <t>ACM Computing Surveys</t>
-  </si>
-  <si>
-    <t>Reviews hallucination principles, taxonomies, causes, evaluation, detection and mitigation in LLMs.</t>
-  </si>
-  <si>
-    <t>Helps distinguish factual reliability problems from broader moral or social harms.</t>
-  </si>
-  <si>
-    <t>Truthfulness; reliability; high-stakes deployment</t>
-  </si>
-  <si>
-    <t>When is an incorrect LLM output merely an error, and when does it become an ethical harm?</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3703155</t>
-  </si>
-  <si>
-    <t>High-value technical survey.</t>
-  </si>
-  <si>
-    <t>Training-data leakage</t>
-  </si>
-  <si>
-    <t>New Privacy Risks for Large Language Models</t>
-  </si>
-  <si>
-    <t>Research paper</t>
-  </si>
-  <si>
-    <t>Preprint / current research</t>
-  </si>
-  <si>
-    <t>Examines data extraction and memorization risks, connecting privacy leakage with copyright and training-data provenance concerns.</t>
-  </si>
-  <si>
-    <t>Useful 2026 update showing privacy risk is not limited to classic membership inference.</t>
-  </si>
-  <si>
-    <t>Privacy section; training data; model memorization</t>
-  </si>
-  <si>
-    <t>What does a model owe people whose private or copyrighted data it can reproduce?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2509.14278v2</t>
-  </si>
-  <si>
-    <t>Version available Jan 2026.</t>
-  </si>
-  <si>
-    <t>Privacy threat landscape</t>
-  </si>
-  <si>
-    <t>SoK: The Privacy Paradox of Large Language Models</t>
-  </si>
-  <si>
-    <t>Systematization of knowledge</t>
-  </si>
-  <si>
-    <t>Preprint / research</t>
-  </si>
-  <si>
-    <t>Systematizes training-data extraction, reconstruction, inference-time privacy and protection mechanisms.</t>
-  </si>
-  <si>
-    <t>Gives readers a map of privacy attack surfaces instead of isolated examples.</t>
-  </si>
-  <si>
-    <t>Security/privacy module; research gap identification</t>
-  </si>
-  <si>
-    <t>Can LLM utility and strong privacy guarantees be achieved simultaneously?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2506.12699v2</t>
-  </si>
-  <si>
-    <t>Useful bridge between AI ethics and security.</t>
-  </si>
-  <si>
-    <t>Empirical privacy evaluation</t>
-  </si>
-  <si>
-    <t>Privacy Auditing of Large Language Models</t>
-  </si>
-  <si>
-    <t>Develops stronger privacy auditing techniques and more effective canaries for estimating empirical leakage.</t>
-  </si>
-  <si>
-    <t>Shows readers how privacy claims can be tested rather than assumed.</t>
-  </si>
-  <si>
-    <t>Methodology; model audit; technical assignment</t>
-  </si>
-  <si>
-    <t>Specialist</t>
-  </si>
-  <si>
-    <t>How should developers demonstrate that a language model is not leaking training data?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2503.06808v1</t>
-  </si>
-  <si>
-    <t>Technical privacy-auditing work.</t>
-  </si>
-  <si>
-    <t>Reference as needed</t>
-  </si>
-  <si>
-    <t>Agent memory and contextual leakage</t>
-  </si>
-  <si>
-    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory</t>
-  </si>
-  <si>
-    <t>Security research</t>
-  </si>
-  <si>
-    <t>Studies privacy leakage from inference-time contextual memory in LLM agents, beyond training-data privacy.</t>
-  </si>
-  <si>
-    <t>Important for 2026 because persistent AI assistants and agents create a new privacy attack surface.</t>
-  </si>
-  <si>
-    <t>Agentic AI; memory privacy; security discussion</t>
-  </si>
-  <si>
-    <t>Research / agents</t>
-  </si>
-  <si>
-    <t>What privacy risks appear when AI systems remember and act on user context over time?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2604.23711v1</t>
-  </si>
-  <si>
-    <t>2026 agent-memory privacy paper.</t>
-  </si>
-  <si>
-    <t>Persuasion landscape</t>
-  </si>
-  <si>
-    <t>Research survey</t>
-  </si>
-  <si>
-    <t>Reviews empirical evidence on automated, personalized and interactive LLM persuasion and its effects on attitudes and behavior.</t>
-  </si>
-  <si>
-    <t>A direct entry point into one of the most important newer AI-ethics issues.</t>
-  </si>
-  <si>
-    <t>Manipulation lecture; social influence; governance</t>
-  </si>
-  <si>
-    <t>When does helpful persuasion become manipulation or undue influence?</t>
-  </si>
-  <si>
-    <t>Updated Apr 2026.</t>
-  </si>
-  <si>
-    <t>Human vs AI persuasion</t>
-  </si>
-  <si>
-    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders</t>
-  </si>
-  <si>
-    <t>Schoenegger et al.</t>
-  </si>
-  <si>
-    <t>Large-scale experiment</t>
-  </si>
-  <si>
-    <t>Compares a frontier LLM with incentivized human persuaders in interactive settings and measures compliance with correct and incorrect persuasion.</t>
-  </si>
-  <si>
-    <t>Provides concrete empirical evidence that persuasive capability can create both benefits and harms.</t>
-  </si>
-  <si>
-    <t>Case study; empirical evidence; class discussion</t>
-  </si>
-  <si>
-    <t>Should systems with human-level or greater persuasive power face special safeguards?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2505.09662</t>
-  </si>
-  <si>
-    <t>Preregistered, large-scale incentivized experiment.</t>
-  </si>
-  <si>
-    <t>Harmful influence evaluation</t>
-  </si>
-  <si>
-    <t>Evaluating Language Models for Harmful Manipulation</t>
-  </si>
-  <si>
-    <t>Akbulut et al.</t>
-  </si>
-  <si>
-    <t>Human-subject evaluation</t>
-  </si>
-  <si>
-    <t>Research / preprint</t>
-  </si>
-  <si>
-    <t>Introduces a framework for measuring harmful manipulation across public policy, finance and health with participants from multiple countries.</t>
-  </si>
-  <si>
-    <t>Shows how manipulation can be operationalized and evaluated across consequential domains.</t>
-  </si>
-  <si>
-    <t>Evaluation design; high-stakes AI; cross-country analysis</t>
-  </si>
-  <si>
-    <t>US / UK / India</t>
-  </si>
-  <si>
-    <t>How can harmful manipulation be measured before deployment?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2603.25326</t>
-  </si>
-  <si>
-    <t>Includes 10,101 participants across three locales.</t>
-  </si>
-  <si>
-    <t>Sycophancy to strategic deception</t>
-  </si>
-  <si>
-    <t>From Sycophancy to Deception: A Unified Taxonomy for Misleading LLM Behavior</t>
-  </si>
-  <si>
-    <t>Taxonomy / research</t>
-  </si>
-  <si>
-    <t>Unifies hallucination, omission, pragmatic distortion, sycophancy and strategic deception under a common taxonomy of misleading behavior.</t>
-  </si>
-  <si>
-    <t>Helps readers avoid treating all misleading model outputs as the same failure mode.</t>
-  </si>
-  <si>
-    <t>Conceptual framework; deception; research taxonomy</t>
-  </si>
-  <si>
-    <t>Does intent or goal-directedness change how ethically serious misleading AI behavior is?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2604.04788</t>
-  </si>
-  <si>
-    <t>Current 2026 taxonomy.</t>
-  </si>
-  <si>
-    <t>Sycophancy</t>
-  </si>
-  <si>
-    <t>Sycophancy in Large Language Models: Causes and Mitigations</t>
-  </si>
-  <si>
-    <t>Lars Malmqvist</t>
-  </si>
-  <si>
-    <t>Technical survey</t>
-  </si>
-  <si>
-    <t>Surveys excessive agreement with users, causes, measurement and mitigation, and links sycophancy to hallucination and bias.</t>
-  </si>
-  <si>
-    <t>Useful for discussing why 'agreeable' assistants can become epistemically unsafe.</t>
-  </si>
-  <si>
-    <t>Alignment; user trust; truthfulness</t>
-  </si>
-  <si>
-    <t>Should an assistant prioritize user satisfaction or epistemic honesty when they conflict?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2411.15287</t>
-  </si>
-  <si>
-    <t>Technical survey.</t>
-  </si>
-  <si>
-    <t>Emotional support</t>
-  </si>
-  <si>
-    <t>Huang, Stodolska &amp; Sultana</t>
-  </si>
-  <si>
-    <t>Qualitative HCI research</t>
-  </si>
-  <si>
-    <t>Analyzes how emotional support is co-constructed with AI companions and tensions such as support vs dependency and validation vs delusion.</t>
-  </si>
-  <si>
-    <t>Provides nuanced evidence beyond simplistic claims that AI companions are either beneficial or harmful.</t>
-  </si>
-  <si>
-    <t>HCI ethics; mental-health-adjacent discussion; companionship</t>
-  </si>
-  <si>
-    <t>How should AI offer emotional support without reinforcing dependency or harmful beliefs?</t>
-  </si>
-  <si>
-    <t>2026 HCI-focused research.</t>
-  </si>
-  <si>
-    <t>Companion-app design</t>
-  </si>
-  <si>
-    <t>Empirical audit</t>
-  </si>
-  <si>
-    <t>Audits popular AI companion apps for dark patterns, anthropomorphism, stereotypes, erotica and technical issues.</t>
-  </si>
-  <si>
-    <t>Connects ethical risk to actual interface and monetization design choices, not only model behavior.</t>
-  </si>
-  <si>
-    <t>Product ethics; dark patterns; companion AI</t>
-  </si>
-  <si>
-    <t>EU / UK market</t>
-  </si>
-  <si>
-    <t>Can product incentives push AI companions toward manipulative engagement?</t>
-  </si>
-  <si>
-    <t>Version updated Aug 2026.</t>
-  </si>
-  <si>
-    <t>Emotional dependence</t>
-  </si>
-  <si>
-    <t>Shi et al.</t>
-  </si>
-  <si>
-    <t>Perspective / evidence synthesis</t>
-  </si>
-  <si>
-    <t>Argues that emotional dependence can emerge incidentally in general-purpose AI use and may alter future preferences for human vs AI support.</t>
-  </si>
-  <si>
-    <t>Highlights cumulative interaction effects that one-shot safety evaluations can miss.</t>
-  </si>
-  <si>
-    <t>Long-term interaction ethics; product policy; research gaps</t>
-  </si>
-  <si>
-    <t>Should general-purpose assistants be evaluated for long-term relational effects, not just single-turn harms?</t>
-  </si>
-  <si>
-    <t>Includes synthesis of longitudinal evidence.</t>
-  </si>
-  <si>
-    <t>Identity and parasocial interaction</t>
-  </si>
-  <si>
-    <t>Negotiating Digital Identities with AI Companions</t>
-  </si>
-  <si>
-    <t>HCI / computational social science</t>
-  </si>
-  <si>
-    <t>Studies identity construction and negotiation in AI-companion communities using large-scale online discussions.</t>
-  </si>
-  <si>
-    <t>Useful for understanding anthropomorphism and dependence as social processes rather than merely UI bugs.</t>
-  </si>
-  <si>
-    <t>HCI seminar; identity; anthropomorphism</t>
-  </si>
-  <si>
-    <t>How do AI companions reshape users' identities, expectations and social relationships?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2601.12181v1</t>
-  </si>
-  <si>
-    <t>Analyzes 22,374 online discussions.</t>
-  </si>
-  <si>
-    <t>Governance of autonomous agents</t>
-  </si>
-  <si>
-    <t>Raji &amp; Bashir</t>
-  </si>
-  <si>
-    <t>Systematic review</t>
-  </si>
-  <si>
-    <t>Reviews governance priorities, mechanisms and stakeholder roles for AI systems that autonomously plan and execute tasks.</t>
-  </si>
-  <si>
-    <t>Important 2026 bridge from chatbot ethics to systems that can act in the world.</t>
-  </si>
-  <si>
-    <t>Agentic AI governance; research agenda; seminar</t>
-  </si>
-  <si>
-    <t>How should accountability change when AI can plan, call tools and execute actions autonomously?</t>
-  </si>
-  <si>
-    <t>Published Jul 2026.</t>
-  </si>
-  <si>
-    <t>Security and governance practice</t>
-  </si>
-  <si>
-    <t>State of Agentic AI Security and Governance</t>
-  </si>
-  <si>
-    <t>OWASP GenAI Security Project</t>
-  </si>
-  <si>
-    <t>Security / governance report</t>
-  </si>
-  <si>
-    <t>Practitioner standard</t>
-  </si>
-  <si>
-    <t>Covers governance and security issues for autonomous AI systems, including controls, oversight and operational risk.</t>
-  </si>
-  <si>
-    <t>Gives practitioners a deployment-oriented complement to academic governance work.</t>
-  </si>
-  <si>
-    <t>Agent security; enterprise governance; checklist design</t>
-  </si>
-  <si>
-    <t>What controls are necessary when agents receive tools, permissions and persistent access?</t>
-  </si>
-  <si>
-    <t>https://genai.owasp.org/resource/state-of-agentic-ai-security-and-governance/</t>
-  </si>
-  <si>
-    <t>Practitioner-focused resource.</t>
-  </si>
-  <si>
-    <t>AI in education ethics</t>
-  </si>
-  <si>
-    <t>AI and the future of education: Disruptions, dilemmas and directions</t>
-  </si>
-  <si>
-    <t>Policy / anthology</t>
-  </si>
-  <si>
-    <t>Official / expert collection</t>
-  </si>
-  <si>
-    <t>Explores philosophical, ethical and pedagogical dilemmas created by AI in education and human-machine co-creation.</t>
-  </si>
-  <si>
-    <t>Useful domain case study showing how general AI-ethics principles change in a real institution such as education.</t>
-  </si>
-  <si>
-    <t>Education case study; classroom discussion; policy</t>
-  </si>
-  <si>
-    <t>How should education preserve human agency, fairness and learning integrity in an AI-rich environment?</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/articles/ai-and-future-education-disruptions-dilemmas-and-directions</t>
-  </si>
-  <si>
-    <t>Published Jan 2026.</t>
-  </si>
-  <si>
-    <t>Scale, data and social harms</t>
-  </si>
-  <si>
-    <t>On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
-  </si>
-  <si>
-    <t>Bender et al.</t>
-  </si>
-  <si>
-    <t>FAccT research paper</t>
-  </si>
-  <si>
-    <t>Raises concerns about environmental cost, training-data scale, bias, documentation and the gap between linguistic form and meaning.</t>
-  </si>
-  <si>
-    <t>Foundational critical reading that explains why ethics concerns were present before today's frontier LLMs.</t>
-  </si>
-  <si>
-    <t>Historical foundation; data ethics; critical perspective</t>
-  </si>
-  <si>
-    <t>Does scaling language models without understanding data and social context create predictable harms?</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3442188.3445922</t>
-  </si>
-  <si>
-    <t>FAccT 2021; foundational.</t>
-  </si>
-  <si>
-    <t>Language-model harm taxonomy</t>
-  </si>
-  <si>
-    <t>Ethical and Social Risks of Harm from Language Models</t>
-  </si>
-  <si>
-    <t>Weidinger et al.</t>
-  </si>
-  <si>
-    <t>Risk taxonomy / research</t>
-  </si>
-  <si>
-    <t>Organizes harms around discrimination, information hazards, misinformation, malicious use, human-computer interaction and socioeconomic/environmental harms.</t>
-  </si>
-  <si>
-    <t>One of the clearest early taxonomies for turning 'LLM ethics' into categories of harm.</t>
-  </si>
-  <si>
-    <t>Foundations; risk taxonomy; related work</t>
-  </si>
-  <si>
-    <t>What types of harm can language models create, and through which pathways?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2112.04359</t>
-  </si>
-  <si>
-    <t>Published work originated from DeepMind research.</t>
-  </si>
-  <si>
-    <t>Foundation-model societal impact</t>
-  </si>
-  <si>
-    <t>On the Opportunities and Risks of Foundation Models</t>
-  </si>
-  <si>
-    <t>Bommasani et al.</t>
-  </si>
-  <si>
-    <t>Examines foundation models across capabilities, homogenization, adaptation, evaluation, robustness, security, fairness, misuse, law and societal impact.</t>
-  </si>
-  <si>
-    <t>Provides broad conceptual background for why one upstream model can propagate benefits and harms across many downstream systems.</t>
-  </si>
-  <si>
-    <t>Foundation models; societal impact; literature review</t>
-  </si>
-  <si>
-    <t>How does reliance on a small number of foundation models concentrate systemic risk?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2108.07258</t>
-  </si>
-  <si>
-    <t>Stanford CRFM foundational report.</t>
-  </si>
-  <si>
-    <t>New This Week — Automatically Discovered</t>
-  </si>
-  <si>
-    <t>Recent high-scoring discoveries from scholarly APIs and official policy pages.</t>
-  </si>
-  <si>
-    <t>Detected</t>
-  </si>
-  <si>
-    <t>Published</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Importance Score</t>
-  </si>
-  <si>
-    <t>Why flagged</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>DOI</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>2026-08-16</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>A Common Standard for AI Incident Accountability</t>
-  </si>
-  <si>
-    <t>Zenodo (CERN European Organization for Nuclear Research)</t>
-  </si>
-  <si>
-    <t>article</t>
-  </si>
-  <si>
-    <t>Must Read Candidate</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, accountability, disclosure, reporting; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21907857</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21907857</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Automatically discovered; verify bibliographic details before formal citation.</t>
-  </si>
-  <si>
-    <t>Autonomous Decision Assurance Layer for AI-Driven Enterprise Analytics: Bridging Governance, Multi-Agent AI, and Executive Decision Intelligence in Saudi Vision 2030 Organizations</t>
-  </si>
-  <si>
-    <t>International Journal for Research in Applied Science and Engineering Technology</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.22214/ijraset.2026.84573</t>
-  </si>
-  <si>
-    <t>10.22214/ijraset.2026.84573</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21907856</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21907856</t>
-  </si>
-  <si>
-    <t>Sustainability and Environmental Ethics in Sanskrit Texts: A Geographical Perspective</t>
-  </si>
-  <si>
-    <t>Environment &amp; Labor</t>
-  </si>
-  <si>
-    <t>Prantik Gabeshana Patrika</t>
-  </si>
-  <si>
-    <t>journal-article</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: water, environment, sustainability; strong scholarly metadata source; impact signal: framework, guidelines, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.67841/pgp.260501082</t>
-  </si>
-  <si>
-    <t>10.67841/pgp.260501082</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>Validating the Virtue Ethics Measurement Scale Within an Open Distance e-Learning Higher Education Institution in South Africa: Students’ Perspectives of Generative AI Practices</t>
-  </si>
-  <si>
-    <t>Algorithms</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3390/a19080682</t>
-  </si>
-  <si>
-    <t>10.3390/a19080682</t>
-  </si>
-  <si>
-    <t>2026-08-15</t>
-  </si>
-  <si>
-    <t>Examining the Impact of Social-Emotional Learning on Academic Achievement in African American Middle School Girls</t>
-  </si>
-  <si>
-    <t>Seton Hall University eRepository (Seton Hall University)</t>
-  </si>
-  <si>
-    <t>dissertation</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://openalex.org/W7160680247</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>Managing ESG and cyber risks in Kazakhstan’s low-carbon transition by aligning EU and Chinese standards through demoethics</t>
-  </si>
-  <si>
-    <t>Discover Sustainability</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, sustainability; impact signal: framework, standard, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s43621-026-04260-z</t>
-  </si>
-  <si>
-    <t>10.1007/s43621-026-04260-z</t>
-  </si>
-  <si>
-    <t>A Framework for Protecting Students Privacy in Online and Offline Digital Footprints</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL JOURNAL OF COMPUTER SCIENCE AND MATHEMATICAL THEORY E-ISSN</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
-  </si>
-  <si>
-    <t>10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
-  </si>
-  <si>
-    <t>A Review of the TITAN Guideline: Advancing Transparency and Responsible Artificial Intelligence Use in Medical Research and Scholarly Publishing</t>
-  </si>
-  <si>
-    <t>Electronic Journal of Medical Research</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, accountability, reporting; impact signal: framework, guidelines, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.64813/ejmr.2026.126</t>
-  </si>
-  <si>
-    <t>10.64813/ejmr.2026.126</t>
-  </si>
-  <si>
-    <t>Digital personas of AI use in nursing education: a latent class analysis of learning behaviors and academic engagement</t>
-  </si>
-  <si>
-    <t>Frontiers in Medicine</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fmed.2026.1859093</t>
-  </si>
-  <si>
-    <t>10.3389/fmed.2026.1859093</t>
-  </si>
-  <si>
-    <t>Brazil's ENAMED and the Governance of AI-Supported Exam Preparation: A Conceptual Policy Analysis</t>
-  </si>
-  <si>
-    <t>International Journal For Multidisciplinary Research</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: standard, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.36948/ijfmr.2026.v08i04.84125</t>
-  </si>
-  <si>
-    <t>10.36948/ijfmr.2026.v08i04.84125</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>Beyond Visual Evidence: Revealing and Mitigating Relational Privacy Leakage in Document MLLMs</t>
-  </si>
-  <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>matches Privacy: privacy, leakage, extraction; impact signal: benchmark, framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12911v1</t>
-  </si>
-  <si>
-    <t>10.1145/3767308.3835901</t>
-  </si>
-  <si>
-    <t>Digital Transformation of the Indonesian Public Sector: A Systematic Review of Governance, Audit, and Service Innovation</t>
-  </si>
-  <si>
-    <t>F1000Research</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: systematic review, framework, guidelines; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.12688/f1000research.188727.1</t>
-  </si>
-  <si>
-    <t>10.12688/f1000research.188727.1</t>
-  </si>
-  <si>
-    <t>Performance, interaction, and ethical evaluation in the use of generative artificial intelligence in engineering education</t>
-  </si>
-  <si>
-    <t>Education and Information Technologies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, regulation, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10639-026-14112-y</t>
-  </si>
-  <si>
-    <t>10.1007/s10639-026-14112-y</t>
-  </si>
-  <si>
-    <t>Exploring student use of generative AI in higher education: A dual-institutional study</t>
-  </si>
-  <si>
-    <t>book-chapter</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10639-026-14100-2</t>
-  </si>
-  <si>
-    <t>10.1007/s10639-026-14100-2</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>How Personal and Cognitive Traits Influence AI Attitudes, Ethics, and Well-being: The Role of AI Autonomy and Criticality in Design</t>
-  </si>
-  <si>
-    <t>SN Computer Science</t>
-  </si>
-  <si>
-    <t>matches Persuasion &amp; Manipulation: influence, autonomy; impact signal: survey, framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s42979-026-05214-y</t>
-  </si>
-  <si>
-    <t>10.1007/s42979-026-05214-y</t>
-  </si>
-  <si>
-    <t>Ethics Suppression in AI Development: A Comparative Case Study of Responsible AI Under Competitive Pressure</t>
-  </si>
-  <si>
-    <t>International Journal of Applied Research in Business and Management</t>
-  </si>
-  <si>
-    <t>matches Foundations: ethics, responsible ai; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51137/wrp.ijarbm.869</t>
-  </si>
-  <si>
-    <t>10.51137/wrp.ijarbm.869</t>
-  </si>
-  <si>
-    <t>Generative AI in African Higher Education: A Systematic Review of Opportunities, Ethical Challenges, and Institutional Readiness</t>
-  </si>
-  <si>
-    <t>Journal of University Teaching and Learning Practice</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.53761/c682ye61</t>
-  </si>
-  <si>
-    <t>10.53761/c682ye61</t>
-  </si>
-  <si>
-    <t>Which LLM Is Your Ideal Companion? Evaluating Emotional Companion Capabilities of LLMs Based on Adult Attachment Theory</t>
-  </si>
-  <si>
-    <t>matches Human-AI Relationships: companion, emotional support, attachment; impact signal: benchmark, evaluation; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13168v1</t>
-  </si>
-  <si>
-    <t>InFactPlanner: Planning Sustainable Geo-Distributed LLM Data Centers</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, carbon, sustainability; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12915v1</t>
-  </si>
-  <si>
-    <t>Legitimacy Criteria for Strategic Communication in the Age of Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>The Proceedings of the World Conference on Social Sciences and Humanities.</t>
-  </si>
-  <si>
-    <t>conference-paper</t>
-  </si>
-  <si>
-    <t>matches Persuasion &amp; Manipulation: persuasion, manipulation, influence, behavioral influence; impact signal: framework, regulation, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.33422/shconf.v3i1.2047</t>
-  </si>
-  <si>
-    <t>10.33422/shconf.v3i1.2047</t>
-  </si>
-  <si>
-    <t>A carbon aware job scheduling framework for data center sustainability using deep learning training</t>
-  </si>
-  <si>
-    <t>Discover Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, environment, sustainability; strong scholarly metadata source; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s44163-026-02022-4</t>
-  </si>
-  <si>
-    <t>10.1007/s44163-026-02022-4</t>
-  </si>
-  <si>
-    <t>How electoral management bodies govern digital electoral systems: capacity, authority, and accountability</t>
-  </si>
-  <si>
-    <t>Frontiers in Political Science</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: systematic review, framework, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpos.2026.1877569</t>
-  </si>
-  <si>
-    <t>10.3389/fpos.2026.1877569</t>
-  </si>
-  <si>
-    <t>Leveraging strategic facilities management to achieve corporate ESG and sustainability: a literature review</t>
-  </si>
-  <si>
-    <t>Frontiers in Environmental Economics</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: environment, sustainability; impact signal: framework, governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/frevc.2026.1839120</t>
-  </si>
-  <si>
-    <t>10.3389/frevc.2026.1839120</t>
-  </si>
-  <si>
-    <t>Effect of Artificial Intelligence (AI) Study Tools on the Study Behaviour of Pharmacology and Medical Students in Bauchi State, Nigeria</t>
-  </si>
-  <si>
-    <t>WORLD JOURNAL OF INNOVATION AND MODERN TECHNOLOGY</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, guidelines, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.56201/wjimt.v10.no7.2026.pg351.366</t>
-  </si>
-  <si>
-    <t>10.56201/wjimt.v10.no7.2026.pg351.366</t>
-  </si>
-  <si>
-    <t>Analysis of PAI Students' Readiness for the Integration of Artificial Intelligence in Learning at Ahmad Dahlan University</t>
-  </si>
-  <si>
-    <t>EDUSOSHUM Journal of Islamic Education and Social Humanities</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.52366/edusoshum.v6i3.550</t>
-  </si>
-  <si>
-    <t>10.52366/edusoshum.v6i3.550</t>
-  </si>
-  <si>
-    <t>Beyond the Device: Reforming Higher Education and Teacher Education Curricula from ICT Literacy to AI Pedagogical Readiness in East Africa</t>
-  </si>
-  <si>
-    <t>East African Journal of Education Studies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.37284/eajes.9.3.5567</t>
-  </si>
-  <si>
-    <t>10.37284/eajes.9.3.5567</t>
-  </si>
-  <si>
-    <t>Acceptance of Generative AI for Supporting Innovative Learning in Vocational Education</t>
-  </si>
-  <si>
-    <t>World Journal of Education</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: survey, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5430/wje.v16n3p30</t>
-  </si>
-  <si>
-    <t>10.5430/wje.v16n3p30</t>
-  </si>
-  <si>
-    <t>Benchmarking Knowledge-Extraction Attack and Defense on Retrieval-Augmented Generation (RAG)</t>
-  </si>
-  <si>
-    <t>OpenAlex</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>matches Privacy: privacy, extraction; impact signal: benchmark, framework, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3770855.3817524</t>
-  </si>
-  <si>
-    <t>10.1145/3770855.3817524</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>Governing Agentic AI in FinTech</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11344v2</t>
-  </si>
-  <si>
-    <t>Toward Meaningful Transparency for AI Chatbots: Disclosing Persuasive Intent Reduces Persuasion</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, disclosure, provenance; impact signal: regulation, policy, randomized; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11794v1</t>
-  </si>
-  <si>
-    <t>Research on the Judicial Fairness Challenges and Legal Regulation of AI-Assisted Judgments in the Context of Digital Justice</t>
-  </si>
-  <si>
-    <t>Advanced Electromagnetics</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.7716/aem.v15i3.3403</t>
-  </si>
-  <si>
-    <t>10.7716/aem.v15i3.3403</t>
-  </si>
-  <si>
-    <t>The Correlation Between Exposure to English-Language Content on Instagram and Listening Comprehension among EFL Students at UIN Datokarama Palu</t>
-  </si>
-  <si>
-    <t>Journal of General Education and Humanities</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.58421/gehu.v5i4.1936</t>
-  </si>
-  <si>
-    <t>10.58421/gehu.v5i4.1936</t>
-  </si>
-  <si>
-    <t>Motivation to learn and teach home economics in higher education: Predictors and comparative analysis</t>
-  </si>
-  <si>
-    <t>Social Sciences &amp; Humanities Open</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.ssaho.2026.103414</t>
-  </si>
-  <si>
-    <t>10.1016/j.ssaho.2026.103414</t>
-  </si>
-  <si>
-    <t>The Impact of Artificial Intelligence on English Language Learning, Communication, and Linguistic Development: Opportunities and Challenges</t>
-  </si>
-  <si>
-    <t>Journal of Intelligent Decision Making and Information Science</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.59543/jidmis.v3.1938</t>
-  </si>
-  <si>
-    <t>10.59543/jidmis.v3.1938</t>
-  </si>
-  <si>
-    <t>AI literacy and subject specialization in pre-service teacher education: a mixed-methods study of dimensional profiles and perceived pedagogical challenges</t>
-  </si>
-  <si>
-    <t>Frontiers in Education</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1876627</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1876627</t>
-  </si>
-  <si>
-    <t>Development and pilot testing of multi-stakeholder questionnaires for assessing University 4.0 transformation in higher education institutions</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; impact signal: governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1908552</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1908552</t>
-  </si>
-  <si>
-    <t>PENGARUH MUSIK AI TERHADAP PENINGKATAN MOTIVASI BELAJAR SISWA PADA MATA PELAJARAN IPS DI KELAS IV SD NEGERI 73 AMBON</t>
-  </si>
-  <si>
-    <t>SOCIAL : Jurnal Inovasi Pendidikan IPS</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51878/social.v6i3.14523</t>
-  </si>
-  <si>
-    <t>10.51878/social.v6i3.14523</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>Physical Processing of Aquatic Gel Foods: From Protein Structure Regulation to Health, Sustainability, and Personalized Design</t>
-  </si>
-  <si>
-    <t>Comprehensive Reviews in Food Science and Food Safety</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, sustainability; strong scholarly metadata source; impact signal: regulation, standard, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/1541-4337.70601</t>
-  </si>
-  <si>
-    <t>10.1111/1541-4337.70601</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>ChatGPT and Large Language Models in Contemporary Nursing</t>
-  </si>
-  <si>
-    <t>Journal of Clinical Nursing</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/jocn.70490</t>
-  </si>
-  <si>
-    <t>10.1111/jocn.70490</t>
-  </si>
-  <si>
-    <t>Software Engineering for and with GUI Agent</t>
-  </si>
-  <si>
-    <t>arXiv (Cornell University)</t>
-  </si>
-  <si>
-    <t>preprint</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, evaluation, audit; impact signal: benchmark, framework, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.48550/arxiv.2608.09278</t>
-  </si>
-  <si>
-    <t>10.48550/arxiv.2608.09278</t>
-  </si>
-  <si>
-    <t>Banking Performance under the Lens of Earnings Management: A Theoretical and Bibliometric Systematic Review</t>
-  </si>
-  <si>
-    <t>Bulletin of Social Studies and Community Development</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, disclosure, reporting; impact signal: systematic review, framework, guidelines; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.61436/bsscd/v5i3.pp253-267</t>
-  </si>
-  <si>
-    <t>10.61436/bsscd/v5i3.pp253-267</t>
-  </si>
-  <si>
-    <t>Pedagogical prompting rather than technical mastery: Generative AI use by English and English-medium instruction teachers</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1901680</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1901680</t>
-  </si>
-  <si>
-    <t>Applied and Filtered: An End-to-End Algorithmic Fairness Audit of A Public Employment Agency</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: evaluation, audit; impact signal: evaluation, audit; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13022v1</t>
-  </si>
-  <si>
-    <t>Pre-service teachers' general pedagogical knowledge and pedagogical learning opportunities at entry into induction: comparing traditional and alternative teacher education programs</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: standard, longitudinal; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1790135</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1790135</t>
-  </si>
-  <si>
-    <t>Policy Integration and Implementation Gaps in China’s Dual-Carbon Strategy: A Multi-Dimensional Analysis of Carbon Trading System, New Energy Vehicle Incentives, and Air Quality Policies</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon; impact signal: policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.59543/jidmis.v3.1782</t>
-  </si>
-  <si>
-    <t>10.59543/jidmis.v3.1782</t>
-  </si>
-  <si>
-    <t>Dysfunction of Zakat Village Governance in Papua: Fragmentation of Collaboration and Inequality of Amil Capacity</t>
-  </si>
-  <si>
-    <t>JURNAL ILMIAH GEMA PERENCANA</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, evaluation; strong scholarly metadata source; impact signal: framework, regulation, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.61860/jigp.v5i1.411</t>
-  </si>
-  <si>
-    <t>10.61860/jigp.v5i1.411</t>
-  </si>
-  <si>
-    <t>Human-centric AI governance in the European Union. Accountability, fundamental rights, and institutional resilience in public administration</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpos.2026.1928481</t>
-  </si>
-  <si>
-    <t>10.3389/fpos.2026.1928481</t>
-  </si>
-  <si>
-    <t>Delivering building demand flexibility for grid-interactive operation: from perception and cognition to decision, execution, and verification</t>
-  </si>
-  <si>
-    <t>Applied Energy</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon; impact signal: framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.apenergy.2026.128668</t>
-  </si>
-  <si>
-    <t>10.1016/j.apenergy.2026.128668</t>
-  </si>
-  <si>
-    <t>PENGARUH MODEL PEMBELAJARAN PROJECT BASED LEARNING DAN KEDISIPLINAN BELAJAR TERHADAP KESIAPAN KERJA SISWA PADA JURUSAN AKUNTANSI KEUANGAN LEMABAGA DI SMK NEGERI 1 PANGKEP</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; impact signal: survey; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51878/social.v6i3.14617</t>
-  </si>
-  <si>
-    <t>10.51878/social.v6i3.14617</t>
-  </si>
-  <si>
-    <t>Large Language Model-facilitated national review on the use of ecological tools and processes in Environmental Impact Statements (EIS) in the U.S. with demonstrated use cases for environmental planners, legal practitioners, and researchers</t>
-  </si>
-  <si>
-    <t>Springer Science and Business Media LLC</t>
-  </si>
-  <si>
-    <t>posted-content</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, environment, labor; strong scholarly metadata source; impact signal: benchmark, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.21203/rs.3.rs-10627892/v1</t>
-  </si>
-  <si>
-    <t>10.21203/rs.3.rs-10627892/v1</t>
-  </si>
-  <si>
-    <t>Optimization of Household Equipment and Instrumentation in an Effort to Save Electrical Energy in a Restaurant</t>
-  </si>
-  <si>
-    <t>International Journal Of Community Service</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, environment; strong scholarly metadata source; impact signal: survey, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51601/ijcs.v6i3.1022</t>
-  </si>
-  <si>
-    <t>10.51601/ijcs.v6i3.1022</t>
-  </si>
-  <si>
-    <t>Effect of Public Safety Center Video-Based Education on Emergency Response Attitudes Among High School Students</t>
-  </si>
-  <si>
-    <t>Jurnal Kegawatdaruratan Medis Indonesia</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.58545/jkmi.v5i2.827</t>
-  </si>
-  <si>
-    <t>10.58545/jkmi.v5i2.827</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>From Single Chatbots to Governed Agent Ecosystems: An Agentic AI Pattern Catalogue and Orchestration Framework for Mission-Critical Hospital Information Management Systems</t>
-  </si>
-  <si>
-    <t>matches Agentic AI: agentic ai, autonomous agent, multi-agent; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.07627v1</t>
-  </si>
-  <si>
-    <t>10.38124/ijisrt/26jul830</t>
-  </si>
-  <si>
-    <t>Bias Smells in AI Software Development: Recognizing Potential Sources of Fairness Debt</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.48550/arxiv.2608.10248</t>
-  </si>
-  <si>
-    <t>10.48550/arxiv.2608.10248</t>
-  </si>
-  <si>
-    <t>Quantifying the Relationship Between Clinical Safety and Environmental Impact in Therapeutic LLMs</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, carbon, environment; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11830v1</t>
-  </si>
-  <si>
-    <t>Benchmark-Based Comparative Assessment of Publicly Benchmarked Indian Foundation Models: A Capability and Evaluation-Maturity Framework</t>
-  </si>
-  <si>
-    <t>matches India &amp; Global South: multilingual, india; impact signal: survey, benchmark, framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11891v1</t>
-  </si>
-  <si>
-    <t>Academic League of Artificial Intelligence - An Integrative Perspective of Teaching, Research, and Extension</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13447v1</t>
-  </si>
-  <si>
-    <t>Educational Aspirations in Contemporary Indian Education: A Critical Conceptual Synthesis for Holistic Learner Development</t>
-  </si>
-  <si>
-    <t>Asian Journal of Education and Social Studies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: policy, longitudinal; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.9734/ajess/2026/v52i83261</t>
-  </si>
-  <si>
-    <t>10.9734/ajess/2026/v52i83261</t>
-  </si>
-  <si>
-    <t>Solar Exposure and Photoprotection Behaviors as Determinants of Acne Vulgaris Severity Among University Students in Andalusia-Spain</t>
-  </si>
-  <si>
-    <t>Ibn Sina Journal of Medical Science Health &amp; Pharmacy</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; impact signal: survey, framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.64440/ibnsina/sina0027</t>
-  </si>
-  <si>
-    <t>10.64440/ibnsina/sina0027</t>
-  </si>
-  <si>
-    <t>FSGR: Mitigating Token Frequency Bias for Fair SID-Based Generative Recommendation</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12845v1</t>
-  </si>
-  <si>
-    <t>HEPE — Complete 16-State AI Governance Space with Lyapunov Values (Hardware-Enforced Policy Engine)</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: policy, governance, audit; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21935563</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21935563</t>
-  </si>
-  <si>
-    <t>What Remains Ours to Think? Reclaiming Critical Thinking in AI‐Augmented Student Leadership Education</t>
-  </si>
-  <si>
-    <t>New Directions for Student Leadership</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/yd.70068</t>
-  </si>
-  <si>
-    <t>10.1002/yd.70068</t>
-  </si>
-  <si>
-    <t>Supervision in educational leadership: practices, challenges, and innovations in the UAE — a multi-level coupling analysis of the current and future</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: benchmark, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1862260</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1862260</t>
-  </si>
-  <si>
-    <t>Research ethics and publication policies in journals using the Korea Institute of Science and Technology Information (KISTI) academic publishing platform: a content analysis of 181 journals</t>
-  </si>
-  <si>
-    <t>Science Editing</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: accountability, disclosure; impact signal: guidelines, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.6087/kcse.403</t>
-  </si>
-  <si>
-    <t>10.6087/kcse.403</t>
-  </si>
-  <si>
-    <t>Striking a Balance between the Right to Privacy and Freedom of Expression: A Case Study of Women’s Digital Rights in Tanzania</t>
-  </si>
-  <si>
-    <t>East African Journal of Law and Ethics</t>
-  </si>
-  <si>
-    <t>matches Regulation: regulation, legal framework, standard; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.37284/eajle.9.3.5557</t>
-  </si>
-  <si>
-    <t>10.37284/eajle.9.3.5557</t>
-  </si>
-  <si>
-    <t>Evaluation of the CIPP Model in a Project-Based Basic Electronics Course: A Discriminant Validity and Common Method Bias Analysis</t>
-  </si>
-  <si>
-    <t>Educative: Jurnal Ilmiah Pendidikan</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.70437/educative.v4i2.2180</t>
-  </si>
-  <si>
-    <t>10.70437/educative.v4i2.2180</t>
-  </si>
-  <si>
-    <t>The effectiveness of the contextual teaching and learning model on mathematical literacy skills in terms of learning motivation</t>
-  </si>
-  <si>
-    <t>Union: Jurnal Ilmiah Pendidikan Matematika</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.30738/union.v14i2.22911</t>
-  </si>
-  <si>
-    <t>10.30738/union.v14i2.22911</t>
-  </si>
-  <si>
-    <t>Review Queue — Human-in-the-loop Curation</t>
-  </si>
-  <si>
-    <t>Promote only sources that are genuinely useful. Automatic discovery is intentionally not identical to automatic curation.</t>
-  </si>
-  <si>
-    <t>Topic Map — What to Read for Each AI / LLM Ethics Question</t>
-  </si>
-  <si>
-    <t>Theme-level map generated from the current curated library.</t>
-  </si>
-  <si>
-    <t>Sources in library</t>
-  </si>
-  <si>
-    <t>2026-heavy?</t>
-  </si>
-  <si>
-    <t>Start with</t>
-  </si>
-  <si>
-    <t>Then read</t>
-  </si>
-  <si>
-    <t>Typical reader question</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Recommendation on the Ethics of Artificial Intelligence; On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1); Guidelines for providers of general-purpose AI models</t>
-  </si>
-  <si>
-    <t>An Evaluation of AI Companion Apps; Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
-  </si>
-  <si>
-    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders; Evaluating Language Models for Harmful Manipulation</t>
-  </si>
-  <si>
-    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory; SoK: The Privacy Paradox of Large Language Models</t>
-  </si>
-  <si>
-    <t>2026-Only View</t>
-  </si>
-  <si>
-    <t>Current-year curated items.</t>
-  </si>
-  <si>
-    <t>Policy, Governance &amp; Regulation</t>
-  </si>
-  <si>
-    <t>Curated governance, standards, transparency, law and human-rights sources.</t>
-  </si>
-  <si>
-    <t>Source Configuration</t>
-  </si>
-  <si>
-    <t>Edit config/sources.yaml in the repository to change the automation. This sheet is a readable mirror.</t>
-  </si>
-  <si>
-    <t>Endpoint / URL</t>
-  </si>
-  <si>
-    <t>Enabled</t>
-  </si>
-  <si>
-    <t>Authority</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>https://export.arxiv.org/api/query</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Fresh preprints</t>
-  </si>
-  <si>
-    <t>3-second delay between repeated calls</t>
-  </si>
-  <si>
-    <t>https://api.openalex.org/works</t>
-  </si>
-  <si>
-    <t>Broad scholarly discovery</t>
-  </si>
-  <si>
-    <t>OPENALEX_API_KEY optional</t>
-  </si>
-  <si>
-    <t>Crossref</t>
-  </si>
-  <si>
-    <t>https://api.crossref.org/works</t>
-  </si>
-  <si>
-    <t>Published DOI metadata</t>
-  </si>
-  <si>
-    <t>CONTACT_EMAIL recommended</t>
-  </si>
-  <si>
-    <t>NIST Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Official page watch</t>
-  </si>
-  <si>
-    <t>https://www.nist.gov/artificial-intelligence</t>
-  </si>
-  <si>
-    <t>Policy/news link discovery</t>
-  </si>
-  <si>
-    <t>First scan bootstraps without flooding</t>
-  </si>
-  <si>
-    <t>European Commission AI Act</t>
-  </si>
-  <si>
-    <t>OECD.AI Wonk</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/wonk</t>
-  </si>
-  <si>
-    <t>UNESCO Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/artificial-intelligence</t>
-  </si>
-  <si>
-    <t>IndiaAI / MeitY — PIB Releases</t>
-  </si>
-  <si>
-    <t>https://www.pib.gov.in/AllRelease.aspx?MenuId=30&amp;lang=1&amp;reg=3</t>
-  </si>
-  <si>
-    <t>Automation Update Log</t>
-  </si>
-  <si>
-    <t>Every run records discovery and deduplication counts.</t>
-  </si>
-  <si>
-    <t>New This Week</t>
-  </si>
-  <si>
-    <t>Review Queue</t>
-  </si>
-  <si>
-    <t>Auto-promoted</t>
-  </si>
-  <si>
-    <t>2026-08-16T12:18:00+05:30</t>
-  </si>
-  <si>
-    <t>Initial build</t>
-  </si>
-  <si>
-    <t>Living tracker package initialized</t>
-  </si>
-  <si>
-    <t>2026-08-16T07:19:28+00:00</t>
-  </si>
-  <si>
-    <t>Policy/IndiaAI Safe &amp; Trusted AI: HTTPError: 403 Client Error: Forbidden for url: https://indiaai.gov.in/hub/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>2026-08-16T07:39:54+00:00</t>
   </si>
   <si>
     <t>Automation Guide</t>
@@ -3404,7 +3407,7 @@
         <v>30</v>
       </c>
       <c r="I11" s="7">
-        <v>645</v>
+        <v>640</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3418,7 +3421,7 @@
         <v>31</v>
       </c>
       <c r="I12" s="7">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3527,7 +3530,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="22.7109375" customWidth="1"/>
@@ -3679,7 +3682,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
-        <v>26</v>
+        <v>819</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>28</v>
@@ -3703,6 +3706,35 @@
         <v>0</v>
       </c>
       <c r="I8" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="7">
+        <v>29</v>
+      </c>
+      <c r="D9" s="7">
+        <v>640</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0</v>
+      </c>
+      <c r="F9" s="7">
+        <v>68</v>
+      </c>
+      <c r="G9" s="7">
+        <v>68</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3730,7 +3762,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3740,7 +3772,7 @@
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3753,16 +3785,16 @@
         <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>428</v>
@@ -3773,19 +3805,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>786</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3793,19 +3825,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>786</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3813,19 +3845,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>786</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3833,19 +3865,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3853,19 +3885,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3873,19 +3905,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
   </sheetData>

--- a/AI_LLM_Ethics_Living_Tracker.xlsx
+++ b/AI_LLM_Ethics_Living_Tracker.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2973" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2976" uniqueCount="853">
   <si>
     <t>AI &amp; LLM Ethics — Living Literature Dashboard</t>
   </si>
@@ -111,2386 +111,2389 @@
     <t>Run time</t>
   </si>
   <si>
+    <t>2026-08-16T10:52:38+00:00</t>
+  </si>
+  <si>
+    <t>Mode</t>
+  </si>
+  <si>
+    <t>scheduled/manual</t>
+  </si>
+  <si>
+    <t>Sources checked</t>
+  </si>
+  <si>
+    <t>Candidates fetched</t>
+  </si>
+  <si>
+    <t>New after dedupe</t>
+  </si>
+  <si>
+    <t>Errors / notes</t>
+  </si>
+  <si>
+    <t>Completed without recorded source errors</t>
+  </si>
+  <si>
+    <t>Start Here — 2026-aware AI &amp; LLM Ethics Reading Path</t>
+  </si>
+  <si>
+    <t>Use this sheet for a compact orientation. The automated discovery tabs are intentionally separate from the stable reading path.</t>
+  </si>
+  <si>
+    <t>Curated sources</t>
+  </si>
+  <si>
+    <t>2026 sources</t>
+  </si>
+  <si>
+    <t>Must Read</t>
+  </si>
+  <si>
+    <t>Official / institutional</t>
+  </si>
+  <si>
+    <t>Recommended 10-source reading path</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>Read this</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Why now</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Source URL</t>
+  </si>
+  <si>
+    <t>Responsible AI | The 2026 AI Index Report</t>
+  </si>
+  <si>
+    <t>Current 2025–2026 evidence or governance update</t>
+  </si>
+  <si>
+    <t>https://hai.stanford.edu/ai-index/2026-ai-index-report/responsible-ai</t>
+  </si>
+  <si>
+    <t>AI Act | Shaping Europe's digital future</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/regulatory-framework-ai</t>
+  </si>
+  <si>
+    <t>Guidelines on transparency obligations for providers and deployers of AI systems</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-transparency-ai-generated-content</t>
+  </si>
+  <si>
+    <t>Persuasion with Large Language Models: A Survey of Empirical Studies</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2411.06837v2</t>
+  </si>
+  <si>
+    <t>Emotional Support with Conversational AI: Talking to Machines About Life</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2603.22618v1</t>
+  </si>
+  <si>
+    <t>An Evaluation of AI Companion Apps</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2605.08093v2</t>
+  </si>
+  <si>
+    <t>Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2606.04150</t>
+  </si>
+  <si>
+    <t>Towards Agentic AI Governance: A Preliminary Assessment</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2607.07612</t>
+  </si>
+  <si>
+    <t>The 2025 Foundation Model Transparency Index</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2512.10169</t>
+  </si>
+  <si>
+    <t>India AI Governance Guidelines: Empowering Ethical and Responsible AI</t>
+  </si>
+  <si>
+    <t>https://indiaai.gov.in/article/india-ai-governance-guidelines-empowering-ethical-and-responsible-ai</t>
+  </si>
+  <si>
+    <t>Ethics of Artificial Intelligence &amp; LLMs — Curated Reading Library</t>
+  </si>
+  <si>
+    <t>Stable curated sources. Automatically discovered items are triaged separately before promotion.</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Subtopic</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Author / Body</t>
+  </si>
+  <si>
+    <t>Source Type</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>What it covers</t>
+  </si>
+  <si>
+    <t>Why the reader benefits</t>
+  </si>
+  <si>
+    <t>Best use</t>
+  </si>
+  <si>
+    <t>2026 Relevance Score</t>
+  </si>
+  <si>
+    <t>Read Priority</t>
+  </si>
+  <si>
+    <t>Region / Scope</t>
+  </si>
+  <si>
+    <t>Key ethical question</t>
+  </si>
+  <si>
+    <t>Notes / status</t>
+  </si>
+  <si>
+    <t>Reader mode</t>
+  </si>
+  <si>
+    <t>Responsible AI state of the field</t>
+  </si>
+  <si>
+    <t>Stanford HAI / AI Index</t>
+  </si>
+  <si>
+    <t>Annual evidence report</t>
+  </si>
+  <si>
+    <t>Institutional / data-driven</t>
+  </si>
+  <si>
+    <t>Tracks AI incidents, safety evaluation, transparency, responsible-AI reporting, and the widening gap between capability and governance.</t>
+  </si>
+  <si>
+    <t>Best current snapshot for showing that AI capability is advancing faster than safety measurement and transparency.</t>
+  </si>
+  <si>
+    <t>Lecture opener; literature review motivation; 2026 statistics</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>Are current evaluation and governance systems keeping pace with frontier AI capability?</t>
+  </si>
+  <si>
+    <t>2026 edition; strong source for current facts and figures.</t>
+  </si>
+  <si>
+    <t>Read closely</t>
+  </si>
+  <si>
+    <t>Foundation model transparency</t>
+  </si>
+  <si>
+    <t>Wan et al. / Stanford CRFM</t>
+  </si>
+  <si>
+    <t>Research report / index</t>
+  </si>
+  <si>
+    <t>Research report</t>
+  </si>
+  <si>
+    <t>Scores major foundation-model developers on disclosures covering data, compute, risk mitigation, usage and downstream impacts.</t>
+  </si>
+  <si>
+    <t>Lets readers move from vague calls for transparency to measurable disclosure dimensions and compare developers.</t>
+  </si>
+  <si>
+    <t>Transparency section; accountability case study; assignment</t>
+  </si>
+  <si>
+    <t>Global / industry</t>
+  </si>
+  <si>
+    <t>What information should frontier-model developers be required to disclose?</t>
+  </si>
+  <si>
+    <t>Average score fell from 58/100 in 2024 to 40/100 in 2025.</t>
+  </si>
+  <si>
+    <t>EU AI Act implementation</t>
+  </si>
+  <si>
+    <t>European Commission</t>
+  </si>
+  <si>
+    <t>Regulation / official guidance</t>
+  </si>
+  <si>
+    <t>Official</t>
+  </si>
+  <si>
+    <t>Official overview of the EU AI Act, risk-based obligations, implementation timeline, GPAI rules and transparency requirements.</t>
+  </si>
+  <si>
+    <t>Provides the clearest bridge between ethics principles and enforceable legal duties in 2026.</t>
+  </si>
+  <si>
+    <t>Regulation module; compliance discussion; policy comparison</t>
+  </si>
+  <si>
+    <t>European Union</t>
+  </si>
+  <si>
+    <t>When should ethical expectations become legal obligations?</t>
+  </si>
+  <si>
+    <t>General application date: 2 August 2026, with exceptions and phased provisions.</t>
+  </si>
+  <si>
+    <t>AI-generated content disclosure</t>
+  </si>
+  <si>
+    <t>Regulatory guidance</t>
+  </si>
+  <si>
+    <t>Explains Article 50 duties concerning user disclosure, machine-readable marking, AI-generated content and deepfakes.</t>
+  </si>
+  <si>
+    <t>Useful concrete example of how transparency ethics becomes a product-design requirement.</t>
+  </si>
+  <si>
+    <t>Deepfakes; disclosure; generative-AI product design</t>
+  </si>
+  <si>
+    <t>Should people always know when they are interacting with AI or seeing AI-generated content?</t>
+  </si>
+  <si>
+    <t>Article 50 applies from 2 August 2026.</t>
+  </si>
+  <si>
+    <t>General-purpose AI obligations</t>
+  </si>
+  <si>
+    <t>Guidelines for providers of general-purpose AI models</t>
+  </si>
+  <si>
+    <t>Clarifies obligations for providers of general-purpose AI models and the Commission's enforcement role.</t>
+  </si>
+  <si>
+    <t>Gives readers a current compliance perspective on frontier and general-purpose models rather than generic AI regulation.</t>
+  </si>
+  <si>
+    <t>GPAI governance; provider responsibilities; seminar discussion</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>What extra duties should apply to powerful general-purpose models?</t>
+  </si>
+  <si>
+    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-gpai-providers</t>
+  </si>
+  <si>
+    <t>Commission enforcement powers apply from 2 August 2026.</t>
+  </si>
+  <si>
+    <t>Read/skim</t>
+  </si>
+  <si>
+    <t>India AI governance</t>
+  </si>
+  <si>
+    <t>IndiaAI / MeitY</t>
+  </si>
+  <si>
+    <t>National governance guidance</t>
+  </si>
+  <si>
+    <t>Sets out principles and recommendations around fairness, accountability, safety, inclusivity and trustworthy AI in India.</t>
+  </si>
+  <si>
+    <t>Adds an India-specific governance perspective and prevents the reading list from being US/EU-centric.</t>
+  </si>
+  <si>
+    <t>India case study; policy comparison; local context</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>How should responsible AI governance reflect India's scale, diversity and public-interest priorities?</t>
+  </si>
+  <si>
+    <t>Released 5 Nov 2025 under the IndiaAI Mission.</t>
+  </si>
+  <si>
+    <t>AI safety capacity</t>
+  </si>
+  <si>
+    <t>Safe &amp; Trusted AI Working Group</t>
+  </si>
+  <si>
+    <t>India AI Impact Summit</t>
+  </si>
+  <si>
+    <t>Policy / working-group output</t>
+  </si>
+  <si>
+    <t>Focuses on AI safety capacity, evaluation, governance and incorporating Global South perspectives into international AI safety frameworks.</t>
+  </si>
+  <si>
+    <t>Useful for understanding how safety debates are being localized beyond US/EU institutions.</t>
+  </si>
+  <si>
+    <t>India 2026 update; global governance; discussion prompt</t>
+  </si>
+  <si>
+    <t>India / Global South</t>
+  </si>
+  <si>
+    <t>Who gets to define acceptable AI risk and safety standards globally?</t>
+  </si>
+  <si>
+    <t>https://impact.indiaai.gov.in/working-groups/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>2026-relevant IndiaAI Impact Summit initiative.</t>
+  </si>
+  <si>
+    <t>Risk management framework</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1)</t>
+  </si>
+  <si>
+    <t>NIST</t>
+  </si>
+  <si>
+    <t>Risk-management framework</t>
+  </si>
+  <si>
+    <t>Identifies GenAI-specific risks and actions across the AI lifecycle, aligned with Govern, Map, Measure and Manage.</t>
+  </si>
+  <si>
+    <t>One of the most practical sources for converting ethical concerns into operational risk controls.</t>
+  </si>
+  <si>
+    <t>Risk register; deployment checklist; governance design</t>
+  </si>
+  <si>
+    <t>United States / cross-sector</t>
+  </si>
+  <si>
+    <t>How can an organization operationalize trustworthy GenAI rather than merely state principles?</t>
+  </si>
+  <si>
+    <t>https://www.nist.gov/publications/artificial-intelligence-risk-management-framework-generative-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>Companion to NIST AI RMF 1.0.</t>
+  </si>
+  <si>
+    <t>Human-rights-centered AI ethics</t>
+  </si>
+  <si>
+    <t>Recommendation on the Ethics of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>UNESCO</t>
+  </si>
+  <si>
+    <t>International ethics standard</t>
+  </si>
+  <si>
+    <t>Defines principles including proportionality, do-no-harm, safety, privacy, fairness, transparency, accountability, sustainability and human oversight.</t>
+  </si>
+  <si>
+    <t>Provides a normative foundation for almost every later AI ethics topic.</t>
+  </si>
+  <si>
+    <t>Foundations lecture; ethics framework; compare policies</t>
+  </si>
+  <si>
+    <t>What values should guide the design and deployment of AI systems?</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
+  </si>
+  <si>
+    <t>Global UNESCO recommendation; remains foundational in 2026.</t>
+  </si>
+  <si>
+    <t>Trustworthy AI principles</t>
+  </si>
+  <si>
+    <t>OECD AI Principles</t>
+  </si>
+  <si>
+    <t>OECD</t>
+  </si>
+  <si>
+    <t>International policy principles</t>
+  </si>
+  <si>
+    <t>Principles for innovative and trustworthy AI, covering human rights, fairness, transparency, robustness, security and accountability.</t>
+  </si>
+  <si>
+    <t>Concise policy baseline that is easy to compare against NIST, UNESCO, EU and national frameworks.</t>
+  </si>
+  <si>
+    <t>Framework comparison; policy lecture; exam preparation</t>
+  </si>
+  <si>
+    <t>What minimum principles should trustworthy AI systems satisfy across countries?</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/ai-principles</t>
+  </si>
+  <si>
+    <t>Initially adopted 2019; updated May 2024.</t>
+  </si>
+  <si>
+    <t>International AI treaty</t>
+  </si>
+  <si>
+    <t>Framework Convention on Artificial Intelligence and Human Rights, Democracy and the Rule of Law</t>
+  </si>
+  <si>
+    <t>Council of Europe</t>
+  </si>
+  <si>
+    <t>International treaty</t>
+  </si>
+  <si>
+    <t>Official / legally binding framework</t>
+  </si>
+  <si>
+    <t>Addresses human rights, democratic processes, autonomy, transparency, accountability, equality and privacy across the AI lifecycle.</t>
+  </si>
+  <si>
+    <t>Shows the transition from voluntary ethics to treaty-based human-rights obligations.</t>
+  </si>
+  <si>
+    <t>Human-rights module; legal governance; global policy</t>
+  </si>
+  <si>
+    <t>International</t>
+  </si>
+  <si>
+    <t>How should AI development be constrained when it may affect fundamental rights and democratic institutions?</t>
+  </si>
+  <si>
+    <t>https://www.coe.int/en/web/artificial-intelligence/the-framework-convention-on-artificial-intelligence</t>
+  </si>
+  <si>
+    <t>First international legally binding treaty in this field; opened for signature 5 Sept 2024.</t>
+  </si>
+  <si>
+    <t>Developer risk reporting</t>
+  </si>
+  <si>
+    <t>How are AI developers managing risks? Insights from the Hiroshima AI Process reporting framework</t>
+  </si>
+  <si>
+    <t>International governance report</t>
+  </si>
+  <si>
+    <t>Official / multi-stakeholder</t>
+  </si>
+  <si>
+    <t>Analyzes how organizations report risk identification, safety, governance, content authentication and accountability practices.</t>
+  </si>
+  <si>
+    <t>Gives concrete examples of how frontier developers operationalize risk management, not just what principles say.</t>
+  </si>
+  <si>
+    <t>Industry governance; transparency; comparative analysis</t>
+  </si>
+  <si>
+    <t>G7 / global</t>
+  </si>
+  <si>
+    <t>Can voluntary transparency meaningfully improve accountability for advanced AI developers?</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/ai-publications/how-are-ai-developers-managing-risks-insights-from-responses-to-the-reporting-framework-of-the-hiroshima-ai-process-code-of-conduct</t>
+  </si>
+  <si>
+    <t>Reporting framework launched in 2025.</t>
+  </si>
+  <si>
+    <t>Comprehensive LLM ethics</t>
+  </si>
+  <si>
+    <t>Deconstructing the ethics of large language models from long-standing issues to new-emerging dilemmas</t>
+  </si>
+  <si>
+    <t>Deng et al.</t>
+  </si>
+  <si>
+    <t>Survey / review</t>
+  </si>
+  <si>
+    <t>Peer-reviewed</t>
+  </si>
+  <si>
+    <t>Surveys copyright, systematic bias, privacy, truthfulness, social norms and emerging ethical challenges of LLMs.</t>
+  </si>
+  <si>
+    <t>Good single-paper orientation before readers enter specialized literatures.</t>
+  </si>
+  <si>
+    <t>Literature review starting point; seminar reading</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>Which LLM ethical risks are old problems amplified by scale, and which are genuinely new?</t>
+  </si>
+  <si>
+    <t>https://link.springer.com/article/10.1007/s43681-025-00797-3</t>
+  </si>
+  <si>
+    <t>Published in AI and Ethics.</t>
+  </si>
+  <si>
+    <t>Bias evaluation and mitigation</t>
+  </si>
+  <si>
+    <t>Bias and Fairness in Large Language Models: A Survey</t>
+  </si>
+  <si>
+    <t>Gallegos et al.</t>
+  </si>
+  <si>
+    <t>Survey</t>
+  </si>
+  <si>
+    <t>Research / arXiv</t>
+  </si>
+  <si>
+    <t>Organizes social bias harms, evaluation metrics, datasets and mitigation techniques for LLMs.</t>
+  </si>
+  <si>
+    <t>Provides a technical taxonomy that makes 'AI bias' measurable rather than purely rhetorical.</t>
+  </si>
+  <si>
+    <t>Bias lecture; evaluation design; related work</t>
+  </si>
+  <si>
+    <t>How should fairness be defined and measured for generative language systems?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2309.00770</t>
+  </si>
+  <si>
+    <t>Still a useful technical survey in 2026.</t>
+  </si>
+  <si>
+    <t>Hallucination taxonomy</t>
+  </si>
+  <si>
+    <t>A Survey on Hallucination in Large Language Models</t>
+  </si>
+  <si>
+    <t>ACM Computing Surveys</t>
+  </si>
+  <si>
+    <t>Reviews hallucination principles, taxonomies, causes, evaluation, detection and mitigation in LLMs.</t>
+  </si>
+  <si>
+    <t>Helps distinguish factual reliability problems from broader moral or social harms.</t>
+  </si>
+  <si>
+    <t>Truthfulness; reliability; high-stakes deployment</t>
+  </si>
+  <si>
+    <t>When is an incorrect LLM output merely an error, and when does it become an ethical harm?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3703155</t>
+  </si>
+  <si>
+    <t>High-value technical survey.</t>
+  </si>
+  <si>
+    <t>Training-data leakage</t>
+  </si>
+  <si>
+    <t>New Privacy Risks for Large Language Models</t>
+  </si>
+  <si>
+    <t>Research paper</t>
+  </si>
+  <si>
+    <t>Preprint / current research</t>
+  </si>
+  <si>
+    <t>Examines data extraction and memorization risks, connecting privacy leakage with copyright and training-data provenance concerns.</t>
+  </si>
+  <si>
+    <t>Useful 2026 update showing privacy risk is not limited to classic membership inference.</t>
+  </si>
+  <si>
+    <t>Privacy section; training data; model memorization</t>
+  </si>
+  <si>
+    <t>What does a model owe people whose private or copyrighted data it can reproduce?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2509.14278v2</t>
+  </si>
+  <si>
+    <t>Version available Jan 2026.</t>
+  </si>
+  <si>
+    <t>Privacy threat landscape</t>
+  </si>
+  <si>
+    <t>SoK: The Privacy Paradox of Large Language Models</t>
+  </si>
+  <si>
+    <t>Systematization of knowledge</t>
+  </si>
+  <si>
+    <t>Preprint / research</t>
+  </si>
+  <si>
+    <t>Systematizes training-data extraction, reconstruction, inference-time privacy and protection mechanisms.</t>
+  </si>
+  <si>
+    <t>Gives readers a map of privacy attack surfaces instead of isolated examples.</t>
+  </si>
+  <si>
+    <t>Security/privacy module; research gap identification</t>
+  </si>
+  <si>
+    <t>Can LLM utility and strong privacy guarantees be achieved simultaneously?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2506.12699v2</t>
+  </si>
+  <si>
+    <t>Useful bridge between AI ethics and security.</t>
+  </si>
+  <si>
+    <t>Empirical privacy evaluation</t>
+  </si>
+  <si>
+    <t>Privacy Auditing of Large Language Models</t>
+  </si>
+  <si>
+    <t>Develops stronger privacy auditing techniques and more effective canaries for estimating empirical leakage.</t>
+  </si>
+  <si>
+    <t>Shows readers how privacy claims can be tested rather than assumed.</t>
+  </si>
+  <si>
+    <t>Methodology; model audit; technical assignment</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>How should developers demonstrate that a language model is not leaking training data?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2503.06808v1</t>
+  </si>
+  <si>
+    <t>Technical privacy-auditing work.</t>
+  </si>
+  <si>
+    <t>Reference as needed</t>
+  </si>
+  <si>
+    <t>Agent memory and contextual leakage</t>
+  </si>
+  <si>
+    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory</t>
+  </si>
+  <si>
+    <t>Security research</t>
+  </si>
+  <si>
+    <t>Studies privacy leakage from inference-time contextual memory in LLM agents, beyond training-data privacy.</t>
+  </si>
+  <si>
+    <t>Important for 2026 because persistent AI assistants and agents create a new privacy attack surface.</t>
+  </si>
+  <si>
+    <t>Agentic AI; memory privacy; security discussion</t>
+  </si>
+  <si>
+    <t>Research / agents</t>
+  </si>
+  <si>
+    <t>What privacy risks appear when AI systems remember and act on user context over time?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2604.23711v1</t>
+  </si>
+  <si>
+    <t>2026 agent-memory privacy paper.</t>
+  </si>
+  <si>
+    <t>Persuasion landscape</t>
+  </si>
+  <si>
+    <t>Research survey</t>
+  </si>
+  <si>
+    <t>Reviews empirical evidence on automated, personalized and interactive LLM persuasion and its effects on attitudes and behavior.</t>
+  </si>
+  <si>
+    <t>A direct entry point into one of the most important newer AI-ethics issues.</t>
+  </si>
+  <si>
+    <t>Manipulation lecture; social influence; governance</t>
+  </si>
+  <si>
+    <t>When does helpful persuasion become manipulation or undue influence?</t>
+  </si>
+  <si>
+    <t>Updated Apr 2026.</t>
+  </si>
+  <si>
+    <t>Human vs AI persuasion</t>
+  </si>
+  <si>
+    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders</t>
+  </si>
+  <si>
+    <t>Schoenegger et al.</t>
+  </si>
+  <si>
+    <t>Large-scale experiment</t>
+  </si>
+  <si>
+    <t>Compares a frontier LLM with incentivized human persuaders in interactive settings and measures compliance with correct and incorrect persuasion.</t>
+  </si>
+  <si>
+    <t>Provides concrete empirical evidence that persuasive capability can create both benefits and harms.</t>
+  </si>
+  <si>
+    <t>Case study; empirical evidence; class discussion</t>
+  </si>
+  <si>
+    <t>Should systems with human-level or greater persuasive power face special safeguards?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2505.09662</t>
+  </si>
+  <si>
+    <t>Preregistered, large-scale incentivized experiment.</t>
+  </si>
+  <si>
+    <t>Harmful influence evaluation</t>
+  </si>
+  <si>
+    <t>Evaluating Language Models for Harmful Manipulation</t>
+  </si>
+  <si>
+    <t>Akbulut et al.</t>
+  </si>
+  <si>
+    <t>Human-subject evaluation</t>
+  </si>
+  <si>
+    <t>Research / preprint</t>
+  </si>
+  <si>
+    <t>Introduces a framework for measuring harmful manipulation across public policy, finance and health with participants from multiple countries.</t>
+  </si>
+  <si>
+    <t>Shows how manipulation can be operationalized and evaluated across consequential domains.</t>
+  </si>
+  <si>
+    <t>Evaluation design; high-stakes AI; cross-country analysis</t>
+  </si>
+  <si>
+    <t>US / UK / India</t>
+  </si>
+  <si>
+    <t>How can harmful manipulation be measured before deployment?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/pdf/2603.25326</t>
+  </si>
+  <si>
+    <t>Includes 10,101 participants across three locales.</t>
+  </si>
+  <si>
+    <t>Sycophancy to strategic deception</t>
+  </si>
+  <si>
+    <t>From Sycophancy to Deception: A Unified Taxonomy for Misleading LLM Behavior</t>
+  </si>
+  <si>
+    <t>Taxonomy / research</t>
+  </si>
+  <si>
+    <t>Unifies hallucination, omission, pragmatic distortion, sycophancy and strategic deception under a common taxonomy of misleading behavior.</t>
+  </si>
+  <si>
+    <t>Helps readers avoid treating all misleading model outputs as the same failure mode.</t>
+  </si>
+  <si>
+    <t>Conceptual framework; deception; research taxonomy</t>
+  </si>
+  <si>
+    <t>Does intent or goal-directedness change how ethically serious misleading AI behavior is?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2604.04788</t>
+  </si>
+  <si>
+    <t>Current 2026 taxonomy.</t>
+  </si>
+  <si>
+    <t>Sycophancy</t>
+  </si>
+  <si>
+    <t>Sycophancy in Large Language Models: Causes and Mitigations</t>
+  </si>
+  <si>
+    <t>Lars Malmqvist</t>
+  </si>
+  <si>
+    <t>Technical survey</t>
+  </si>
+  <si>
+    <t>Surveys excessive agreement with users, causes, measurement and mitigation, and links sycophancy to hallucination and bias.</t>
+  </si>
+  <si>
+    <t>Useful for discussing why 'agreeable' assistants can become epistemically unsafe.</t>
+  </si>
+  <si>
+    <t>Alignment; user trust; truthfulness</t>
+  </si>
+  <si>
+    <t>Should an assistant prioritize user satisfaction or epistemic honesty when they conflict?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2411.15287</t>
+  </si>
+  <si>
+    <t>Technical survey.</t>
+  </si>
+  <si>
+    <t>Emotional support</t>
+  </si>
+  <si>
+    <t>Huang, Stodolska &amp; Sultana</t>
+  </si>
+  <si>
+    <t>Qualitative HCI research</t>
+  </si>
+  <si>
+    <t>Analyzes how emotional support is co-constructed with AI companions and tensions such as support vs dependency and validation vs delusion.</t>
+  </si>
+  <si>
+    <t>Provides nuanced evidence beyond simplistic claims that AI companions are either beneficial or harmful.</t>
+  </si>
+  <si>
+    <t>HCI ethics; mental-health-adjacent discussion; companionship</t>
+  </si>
+  <si>
+    <t>How should AI offer emotional support without reinforcing dependency or harmful beliefs?</t>
+  </si>
+  <si>
+    <t>2026 HCI-focused research.</t>
+  </si>
+  <si>
+    <t>Companion-app design</t>
+  </si>
+  <si>
+    <t>Empirical audit</t>
+  </si>
+  <si>
+    <t>Audits popular AI companion apps for dark patterns, anthropomorphism, stereotypes, erotica and technical issues.</t>
+  </si>
+  <si>
+    <t>Connects ethical risk to actual interface and monetization design choices, not only model behavior.</t>
+  </si>
+  <si>
+    <t>Product ethics; dark patterns; companion AI</t>
+  </si>
+  <si>
+    <t>EU / UK market</t>
+  </si>
+  <si>
+    <t>Can product incentives push AI companions toward manipulative engagement?</t>
+  </si>
+  <si>
+    <t>Version updated Aug 2026.</t>
+  </si>
+  <si>
+    <t>Emotional dependence</t>
+  </si>
+  <si>
+    <t>Shi et al.</t>
+  </si>
+  <si>
+    <t>Perspective / evidence synthesis</t>
+  </si>
+  <si>
+    <t>Argues that emotional dependence can emerge incidentally in general-purpose AI use and may alter future preferences for human vs AI support.</t>
+  </si>
+  <si>
+    <t>Highlights cumulative interaction effects that one-shot safety evaluations can miss.</t>
+  </si>
+  <si>
+    <t>Long-term interaction ethics; product policy; research gaps</t>
+  </si>
+  <si>
+    <t>Should general-purpose assistants be evaluated for long-term relational effects, not just single-turn harms?</t>
+  </si>
+  <si>
+    <t>Includes synthesis of longitudinal evidence.</t>
+  </si>
+  <si>
+    <t>Identity and parasocial interaction</t>
+  </si>
+  <si>
+    <t>Negotiating Digital Identities with AI Companions</t>
+  </si>
+  <si>
+    <t>HCI / computational social science</t>
+  </si>
+  <si>
+    <t>Studies identity construction and negotiation in AI-companion communities using large-scale online discussions.</t>
+  </si>
+  <si>
+    <t>Useful for understanding anthropomorphism and dependence as social processes rather than merely UI bugs.</t>
+  </si>
+  <si>
+    <t>HCI seminar; identity; anthropomorphism</t>
+  </si>
+  <si>
+    <t>How do AI companions reshape users' identities, expectations and social relationships?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/html/2601.12181v1</t>
+  </si>
+  <si>
+    <t>Analyzes 22,374 online discussions.</t>
+  </si>
+  <si>
+    <t>Governance of autonomous agents</t>
+  </si>
+  <si>
+    <t>Raji &amp; Bashir</t>
+  </si>
+  <si>
+    <t>Systematic review</t>
+  </si>
+  <si>
+    <t>Reviews governance priorities, mechanisms and stakeholder roles for AI systems that autonomously plan and execute tasks.</t>
+  </si>
+  <si>
+    <t>Important 2026 bridge from chatbot ethics to systems that can act in the world.</t>
+  </si>
+  <si>
+    <t>Agentic AI governance; research agenda; seminar</t>
+  </si>
+  <si>
+    <t>How should accountability change when AI can plan, call tools and execute actions autonomously?</t>
+  </si>
+  <si>
+    <t>Published Jul 2026.</t>
+  </si>
+  <si>
+    <t>Security and governance practice</t>
+  </si>
+  <si>
+    <t>State of Agentic AI Security and Governance</t>
+  </si>
+  <si>
+    <t>OWASP GenAI Security Project</t>
+  </si>
+  <si>
+    <t>Security / governance report</t>
+  </si>
+  <si>
+    <t>Practitioner standard</t>
+  </si>
+  <si>
+    <t>Covers governance and security issues for autonomous AI systems, including controls, oversight and operational risk.</t>
+  </si>
+  <si>
+    <t>Gives practitioners a deployment-oriented complement to academic governance work.</t>
+  </si>
+  <si>
+    <t>Agent security; enterprise governance; checklist design</t>
+  </si>
+  <si>
+    <t>What controls are necessary when agents receive tools, permissions and persistent access?</t>
+  </si>
+  <si>
+    <t>https://genai.owasp.org/resource/state-of-agentic-ai-security-and-governance/</t>
+  </si>
+  <si>
+    <t>Practitioner-focused resource.</t>
+  </si>
+  <si>
+    <t>AI in education ethics</t>
+  </si>
+  <si>
+    <t>AI and the future of education: Disruptions, dilemmas and directions</t>
+  </si>
+  <si>
+    <t>Policy / anthology</t>
+  </si>
+  <si>
+    <t>Official / expert collection</t>
+  </si>
+  <si>
+    <t>Explores philosophical, ethical and pedagogical dilemmas created by AI in education and human-machine co-creation.</t>
+  </si>
+  <si>
+    <t>Useful domain case study showing how general AI-ethics principles change in a real institution such as education.</t>
+  </si>
+  <si>
+    <t>Education case study; classroom discussion; policy</t>
+  </si>
+  <si>
+    <t>How should education preserve human agency, fairness and learning integrity in an AI-rich environment?</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/articles/ai-and-future-education-disruptions-dilemmas-and-directions</t>
+  </si>
+  <si>
+    <t>Published Jan 2026.</t>
+  </si>
+  <si>
+    <t>Scale, data and social harms</t>
+  </si>
+  <si>
+    <t>On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
+  </si>
+  <si>
+    <t>Bender et al.</t>
+  </si>
+  <si>
+    <t>FAccT research paper</t>
+  </si>
+  <si>
+    <t>Raises concerns about environmental cost, training-data scale, bias, documentation and the gap between linguistic form and meaning.</t>
+  </si>
+  <si>
+    <t>Foundational critical reading that explains why ethics concerns were present before today's frontier LLMs.</t>
+  </si>
+  <si>
+    <t>Historical foundation; data ethics; critical perspective</t>
+  </si>
+  <si>
+    <t>Does scaling language models without understanding data and social context create predictable harms?</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3442188.3445922</t>
+  </si>
+  <si>
+    <t>FAccT 2021; foundational.</t>
+  </si>
+  <si>
+    <t>Language-model harm taxonomy</t>
+  </si>
+  <si>
+    <t>Ethical and Social Risks of Harm from Language Models</t>
+  </si>
+  <si>
+    <t>Weidinger et al.</t>
+  </si>
+  <si>
+    <t>Risk taxonomy / research</t>
+  </si>
+  <si>
+    <t>Organizes harms around discrimination, information hazards, misinformation, malicious use, human-computer interaction and socioeconomic/environmental harms.</t>
+  </si>
+  <si>
+    <t>One of the clearest early taxonomies for turning 'LLM ethics' into categories of harm.</t>
+  </si>
+  <si>
+    <t>Foundations; risk taxonomy; related work</t>
+  </si>
+  <si>
+    <t>What types of harm can language models create, and through which pathways?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2112.04359</t>
+  </si>
+  <si>
+    <t>Published work originated from DeepMind research.</t>
+  </si>
+  <si>
+    <t>Foundation-model societal impact</t>
+  </si>
+  <si>
+    <t>On the Opportunities and Risks of Foundation Models</t>
+  </si>
+  <si>
+    <t>Bommasani et al.</t>
+  </si>
+  <si>
+    <t>Examines foundation models across capabilities, homogenization, adaptation, evaluation, robustness, security, fairness, misuse, law and societal impact.</t>
+  </si>
+  <si>
+    <t>Provides broad conceptual background for why one upstream model can propagate benefits and harms across many downstream systems.</t>
+  </si>
+  <si>
+    <t>Foundation models; societal impact; literature review</t>
+  </si>
+  <si>
+    <t>How does reliance on a small number of foundation models concentrate systemic risk?</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2108.07258</t>
+  </si>
+  <si>
+    <t>Stanford CRFM foundational report.</t>
+  </si>
+  <si>
+    <t>New This Week — Automatically Discovered</t>
+  </si>
+  <si>
+    <t>Recent high-scoring discoveries from scholarly APIs and official policy pages.</t>
+  </si>
+  <si>
+    <t>Detected</t>
+  </si>
+  <si>
+    <t>Published</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Importance Score</t>
+  </si>
+  <si>
+    <t>Why flagged</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>2026-08-16</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>A Common Standard for AI Incident Accountability</t>
+  </si>
+  <si>
+    <t>Zenodo (CERN European Organization for Nuclear Research)</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>Must Read Candidate</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, accountability, disclosure, reporting; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21907857</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21907857</t>
+  </si>
+  <si>
+    <t>Pending</t>
+  </si>
+  <si>
+    <t>Automatically discovered; verify bibliographic details before formal citation.</t>
+  </si>
+  <si>
+    <t>Autonomous Decision Assurance Layer for AI-Driven Enterprise Analytics: Bridging Governance, Multi-Agent AI, and Executive Decision Intelligence in Saudi Vision 2030 Organizations</t>
+  </si>
+  <si>
+    <t>International Journal for Research in Applied Science and Engineering Technology</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.22214/ijraset.2026.84573</t>
+  </si>
+  <si>
+    <t>10.22214/ijraset.2026.84573</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21907856</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21907856</t>
+  </si>
+  <si>
+    <t>Sustainability and Environmental Ethics in Sanskrit Texts: A Geographical Perspective</t>
+  </si>
+  <si>
+    <t>Environment &amp; Labor</t>
+  </si>
+  <si>
+    <t>Prantik Gabeshana Patrika</t>
+  </si>
+  <si>
+    <t>journal-article</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: water, environment, sustainability; strong scholarly metadata source; impact signal: framework, guidelines, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.67841/pgp.260501082</t>
+  </si>
+  <si>
+    <t>10.67841/pgp.260501082</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>Validating the Virtue Ethics Measurement Scale Within an Open Distance e-Learning Higher Education Institution in South Africa: Students’ Perspectives of Generative AI Practices</t>
+  </si>
+  <si>
+    <t>Algorithms</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3390/a19080682</t>
+  </si>
+  <si>
+    <t>10.3390/a19080682</t>
+  </si>
+  <si>
+    <t>2026-08-15</t>
+  </si>
+  <si>
+    <t>Examining the Impact of Social-Emotional Learning on Academic Achievement in African American Middle School Girls</t>
+  </si>
+  <si>
+    <t>Seton Hall University eRepository (Seton Hall University)</t>
+  </si>
+  <si>
+    <t>dissertation</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://openalex.org/W7160680247</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>Managing ESG and cyber risks in Kazakhstan’s low-carbon transition by aligning EU and Chinese standards through demoethics</t>
+  </si>
+  <si>
+    <t>Discover Sustainability</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, sustainability; impact signal: framework, standard, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s43621-026-04260-z</t>
+  </si>
+  <si>
+    <t>10.1007/s43621-026-04260-z</t>
+  </si>
+  <si>
+    <t>A Framework for Protecting Students Privacy in Online and Offline Digital Footprints</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL JOURNAL OF COMPUTER SCIENCE AND MATHEMATICAL THEORY E-ISSN</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
+  </si>
+  <si>
+    <t>10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
+  </si>
+  <si>
+    <t>A Review of the TITAN Guideline: Advancing Transparency and Responsible Artificial Intelligence Use in Medical Research and Scholarly Publishing</t>
+  </si>
+  <si>
+    <t>Electronic Journal of Medical Research</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, accountability, reporting; impact signal: framework, guidelines, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.64813/ejmr.2026.126</t>
+  </si>
+  <si>
+    <t>10.64813/ejmr.2026.126</t>
+  </si>
+  <si>
+    <t>Digital personas of AI use in nursing education: a latent class analysis of learning behaviors and academic engagement</t>
+  </si>
+  <si>
+    <t>Frontiers in Medicine</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fmed.2026.1859093</t>
+  </si>
+  <si>
+    <t>10.3389/fmed.2026.1859093</t>
+  </si>
+  <si>
+    <t>Brazil's ENAMED and the Governance of AI-Supported Exam Preparation: A Conceptual Policy Analysis</t>
+  </si>
+  <si>
+    <t>International Journal For Multidisciplinary Research</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: standard, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.36948/ijfmr.2026.v08i04.84125</t>
+  </si>
+  <si>
+    <t>10.36948/ijfmr.2026.v08i04.84125</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>Beyond Visual Evidence: Revealing and Mitigating Relational Privacy Leakage in Document MLLMs</t>
+  </si>
+  <si>
+    <t>arXiv</t>
+  </si>
+  <si>
+    <t>matches Privacy: privacy, leakage, extraction; impact signal: benchmark, framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12911v1</t>
+  </si>
+  <si>
+    <t>10.1145/3767308.3835901</t>
+  </si>
+  <si>
+    <t>Digital Transformation of the Indonesian Public Sector: A Systematic Review of Governance, Audit, and Service Innovation</t>
+  </si>
+  <si>
+    <t>F1000Research</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: systematic review, framework, guidelines; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.12688/f1000research.188727.1</t>
+  </si>
+  <si>
+    <t>10.12688/f1000research.188727.1</t>
+  </si>
+  <si>
+    <t>Performance, interaction, and ethical evaluation in the use of generative artificial intelligence in engineering education</t>
+  </si>
+  <si>
+    <t>Education and Information Technologies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, regulation, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10639-026-14112-y</t>
+  </si>
+  <si>
+    <t>10.1007/s10639-026-14112-y</t>
+  </si>
+  <si>
+    <t>Exploring student use of generative AI in higher education: A dual-institutional study</t>
+  </si>
+  <si>
+    <t>book-chapter</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s10639-026-14100-2</t>
+  </si>
+  <si>
+    <t>10.1007/s10639-026-14100-2</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>How Personal and Cognitive Traits Influence AI Attitudes, Ethics, and Well-being: The Role of AI Autonomy and Criticality in Design</t>
+  </si>
+  <si>
+    <t>SN Computer Science</t>
+  </si>
+  <si>
+    <t>matches Persuasion &amp; Manipulation: influence, autonomy; impact signal: survey, framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s42979-026-05214-y</t>
+  </si>
+  <si>
+    <t>10.1007/s42979-026-05214-y</t>
+  </si>
+  <si>
+    <t>Ethics Suppression in AI Development: A Comparative Case Study of Responsible AI Under Competitive Pressure</t>
+  </si>
+  <si>
+    <t>International Journal of Applied Research in Business and Management</t>
+  </si>
+  <si>
+    <t>matches Foundations: ethics, responsible ai; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51137/wrp.ijarbm.869</t>
+  </si>
+  <si>
+    <t>10.51137/wrp.ijarbm.869</t>
+  </si>
+  <si>
+    <t>Generative AI in African Higher Education: A Systematic Review of Opportunities, Ethical Challenges, and Institutional Readiness</t>
+  </si>
+  <si>
+    <t>Journal of University Teaching and Learning Practice</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.53761/c682ye61</t>
+  </si>
+  <si>
+    <t>10.53761/c682ye61</t>
+  </si>
+  <si>
+    <t>Which LLM Is Your Ideal Companion? Evaluating Emotional Companion Capabilities of LLMs Based on Adult Attachment Theory</t>
+  </si>
+  <si>
+    <t>matches Human-AI Relationships: companion, emotional support, attachment; impact signal: benchmark, evaluation; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13168v1</t>
+  </si>
+  <si>
+    <t>InFactPlanner: Planning Sustainable Geo-Distributed LLM Data Centers</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, carbon, sustainability; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12915v1</t>
+  </si>
+  <si>
+    <t>Legitimacy Criteria for Strategic Communication in the Age of Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>The Proceedings of the World Conference on Social Sciences and Humanities.</t>
+  </si>
+  <si>
+    <t>conference-paper</t>
+  </si>
+  <si>
+    <t>matches Persuasion &amp; Manipulation: persuasion, manipulation, influence, behavioral influence; impact signal: framework, regulation, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.33422/shconf.v3i1.2047</t>
+  </si>
+  <si>
+    <t>10.33422/shconf.v3i1.2047</t>
+  </si>
+  <si>
+    <t>A carbon aware job scheduling framework for data center sustainability using deep learning training</t>
+  </si>
+  <si>
+    <t>Discover Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, environment, sustainability; strong scholarly metadata source; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s44163-026-02022-4</t>
+  </si>
+  <si>
+    <t>10.1007/s44163-026-02022-4</t>
+  </si>
+  <si>
+    <t>How electoral management bodies govern digital electoral systems: capacity, authority, and accountability</t>
+  </si>
+  <si>
+    <t>Frontiers in Political Science</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: systematic review, framework, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpos.2026.1877569</t>
+  </si>
+  <si>
+    <t>10.3389/fpos.2026.1877569</t>
+  </si>
+  <si>
+    <t>Leveraging strategic facilities management to achieve corporate ESG and sustainability: a literature review</t>
+  </si>
+  <si>
+    <t>Frontiers in Environmental Economics</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: environment, sustainability; impact signal: framework, governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/frevc.2026.1839120</t>
+  </si>
+  <si>
+    <t>10.3389/frevc.2026.1839120</t>
+  </si>
+  <si>
+    <t>Effect of Artificial Intelligence (AI) Study Tools on the Study Behaviour of Pharmacology and Medical Students in Bauchi State, Nigeria</t>
+  </si>
+  <si>
+    <t>WORLD JOURNAL OF INNOVATION AND MODERN TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, guidelines, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.56201/wjimt.v10.no7.2026.pg351.366</t>
+  </si>
+  <si>
+    <t>10.56201/wjimt.v10.no7.2026.pg351.366</t>
+  </si>
+  <si>
+    <t>Analysis of PAI Students' Readiness for the Integration of Artificial Intelligence in Learning at Ahmad Dahlan University</t>
+  </si>
+  <si>
+    <t>EDUSOSHUM Journal of Islamic Education and Social Humanities</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.52366/edusoshum.v6i3.550</t>
+  </si>
+  <si>
+    <t>10.52366/edusoshum.v6i3.550</t>
+  </si>
+  <si>
+    <t>Beyond the Device: Reforming Higher Education and Teacher Education Curricula from ICT Literacy to AI Pedagogical Readiness in East Africa</t>
+  </si>
+  <si>
+    <t>East African Journal of Education Studies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.37284/eajes.9.3.5567</t>
+  </si>
+  <si>
+    <t>10.37284/eajes.9.3.5567</t>
+  </si>
+  <si>
+    <t>Acceptance of Generative AI for Supporting Innovative Learning in Vocational Education</t>
+  </si>
+  <si>
+    <t>World Journal of Education</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: survey, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5430/wje.v16n3p30</t>
+  </si>
+  <si>
+    <t>10.5430/wje.v16n3p30</t>
+  </si>
+  <si>
+    <t>Benchmarking Knowledge-Extraction Attack and Defense on Retrieval-Augmented Generation (RAG)</t>
+  </si>
+  <si>
+    <t>OpenAlex</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>matches Privacy: privacy, extraction; impact signal: benchmark, framework, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3770855.3817524</t>
+  </si>
+  <si>
+    <t>10.1145/3770855.3817524</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>Governing Agentic AI in FinTech</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11344v2</t>
+  </si>
+  <si>
+    <t>Toward Meaningful Transparency for AI Chatbots: Disclosing Persuasive Intent Reduces Persuasion</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, disclosure, provenance; impact signal: regulation, policy, randomized; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11794v1</t>
+  </si>
+  <si>
+    <t>Research on the Judicial Fairness Challenges and Legal Regulation of AI-Assisted Judgments in the Context of Digital Justice</t>
+  </si>
+  <si>
+    <t>Advanced Electromagnetics</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.7716/aem.v15i3.3403</t>
+  </si>
+  <si>
+    <t>10.7716/aem.v15i3.3403</t>
+  </si>
+  <si>
+    <t>The Correlation Between Exposure to English-Language Content on Instagram and Listening Comprehension among EFL Students at UIN Datokarama Palu</t>
+  </si>
+  <si>
+    <t>Journal of General Education and Humanities</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.58421/gehu.v5i4.1936</t>
+  </si>
+  <si>
+    <t>10.58421/gehu.v5i4.1936</t>
+  </si>
+  <si>
+    <t>Motivation to learn and teach home economics in higher education: Predictors and comparative analysis</t>
+  </si>
+  <si>
+    <t>Social Sciences &amp; Humanities Open</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ssaho.2026.103414</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssaho.2026.103414</t>
+  </si>
+  <si>
+    <t>The Impact of Artificial Intelligence on English Language Learning, Communication, and Linguistic Development: Opportunities and Challenges</t>
+  </si>
+  <si>
+    <t>Journal of Intelligent Decision Making and Information Science</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.59543/jidmis.v3.1938</t>
+  </si>
+  <si>
+    <t>10.59543/jidmis.v3.1938</t>
+  </si>
+  <si>
+    <t>AI literacy and subject specialization in pre-service teacher education: a mixed-methods study of dimensional profiles and perceived pedagogical challenges</t>
+  </si>
+  <si>
+    <t>Frontiers in Education</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1876627</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1876627</t>
+  </si>
+  <si>
+    <t>Development and pilot testing of multi-stakeholder questionnaires for assessing University 4.0 transformation in higher education institutions</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; impact signal: governance, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1908552</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1908552</t>
+  </si>
+  <si>
+    <t>PENGARUH MUSIK AI TERHADAP PENINGKATAN MOTIVASI BELAJAR SISWA PADA MATA PELAJARAN IPS DI KELAS IV SD NEGERI 73 AMBON</t>
+  </si>
+  <si>
+    <t>SOCIAL : Jurnal Inovasi Pendidikan IPS</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51878/social.v6i3.14523</t>
+  </si>
+  <si>
+    <t>10.51878/social.v6i3.14523</t>
+  </si>
+  <si>
+    <t>2026-09-01</t>
+  </si>
+  <si>
+    <t>Physical Processing of Aquatic Gel Foods: From Protein Structure Regulation to Health, Sustainability, and Personalized Design</t>
+  </si>
+  <si>
+    <t>Comprehensive Reviews in Food Science and Food Safety</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, sustainability; strong scholarly metadata source; impact signal: regulation, standard, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/1541-4337.70601</t>
+  </si>
+  <si>
+    <t>10.1111/1541-4337.70601</t>
+  </si>
+  <si>
+    <t>2026-08-08</t>
+  </si>
+  <si>
+    <t>ChatGPT and Large Language Models in Contemporary Nursing</t>
+  </si>
+  <si>
+    <t>Journal of Clinical Nursing</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1111/jocn.70490</t>
+  </si>
+  <si>
+    <t>10.1111/jocn.70490</t>
+  </si>
+  <si>
+    <t>Software Engineering for and with GUI Agent</t>
+  </si>
+  <si>
+    <t>arXiv (Cornell University)</t>
+  </si>
+  <si>
+    <t>preprint</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, evaluation, audit; impact signal: benchmark, framework, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arxiv.2608.09278</t>
+  </si>
+  <si>
+    <t>10.48550/arxiv.2608.09278</t>
+  </si>
+  <si>
+    <t>Banking Performance under the Lens of Earnings Management: A Theoretical and Bibliometric Systematic Review</t>
+  </si>
+  <si>
+    <t>Bulletin of Social Studies and Community Development</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: transparency, disclosure, reporting; impact signal: systematic review, framework, guidelines; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.61436/bsscd/v5i3.pp253-267</t>
+  </si>
+  <si>
+    <t>10.61436/bsscd/v5i3.pp253-267</t>
+  </si>
+  <si>
+    <t>Pedagogical prompting rather than technical mastery: Generative AI use by English and English-medium instruction teachers</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1901680</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1901680</t>
+  </si>
+  <si>
+    <t>Applied and Filtered: An End-to-End Algorithmic Fairness Audit of A Public Employment Agency</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: evaluation, audit; impact signal: evaluation, audit; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13022v1</t>
+  </si>
+  <si>
+    <t>Pre-service teachers' general pedagogical knowledge and pedagogical learning opportunities at entry into induction: comparing traditional and alternative teacher education programs</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: standard, longitudinal; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1790135</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1790135</t>
+  </si>
+  <si>
+    <t>Policy Integration and Implementation Gaps in China’s Dual-Carbon Strategy: A Multi-Dimensional Analysis of Carbon Trading System, New Energy Vehicle Incentives, and Air Quality Policies</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon; impact signal: policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.59543/jidmis.v3.1782</t>
+  </si>
+  <si>
+    <t>10.59543/jidmis.v3.1782</t>
+  </si>
+  <si>
+    <t>Dysfunction of Zakat Village Governance in Papua: Fragmentation of Collaboration and Inequality of Amil Capacity</t>
+  </si>
+  <si>
+    <t>JURNAL ILMIAH GEMA PERENCANA</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, evaluation; strong scholarly metadata source; impact signal: framework, regulation, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.61860/jigp.v5i1.411</t>
+  </si>
+  <si>
+    <t>10.61860/jigp.v5i1.411</t>
+  </si>
+  <si>
+    <t>Human-centric AI governance in the European Union. Accountability, fundamental rights, and institutional resilience in public administration</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/fpos.2026.1928481</t>
+  </si>
+  <si>
+    <t>10.3389/fpos.2026.1928481</t>
+  </si>
+  <si>
+    <t>Delivering building demand flexibility for grid-interactive operation: from perception and cognition to decision, execution, and verification</t>
+  </si>
+  <si>
+    <t>Applied Energy</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon; impact signal: framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.apenergy.2026.128668</t>
+  </si>
+  <si>
+    <t>10.1016/j.apenergy.2026.128668</t>
+  </si>
+  <si>
+    <t>PENGARUH MODEL PEMBELAJARAN PROJECT BASED LEARNING DAN KEDISIPLINAN BELAJAR TERHADAP KESIAPAN KERJA SISWA PADA JURUSAN AKUNTANSI KEUANGAN LEMABAGA DI SMK NEGERI 1 PANGKEP</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; impact signal: survey; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51878/social.v6i3.14617</t>
+  </si>
+  <si>
+    <t>10.51878/social.v6i3.14617</t>
+  </si>
+  <si>
+    <t>Large Language Model-facilitated national review on the use of ecological tools and processes in Environmental Impact Statements (EIS) in the U.S. with demonstrated use cases for environmental planners, legal practitioners, and researchers</t>
+  </si>
+  <si>
+    <t>Springer Science and Business Media LLC</t>
+  </si>
+  <si>
+    <t>posted-content</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, environment, labor; strong scholarly metadata source; impact signal: benchmark, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.21203/rs.3.rs-10627892/v1</t>
+  </si>
+  <si>
+    <t>10.21203/rs.3.rs-10627892/v1</t>
+  </si>
+  <si>
+    <t>Optimization of Household Equipment and Instrumentation in an Effort to Save Electrical Energy in a Restaurant</t>
+  </si>
+  <si>
+    <t>International Journal Of Community Service</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, carbon, environment; strong scholarly metadata source; impact signal: survey, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.51601/ijcs.v6i3.1022</t>
+  </si>
+  <si>
+    <t>10.51601/ijcs.v6i3.1022</t>
+  </si>
+  <si>
+    <t>Effect of Public Safety Center Video-Based Education on Emergency Response Attitudes Among High School Students</t>
+  </si>
+  <si>
+    <t>Jurnal Kegawatdaruratan Medis Indonesia</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.58545/jkmi.v5i2.827</t>
+  </si>
+  <si>
+    <t>10.58545/jkmi.v5i2.827</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>From Single Chatbots to Governed Agent Ecosystems: An Agentic AI Pattern Catalogue and Orchestration Framework for Mission-Critical Hospital Information Management Systems</t>
+  </si>
+  <si>
+    <t>matches Agentic AI: agentic ai, autonomous agent, multi-agent; impact signal: framework, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.07627v1</t>
+  </si>
+  <si>
+    <t>10.38124/ijisrt/26jul830</t>
+  </si>
+  <si>
+    <t>Bias Smells in AI Software Development: Recognizing Potential Sources of Fairness Debt</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.48550/arxiv.2608.10248</t>
+  </si>
+  <si>
+    <t>10.48550/arxiv.2608.10248</t>
+  </si>
+  <si>
+    <t>Quantifying the Relationship Between Clinical Safety and Environmental Impact in Therapeutic LLMs</t>
+  </si>
+  <si>
+    <t>matches Environment &amp; Labor: energy, water, carbon, environment; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11830v1</t>
+  </si>
+  <si>
+    <t>Benchmark-Based Comparative Assessment of Publicly Benchmarked Indian Foundation Models: A Capability and Evaluation-Maturity Framework</t>
+  </si>
+  <si>
+    <t>matches India &amp; Global South: multilingual, india; impact signal: survey, benchmark, framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.11891v1</t>
+  </si>
+  <si>
+    <t>Academic League of Artificial Intelligence - An Integrative Perspective of Teaching, Research, and Extension</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.13447v1</t>
+  </si>
+  <si>
+    <t>Educational Aspirations in Contemporary Indian Education: A Critical Conceptual Synthesis for Holistic Learner Development</t>
+  </si>
+  <si>
+    <t>Asian Journal of Education and Social Studies</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: policy, longitudinal; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.9734/ajess/2026/v52i83261</t>
+  </si>
+  <si>
+    <t>10.9734/ajess/2026/v52i83261</t>
+  </si>
+  <si>
+    <t>Solar Exposure and Photoprotection Behaviors as Determinants of Acne Vulgaris Severity Among University Students in Andalusia-Spain</t>
+  </si>
+  <si>
+    <t>Ibn Sina Journal of Medical Science Health &amp; Pharmacy</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student; impact signal: survey, framework, evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.64440/ibnsina/sina0027</t>
+  </si>
+  <si>
+    <t>10.64440/ibnsina/sina0027</t>
+  </si>
+  <si>
+    <t>FSGR: Mitigating Token Frequency Bias for Fair SID-Based Generative Recommendation</t>
+  </si>
+  <si>
+    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework; recent</t>
+  </si>
+  <si>
+    <t>http://arxiv.org/abs/2608.12845v1</t>
+  </si>
+  <si>
+    <t>HEPE — Complete 16-State AI Governance Space with Lyapunov Values (Hardware-Enforced Policy Engine)</t>
+  </si>
+  <si>
+    <t>matches Governance &amp; Measurement: governance, audit; impact signal: policy, governance, audit; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5281/zenodo.21935563</t>
+  </si>
+  <si>
+    <t>10.5281/zenodo.21935563</t>
+  </si>
+  <si>
+    <t>What Remains Ours to Think? Reclaiming Critical Thinking in AI‐Augmented Student Leadership Education</t>
+  </si>
+  <si>
+    <t>New Directions for Student Leadership</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1002/yd.70068</t>
+  </si>
+  <si>
+    <t>10.1002/yd.70068</t>
+  </si>
+  <si>
+    <t>Supervision in educational leadership: practices, challenges, and innovations in the UAE — a multi-level coupling analysis of the current and future</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, learning; impact signal: benchmark, policy, governance; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feduc.2026.1862260</t>
+  </si>
+  <si>
+    <t>10.3389/feduc.2026.1862260</t>
+  </si>
+  <si>
+    <t>Research ethics and publication policies in journals using the Korea Institute of Science and Technology Information (KISTI) academic publishing platform: a content analysis of 181 journals</t>
+  </si>
+  <si>
+    <t>Science Editing</t>
+  </si>
+  <si>
+    <t>matches Transparency &amp; Accountability: accountability, disclosure; impact signal: guidelines, standard, policy; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.6087/kcse.403</t>
+  </si>
+  <si>
+    <t>10.6087/kcse.403</t>
+  </si>
+  <si>
+    <t>Striking a Balance between the Right to Privacy and Freedom of Expression: A Case Study of Women’s Digital Rights in Tanzania</t>
+  </si>
+  <si>
+    <t>East African Journal of Law and Ethics</t>
+  </si>
+  <si>
+    <t>matches Regulation: regulation, legal framework, standard; impact signal: framework, regulation, standard; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.37284/eajle.9.3.5557</t>
+  </si>
+  <si>
+    <t>10.37284/eajle.9.3.5557</t>
+  </si>
+  <si>
+    <t>Evaluation of the CIPP Model in a Project-Based Basic Electronics Course: A Discriminant Validity and Common Method Bias Analysis</t>
+  </si>
+  <si>
+    <t>Educative: Jurnal Ilmiah Pendidikan</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: evaluation; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.70437/educative.v4i2.2180</t>
+  </si>
+  <si>
+    <t>10.70437/educative.v4i2.2180</t>
+  </si>
+  <si>
+    <t>The effectiveness of the contextual teaching and learning model on mathematical literacy skills in terms of learning motivation</t>
+  </si>
+  <si>
+    <t>Union: Jurnal Ilmiah Pendidikan Matematika</t>
+  </si>
+  <si>
+    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; recent</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.30738/union.v14i2.22911</t>
+  </si>
+  <si>
+    <t>10.30738/union.v14i2.22911</t>
+  </si>
+  <si>
+    <t>Review Queue — Human-in-the-loop Curation</t>
+  </si>
+  <si>
+    <t>Promote only sources that are genuinely useful. Automatic discovery is intentionally not identical to automatic curation.</t>
+  </si>
+  <si>
+    <t>Topic Map — What to Read for Each AI / LLM Ethics Question</t>
+  </si>
+  <si>
+    <t>Theme-level map generated from the current curated library.</t>
+  </si>
+  <si>
+    <t>Sources in library</t>
+  </si>
+  <si>
+    <t>2026-heavy?</t>
+  </si>
+  <si>
+    <t>Start with</t>
+  </si>
+  <si>
+    <t>Then read</t>
+  </si>
+  <si>
+    <t>Typical reader question</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Recommendation on the Ethics of Artificial Intelligence; On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1); Guidelines for providers of general-purpose AI models</t>
+  </si>
+  <si>
+    <t>An Evaluation of AI Companion Apps; Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
+  </si>
+  <si>
+    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders; Evaluating Language Models for Harmful Manipulation</t>
+  </si>
+  <si>
+    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory; SoK: The Privacy Paradox of Large Language Models</t>
+  </si>
+  <si>
+    <t>2026-Only View</t>
+  </si>
+  <si>
+    <t>Current-year curated items.</t>
+  </si>
+  <si>
+    <t>Policy, Governance &amp; Regulation</t>
+  </si>
+  <si>
+    <t>Curated governance, standards, transparency, law and human-rights sources.</t>
+  </si>
+  <si>
+    <t>Source Configuration</t>
+  </si>
+  <si>
+    <t>Edit config/sources.yaml in the repository to change the automation. This sheet is a readable mirror.</t>
+  </si>
+  <si>
+    <t>Endpoint / URL</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>Authority</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>https://export.arxiv.org/api/query</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Fresh preprints</t>
+  </si>
+  <si>
+    <t>3-second delay between repeated calls</t>
+  </si>
+  <si>
+    <t>https://api.openalex.org/works</t>
+  </si>
+  <si>
+    <t>Broad scholarly discovery</t>
+  </si>
+  <si>
+    <t>OPENALEX_API_KEY optional</t>
+  </si>
+  <si>
+    <t>Crossref</t>
+  </si>
+  <si>
+    <t>https://api.crossref.org/works</t>
+  </si>
+  <si>
+    <t>Published DOI metadata</t>
+  </si>
+  <si>
+    <t>CONTACT_EMAIL recommended</t>
+  </si>
+  <si>
+    <t>NIST Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Official page watch</t>
+  </si>
+  <si>
+    <t>https://www.nist.gov/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>Policy/news link discovery</t>
+  </si>
+  <si>
+    <t>First scan bootstraps without flooding</t>
+  </si>
+  <si>
+    <t>European Commission AI Act</t>
+  </si>
+  <si>
+    <t>OECD.AI Wonk</t>
+  </si>
+  <si>
+    <t>https://oecd.ai/en/wonk</t>
+  </si>
+  <si>
+    <t>UNESCO Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>https://www.unesco.org/en/artificial-intelligence</t>
+  </si>
+  <si>
+    <t>IndiaAI / MeitY — PIB Releases</t>
+  </si>
+  <si>
+    <t>https://www.pib.gov.in/AllRelease.aspx?MenuId=30&amp;lang=1&amp;reg=3</t>
+  </si>
+  <si>
+    <t>Automation Update Log</t>
+  </si>
+  <si>
+    <t>Every run records discovery and deduplication counts.</t>
+  </si>
+  <si>
+    <t>New This Week</t>
+  </si>
+  <si>
+    <t>Review Queue</t>
+  </si>
+  <si>
+    <t>Auto-promoted</t>
+  </si>
+  <si>
+    <t>2026-08-16T12:18:00+05:30</t>
+  </si>
+  <si>
+    <t>Initial build</t>
+  </si>
+  <si>
+    <t>Living tracker package initialized</t>
+  </si>
+  <si>
+    <t>2026-08-16T07:19:28+00:00</t>
+  </si>
+  <si>
+    <t>Policy/IndiaAI Safe &amp; Trusted AI: HTTPError: 403 Client Error: Forbidden for url: https://indiaai.gov.in/hub/safe-trusted-ai</t>
+  </si>
+  <si>
+    <t>2026-08-16T07:39:54+00:00</t>
+  </si>
+  <si>
+    <t>2026-08-16T10:42:00+00:00</t>
+  </si>
+  <si>
     <t>2026-08-16T10:48:23+00:00</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>scheduled/manual</t>
-  </si>
-  <si>
-    <t>Sources checked</t>
-  </si>
-  <si>
-    <t>Candidates fetched</t>
-  </si>
-  <si>
-    <t>New after dedupe</t>
-  </si>
-  <si>
-    <t>Errors / notes</t>
-  </si>
-  <si>
-    <t>Completed without recorded source errors</t>
-  </si>
-  <si>
-    <t>Start Here — 2026-aware AI &amp; LLM Ethics Reading Path</t>
-  </si>
-  <si>
-    <t>Use this sheet for a compact orientation. The automated discovery tabs are intentionally separate from the stable reading path.</t>
-  </si>
-  <si>
-    <t>Curated sources</t>
-  </si>
-  <si>
-    <t>2026 sources</t>
-  </si>
-  <si>
-    <t>Must Read</t>
-  </si>
-  <si>
-    <t>Official / institutional</t>
-  </si>
-  <si>
-    <t>Recommended 10-source reading path</t>
-  </si>
-  <si>
-    <t>Step</t>
-  </si>
-  <si>
-    <t>Read this</t>
-  </si>
-  <si>
-    <t>Year</t>
-  </si>
-  <si>
-    <t>Why now</t>
-  </si>
-  <si>
-    <t>Priority</t>
-  </si>
-  <si>
-    <t>Source URL</t>
-  </si>
-  <si>
-    <t>Responsible AI | The 2026 AI Index Report</t>
-  </si>
-  <si>
-    <t>Current 2025–2026 evidence or governance update</t>
-  </si>
-  <si>
-    <t>https://hai.stanford.edu/ai-index/2026-ai-index-report/responsible-ai</t>
-  </si>
-  <si>
-    <t>AI Act | Shaping Europe's digital future</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/regulatory-framework-ai</t>
-  </si>
-  <si>
-    <t>Guidelines on transparency obligations for providers and deployers of AI systems</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-transparency-ai-generated-content</t>
-  </si>
-  <si>
-    <t>Persuasion with Large Language Models: A Survey of Empirical Studies</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2411.06837v2</t>
-  </si>
-  <si>
-    <t>Emotional Support with Conversational AI: Talking to Machines About Life</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2603.22618v1</t>
-  </si>
-  <si>
-    <t>An Evaluation of AI Companion Apps</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2605.08093v2</t>
-  </si>
-  <si>
-    <t>Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2606.04150</t>
-  </si>
-  <si>
-    <t>Towards Agentic AI Governance: A Preliminary Assessment</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2607.07612</t>
-  </si>
-  <si>
-    <t>The 2025 Foundation Model Transparency Index</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2512.10169</t>
-  </si>
-  <si>
-    <t>India AI Governance Guidelines: Empowering Ethical and Responsible AI</t>
-  </si>
-  <si>
-    <t>https://indiaai.gov.in/article/india-ai-governance-guidelines-empowering-ethical-and-responsible-ai</t>
-  </si>
-  <si>
-    <t>Ethics of Artificial Intelligence &amp; LLMs — Curated Reading Library</t>
-  </si>
-  <si>
-    <t>Stable curated sources. Automatically discovered items are triaged separately before promotion.</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Subtopic</t>
-  </si>
-  <si>
-    <t>Title</t>
-  </si>
-  <si>
-    <t>Author / Body</t>
-  </si>
-  <si>
-    <t>Source Type</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>What it covers</t>
-  </si>
-  <si>
-    <t>Why the reader benefits</t>
-  </si>
-  <si>
-    <t>Best use</t>
-  </si>
-  <si>
-    <t>2026 Relevance Score</t>
-  </si>
-  <si>
-    <t>Read Priority</t>
-  </si>
-  <si>
-    <t>Region / Scope</t>
-  </si>
-  <si>
-    <t>Key ethical question</t>
-  </si>
-  <si>
-    <t>Notes / status</t>
-  </si>
-  <si>
-    <t>Reader mode</t>
-  </si>
-  <si>
-    <t>Responsible AI state of the field</t>
-  </si>
-  <si>
-    <t>Stanford HAI / AI Index</t>
-  </si>
-  <si>
-    <t>Annual evidence report</t>
-  </si>
-  <si>
-    <t>Institutional / data-driven</t>
-  </si>
-  <si>
-    <t>Tracks AI incidents, safety evaluation, transparency, responsible-AI reporting, and the widening gap between capability and governance.</t>
-  </si>
-  <si>
-    <t>Best current snapshot for showing that AI capability is advancing faster than safety measurement and transparency.</t>
-  </si>
-  <si>
-    <t>Lecture opener; literature review motivation; 2026 statistics</t>
-  </si>
-  <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t>Are current evaluation and governance systems keeping pace with frontier AI capability?</t>
-  </si>
-  <si>
-    <t>2026 edition; strong source for current facts and figures.</t>
-  </si>
-  <si>
-    <t>Read closely</t>
-  </si>
-  <si>
-    <t>Foundation model transparency</t>
-  </si>
-  <si>
-    <t>Wan et al. / Stanford CRFM</t>
-  </si>
-  <si>
-    <t>Research report / index</t>
-  </si>
-  <si>
-    <t>Research report</t>
-  </si>
-  <si>
-    <t>Scores major foundation-model developers on disclosures covering data, compute, risk mitigation, usage and downstream impacts.</t>
-  </si>
-  <si>
-    <t>Lets readers move from vague calls for transparency to measurable disclosure dimensions and compare developers.</t>
-  </si>
-  <si>
-    <t>Transparency section; accountability case study; assignment</t>
-  </si>
-  <si>
-    <t>Global / industry</t>
-  </si>
-  <si>
-    <t>What information should frontier-model developers be required to disclose?</t>
-  </si>
-  <si>
-    <t>Average score fell from 58/100 in 2024 to 40/100 in 2025.</t>
-  </si>
-  <si>
-    <t>EU AI Act implementation</t>
-  </si>
-  <si>
-    <t>European Commission</t>
-  </si>
-  <si>
-    <t>Regulation / official guidance</t>
-  </si>
-  <si>
-    <t>Official</t>
-  </si>
-  <si>
-    <t>Official overview of the EU AI Act, risk-based obligations, implementation timeline, GPAI rules and transparency requirements.</t>
-  </si>
-  <si>
-    <t>Provides the clearest bridge between ethics principles and enforceable legal duties in 2026.</t>
-  </si>
-  <si>
-    <t>Regulation module; compliance discussion; policy comparison</t>
-  </si>
-  <si>
-    <t>European Union</t>
-  </si>
-  <si>
-    <t>When should ethical expectations become legal obligations?</t>
-  </si>
-  <si>
-    <t>General application date: 2 August 2026, with exceptions and phased provisions.</t>
-  </si>
-  <si>
-    <t>AI-generated content disclosure</t>
-  </si>
-  <si>
-    <t>Regulatory guidance</t>
-  </si>
-  <si>
-    <t>Explains Article 50 duties concerning user disclosure, machine-readable marking, AI-generated content and deepfakes.</t>
-  </si>
-  <si>
-    <t>Useful concrete example of how transparency ethics becomes a product-design requirement.</t>
-  </si>
-  <si>
-    <t>Deepfakes; disclosure; generative-AI product design</t>
-  </si>
-  <si>
-    <t>Should people always know when they are interacting with AI or seeing AI-generated content?</t>
-  </si>
-  <si>
-    <t>Article 50 applies from 2 August 2026.</t>
-  </si>
-  <si>
-    <t>General-purpose AI obligations</t>
-  </si>
-  <si>
-    <t>Guidelines for providers of general-purpose AI models</t>
-  </si>
-  <si>
-    <t>Clarifies obligations for providers of general-purpose AI models and the Commission's enforcement role.</t>
-  </si>
-  <si>
-    <t>Gives readers a current compliance perspective on frontier and general-purpose models rather than generic AI regulation.</t>
-  </si>
-  <si>
-    <t>GPAI governance; provider responsibilities; seminar discussion</t>
-  </si>
-  <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>What extra duties should apply to powerful general-purpose models?</t>
-  </si>
-  <si>
-    <t>https://digital-strategy.ec.europa.eu/en/policies/guidelines-gpai-providers</t>
-  </si>
-  <si>
-    <t>Commission enforcement powers apply from 2 August 2026.</t>
-  </si>
-  <si>
-    <t>Read/skim</t>
-  </si>
-  <si>
-    <t>India AI governance</t>
-  </si>
-  <si>
-    <t>IndiaAI / MeitY</t>
-  </si>
-  <si>
-    <t>National governance guidance</t>
-  </si>
-  <si>
-    <t>Sets out principles and recommendations around fairness, accountability, safety, inclusivity and trustworthy AI in India.</t>
-  </si>
-  <si>
-    <t>Adds an India-specific governance perspective and prevents the reading list from being US/EU-centric.</t>
-  </si>
-  <si>
-    <t>India case study; policy comparison; local context</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>How should responsible AI governance reflect India's scale, diversity and public-interest priorities?</t>
-  </si>
-  <si>
-    <t>Released 5 Nov 2025 under the IndiaAI Mission.</t>
-  </si>
-  <si>
-    <t>AI safety capacity</t>
-  </si>
-  <si>
-    <t>Safe &amp; Trusted AI Working Group</t>
-  </si>
-  <si>
-    <t>India AI Impact Summit</t>
-  </si>
-  <si>
-    <t>Policy / working-group output</t>
-  </si>
-  <si>
-    <t>Focuses on AI safety capacity, evaluation, governance and incorporating Global South perspectives into international AI safety frameworks.</t>
-  </si>
-  <si>
-    <t>Useful for understanding how safety debates are being localized beyond US/EU institutions.</t>
-  </si>
-  <si>
-    <t>India 2026 update; global governance; discussion prompt</t>
-  </si>
-  <si>
-    <t>India / Global South</t>
-  </si>
-  <si>
-    <t>Who gets to define acceptable AI risk and safety standards globally?</t>
-  </si>
-  <si>
-    <t>https://impact.indiaai.gov.in/working-groups/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>2026-relevant IndiaAI Impact Summit initiative.</t>
-  </si>
-  <si>
-    <t>Risk management framework</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1)</t>
-  </si>
-  <si>
-    <t>NIST</t>
-  </si>
-  <si>
-    <t>Risk-management framework</t>
-  </si>
-  <si>
-    <t>Identifies GenAI-specific risks and actions across the AI lifecycle, aligned with Govern, Map, Measure and Manage.</t>
-  </si>
-  <si>
-    <t>One of the most practical sources for converting ethical concerns into operational risk controls.</t>
-  </si>
-  <si>
-    <t>Risk register; deployment checklist; governance design</t>
-  </si>
-  <si>
-    <t>United States / cross-sector</t>
-  </si>
-  <si>
-    <t>How can an organization operationalize trustworthy GenAI rather than merely state principles?</t>
-  </si>
-  <si>
-    <t>https://www.nist.gov/publications/artificial-intelligence-risk-management-framework-generative-artificial-intelligence</t>
-  </si>
-  <si>
-    <t>Companion to NIST AI RMF 1.0.</t>
-  </si>
-  <si>
-    <t>Human-rights-centered AI ethics</t>
-  </si>
-  <si>
-    <t>Recommendation on the Ethics of Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>UNESCO</t>
-  </si>
-  <si>
-    <t>International ethics standard</t>
-  </si>
-  <si>
-    <t>Defines principles including proportionality, do-no-harm, safety, privacy, fairness, transparency, accountability, sustainability and human oversight.</t>
-  </si>
-  <si>
-    <t>Provides a normative foundation for almost every later AI ethics topic.</t>
-  </si>
-  <si>
-    <t>Foundations lecture; ethics framework; compare policies</t>
-  </si>
-  <si>
-    <t>What values should guide the design and deployment of AI systems?</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/artificial-intelligence/recommendation-ethics</t>
-  </si>
-  <si>
-    <t>Global UNESCO recommendation; remains foundational in 2026.</t>
-  </si>
-  <si>
-    <t>Trustworthy AI principles</t>
-  </si>
-  <si>
-    <t>OECD AI Principles</t>
-  </si>
-  <si>
-    <t>OECD</t>
-  </si>
-  <si>
-    <t>International policy principles</t>
-  </si>
-  <si>
-    <t>Principles for innovative and trustworthy AI, covering human rights, fairness, transparency, robustness, security and accountability.</t>
-  </si>
-  <si>
-    <t>Concise policy baseline that is easy to compare against NIST, UNESCO, EU and national frameworks.</t>
-  </si>
-  <si>
-    <t>Framework comparison; policy lecture; exam preparation</t>
-  </si>
-  <si>
-    <t>What minimum principles should trustworthy AI systems satisfy across countries?</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/ai-principles</t>
-  </si>
-  <si>
-    <t>Initially adopted 2019; updated May 2024.</t>
-  </si>
-  <si>
-    <t>International AI treaty</t>
-  </si>
-  <si>
-    <t>Framework Convention on Artificial Intelligence and Human Rights, Democracy and the Rule of Law</t>
-  </si>
-  <si>
-    <t>Council of Europe</t>
-  </si>
-  <si>
-    <t>International treaty</t>
-  </si>
-  <si>
-    <t>Official / legally binding framework</t>
-  </si>
-  <si>
-    <t>Addresses human rights, democratic processes, autonomy, transparency, accountability, equality and privacy across the AI lifecycle.</t>
-  </si>
-  <si>
-    <t>Shows the transition from voluntary ethics to treaty-based human-rights obligations.</t>
-  </si>
-  <si>
-    <t>Human-rights module; legal governance; global policy</t>
-  </si>
-  <si>
-    <t>International</t>
-  </si>
-  <si>
-    <t>How should AI development be constrained when it may affect fundamental rights and democratic institutions?</t>
-  </si>
-  <si>
-    <t>https://www.coe.int/en/web/artificial-intelligence/the-framework-convention-on-artificial-intelligence</t>
-  </si>
-  <si>
-    <t>First international legally binding treaty in this field; opened for signature 5 Sept 2024.</t>
-  </si>
-  <si>
-    <t>Developer risk reporting</t>
-  </si>
-  <si>
-    <t>How are AI developers managing risks? Insights from the Hiroshima AI Process reporting framework</t>
-  </si>
-  <si>
-    <t>International governance report</t>
-  </si>
-  <si>
-    <t>Official / multi-stakeholder</t>
-  </si>
-  <si>
-    <t>Analyzes how organizations report risk identification, safety, governance, content authentication and accountability practices.</t>
-  </si>
-  <si>
-    <t>Gives concrete examples of how frontier developers operationalize risk management, not just what principles say.</t>
-  </si>
-  <si>
-    <t>Industry governance; transparency; comparative analysis</t>
-  </si>
-  <si>
-    <t>G7 / global</t>
-  </si>
-  <si>
-    <t>Can voluntary transparency meaningfully improve accountability for advanced AI developers?</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/ai-publications/how-are-ai-developers-managing-risks-insights-from-responses-to-the-reporting-framework-of-the-hiroshima-ai-process-code-of-conduct</t>
-  </si>
-  <si>
-    <t>Reporting framework launched in 2025.</t>
-  </si>
-  <si>
-    <t>Comprehensive LLM ethics</t>
-  </si>
-  <si>
-    <t>Deconstructing the ethics of large language models from long-standing issues to new-emerging dilemmas</t>
-  </si>
-  <si>
-    <t>Deng et al.</t>
-  </si>
-  <si>
-    <t>Survey / review</t>
-  </si>
-  <si>
-    <t>Peer-reviewed</t>
-  </si>
-  <si>
-    <t>Surveys copyright, systematic bias, privacy, truthfulness, social norms and emerging ethical challenges of LLMs.</t>
-  </si>
-  <si>
-    <t>Good single-paper orientation before readers enter specialized literatures.</t>
-  </si>
-  <si>
-    <t>Literature review starting point; seminar reading</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Which LLM ethical risks are old problems amplified by scale, and which are genuinely new?</t>
-  </si>
-  <si>
-    <t>https://link.springer.com/article/10.1007/s43681-025-00797-3</t>
-  </si>
-  <si>
-    <t>Published in AI and Ethics.</t>
-  </si>
-  <si>
-    <t>Bias evaluation and mitigation</t>
-  </si>
-  <si>
-    <t>Bias and Fairness in Large Language Models: A Survey</t>
-  </si>
-  <si>
-    <t>Gallegos et al.</t>
-  </si>
-  <si>
-    <t>Survey</t>
-  </si>
-  <si>
-    <t>Research / arXiv</t>
-  </si>
-  <si>
-    <t>Organizes social bias harms, evaluation metrics, datasets and mitigation techniques for LLMs.</t>
-  </si>
-  <si>
-    <t>Provides a technical taxonomy that makes 'AI bias' measurable rather than purely rhetorical.</t>
-  </si>
-  <si>
-    <t>Bias lecture; evaluation design; related work</t>
-  </si>
-  <si>
-    <t>How should fairness be defined and measured for generative language systems?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2309.00770</t>
-  </si>
-  <si>
-    <t>Still a useful technical survey in 2026.</t>
-  </si>
-  <si>
-    <t>Hallucination taxonomy</t>
-  </si>
-  <si>
-    <t>A Survey on Hallucination in Large Language Models</t>
-  </si>
-  <si>
-    <t>ACM Computing Surveys</t>
-  </si>
-  <si>
-    <t>Reviews hallucination principles, taxonomies, causes, evaluation, detection and mitigation in LLMs.</t>
-  </si>
-  <si>
-    <t>Helps distinguish factual reliability problems from broader moral or social harms.</t>
-  </si>
-  <si>
-    <t>Truthfulness; reliability; high-stakes deployment</t>
-  </si>
-  <si>
-    <t>When is an incorrect LLM output merely an error, and when does it become an ethical harm?</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3703155</t>
-  </si>
-  <si>
-    <t>High-value technical survey.</t>
-  </si>
-  <si>
-    <t>Training-data leakage</t>
-  </si>
-  <si>
-    <t>New Privacy Risks for Large Language Models</t>
-  </si>
-  <si>
-    <t>Research paper</t>
-  </si>
-  <si>
-    <t>Preprint / current research</t>
-  </si>
-  <si>
-    <t>Examines data extraction and memorization risks, connecting privacy leakage with copyright and training-data provenance concerns.</t>
-  </si>
-  <si>
-    <t>Useful 2026 update showing privacy risk is not limited to classic membership inference.</t>
-  </si>
-  <si>
-    <t>Privacy section; training data; model memorization</t>
-  </si>
-  <si>
-    <t>What does a model owe people whose private or copyrighted data it can reproduce?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2509.14278v2</t>
-  </si>
-  <si>
-    <t>Version available Jan 2026.</t>
-  </si>
-  <si>
-    <t>Privacy threat landscape</t>
-  </si>
-  <si>
-    <t>SoK: The Privacy Paradox of Large Language Models</t>
-  </si>
-  <si>
-    <t>Systematization of knowledge</t>
-  </si>
-  <si>
-    <t>Preprint / research</t>
-  </si>
-  <si>
-    <t>Systematizes training-data extraction, reconstruction, inference-time privacy and protection mechanisms.</t>
-  </si>
-  <si>
-    <t>Gives readers a map of privacy attack surfaces instead of isolated examples.</t>
-  </si>
-  <si>
-    <t>Security/privacy module; research gap identification</t>
-  </si>
-  <si>
-    <t>Can LLM utility and strong privacy guarantees be achieved simultaneously?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2506.12699v2</t>
-  </si>
-  <si>
-    <t>Useful bridge between AI ethics and security.</t>
-  </si>
-  <si>
-    <t>Empirical privacy evaluation</t>
-  </si>
-  <si>
-    <t>Privacy Auditing of Large Language Models</t>
-  </si>
-  <si>
-    <t>Develops stronger privacy auditing techniques and more effective canaries for estimating empirical leakage.</t>
-  </si>
-  <si>
-    <t>Shows readers how privacy claims can be tested rather than assumed.</t>
-  </si>
-  <si>
-    <t>Methodology; model audit; technical assignment</t>
-  </si>
-  <si>
-    <t>Specialist</t>
-  </si>
-  <si>
-    <t>How should developers demonstrate that a language model is not leaking training data?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2503.06808v1</t>
-  </si>
-  <si>
-    <t>Technical privacy-auditing work.</t>
-  </si>
-  <si>
-    <t>Reference as needed</t>
-  </si>
-  <si>
-    <t>Agent memory and contextual leakage</t>
-  </si>
-  <si>
-    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory</t>
-  </si>
-  <si>
-    <t>Security research</t>
-  </si>
-  <si>
-    <t>Studies privacy leakage from inference-time contextual memory in LLM agents, beyond training-data privacy.</t>
-  </si>
-  <si>
-    <t>Important for 2026 because persistent AI assistants and agents create a new privacy attack surface.</t>
-  </si>
-  <si>
-    <t>Agentic AI; memory privacy; security discussion</t>
-  </si>
-  <si>
-    <t>Research / agents</t>
-  </si>
-  <si>
-    <t>What privacy risks appear when AI systems remember and act on user context over time?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2604.23711v1</t>
-  </si>
-  <si>
-    <t>2026 agent-memory privacy paper.</t>
-  </si>
-  <si>
-    <t>Persuasion landscape</t>
-  </si>
-  <si>
-    <t>Research survey</t>
-  </si>
-  <si>
-    <t>Reviews empirical evidence on automated, personalized and interactive LLM persuasion and its effects on attitudes and behavior.</t>
-  </si>
-  <si>
-    <t>A direct entry point into one of the most important newer AI-ethics issues.</t>
-  </si>
-  <si>
-    <t>Manipulation lecture; social influence; governance</t>
-  </si>
-  <si>
-    <t>When does helpful persuasion become manipulation or undue influence?</t>
-  </si>
-  <si>
-    <t>Updated Apr 2026.</t>
-  </si>
-  <si>
-    <t>Human vs AI persuasion</t>
-  </si>
-  <si>
-    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders</t>
-  </si>
-  <si>
-    <t>Schoenegger et al.</t>
-  </si>
-  <si>
-    <t>Large-scale experiment</t>
-  </si>
-  <si>
-    <t>Compares a frontier LLM with incentivized human persuaders in interactive settings and measures compliance with correct and incorrect persuasion.</t>
-  </si>
-  <si>
-    <t>Provides concrete empirical evidence that persuasive capability can create both benefits and harms.</t>
-  </si>
-  <si>
-    <t>Case study; empirical evidence; class discussion</t>
-  </si>
-  <si>
-    <t>Should systems with human-level or greater persuasive power face special safeguards?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2505.09662</t>
-  </si>
-  <si>
-    <t>Preregistered, large-scale incentivized experiment.</t>
-  </si>
-  <si>
-    <t>Harmful influence evaluation</t>
-  </si>
-  <si>
-    <t>Evaluating Language Models for Harmful Manipulation</t>
-  </si>
-  <si>
-    <t>Akbulut et al.</t>
-  </si>
-  <si>
-    <t>Human-subject evaluation</t>
-  </si>
-  <si>
-    <t>Research / preprint</t>
-  </si>
-  <si>
-    <t>Introduces a framework for measuring harmful manipulation across public policy, finance and health with participants from multiple countries.</t>
-  </si>
-  <si>
-    <t>Shows how manipulation can be operationalized and evaluated across consequential domains.</t>
-  </si>
-  <si>
-    <t>Evaluation design; high-stakes AI; cross-country analysis</t>
-  </si>
-  <si>
-    <t>US / UK / India</t>
-  </si>
-  <si>
-    <t>How can harmful manipulation be measured before deployment?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/pdf/2603.25326</t>
-  </si>
-  <si>
-    <t>Includes 10,101 participants across three locales.</t>
-  </si>
-  <si>
-    <t>Sycophancy to strategic deception</t>
-  </si>
-  <si>
-    <t>From Sycophancy to Deception: A Unified Taxonomy for Misleading LLM Behavior</t>
-  </si>
-  <si>
-    <t>Taxonomy / research</t>
-  </si>
-  <si>
-    <t>Unifies hallucination, omission, pragmatic distortion, sycophancy and strategic deception under a common taxonomy of misleading behavior.</t>
-  </si>
-  <si>
-    <t>Helps readers avoid treating all misleading model outputs as the same failure mode.</t>
-  </si>
-  <si>
-    <t>Conceptual framework; deception; research taxonomy</t>
-  </si>
-  <si>
-    <t>Does intent or goal-directedness change how ethically serious misleading AI behavior is?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2604.04788</t>
-  </si>
-  <si>
-    <t>Current 2026 taxonomy.</t>
-  </si>
-  <si>
-    <t>Sycophancy</t>
-  </si>
-  <si>
-    <t>Sycophancy in Large Language Models: Causes and Mitigations</t>
-  </si>
-  <si>
-    <t>Lars Malmqvist</t>
-  </si>
-  <si>
-    <t>Technical survey</t>
-  </si>
-  <si>
-    <t>Surveys excessive agreement with users, causes, measurement and mitigation, and links sycophancy to hallucination and bias.</t>
-  </si>
-  <si>
-    <t>Useful for discussing why 'agreeable' assistants can become epistemically unsafe.</t>
-  </si>
-  <si>
-    <t>Alignment; user trust; truthfulness</t>
-  </si>
-  <si>
-    <t>Should an assistant prioritize user satisfaction or epistemic honesty when they conflict?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2411.15287</t>
-  </si>
-  <si>
-    <t>Technical survey.</t>
-  </si>
-  <si>
-    <t>Emotional support</t>
-  </si>
-  <si>
-    <t>Huang, Stodolska &amp; Sultana</t>
-  </si>
-  <si>
-    <t>Qualitative HCI research</t>
-  </si>
-  <si>
-    <t>Analyzes how emotional support is co-constructed with AI companions and tensions such as support vs dependency and validation vs delusion.</t>
-  </si>
-  <si>
-    <t>Provides nuanced evidence beyond simplistic claims that AI companions are either beneficial or harmful.</t>
-  </si>
-  <si>
-    <t>HCI ethics; mental-health-adjacent discussion; companionship</t>
-  </si>
-  <si>
-    <t>How should AI offer emotional support without reinforcing dependency or harmful beliefs?</t>
-  </si>
-  <si>
-    <t>2026 HCI-focused research.</t>
-  </si>
-  <si>
-    <t>Companion-app design</t>
-  </si>
-  <si>
-    <t>Empirical audit</t>
-  </si>
-  <si>
-    <t>Audits popular AI companion apps for dark patterns, anthropomorphism, stereotypes, erotica and technical issues.</t>
-  </si>
-  <si>
-    <t>Connects ethical risk to actual interface and monetization design choices, not only model behavior.</t>
-  </si>
-  <si>
-    <t>Product ethics; dark patterns; companion AI</t>
-  </si>
-  <si>
-    <t>EU / UK market</t>
-  </si>
-  <si>
-    <t>Can product incentives push AI companions toward manipulative engagement?</t>
-  </si>
-  <si>
-    <t>Version updated Aug 2026.</t>
-  </si>
-  <si>
-    <t>Emotional dependence</t>
-  </si>
-  <si>
-    <t>Shi et al.</t>
-  </si>
-  <si>
-    <t>Perspective / evidence synthesis</t>
-  </si>
-  <si>
-    <t>Argues that emotional dependence can emerge incidentally in general-purpose AI use and may alter future preferences for human vs AI support.</t>
-  </si>
-  <si>
-    <t>Highlights cumulative interaction effects that one-shot safety evaluations can miss.</t>
-  </si>
-  <si>
-    <t>Long-term interaction ethics; product policy; research gaps</t>
-  </si>
-  <si>
-    <t>Should general-purpose assistants be evaluated for long-term relational effects, not just single-turn harms?</t>
-  </si>
-  <si>
-    <t>Includes synthesis of longitudinal evidence.</t>
-  </si>
-  <si>
-    <t>Identity and parasocial interaction</t>
-  </si>
-  <si>
-    <t>Negotiating Digital Identities with AI Companions</t>
-  </si>
-  <si>
-    <t>HCI / computational social science</t>
-  </si>
-  <si>
-    <t>Studies identity construction and negotiation in AI-companion communities using large-scale online discussions.</t>
-  </si>
-  <si>
-    <t>Useful for understanding anthropomorphism and dependence as social processes rather than merely UI bugs.</t>
-  </si>
-  <si>
-    <t>HCI seminar; identity; anthropomorphism</t>
-  </si>
-  <si>
-    <t>How do AI companions reshape users' identities, expectations and social relationships?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/html/2601.12181v1</t>
-  </si>
-  <si>
-    <t>Analyzes 22,374 online discussions.</t>
-  </si>
-  <si>
-    <t>Governance of autonomous agents</t>
-  </si>
-  <si>
-    <t>Raji &amp; Bashir</t>
-  </si>
-  <si>
-    <t>Systematic review</t>
-  </si>
-  <si>
-    <t>Reviews governance priorities, mechanisms and stakeholder roles for AI systems that autonomously plan and execute tasks.</t>
-  </si>
-  <si>
-    <t>Important 2026 bridge from chatbot ethics to systems that can act in the world.</t>
-  </si>
-  <si>
-    <t>Agentic AI governance; research agenda; seminar</t>
-  </si>
-  <si>
-    <t>How should accountability change when AI can plan, call tools and execute actions autonomously?</t>
-  </si>
-  <si>
-    <t>Published Jul 2026.</t>
-  </si>
-  <si>
-    <t>Security and governance practice</t>
-  </si>
-  <si>
-    <t>State of Agentic AI Security and Governance</t>
-  </si>
-  <si>
-    <t>OWASP GenAI Security Project</t>
-  </si>
-  <si>
-    <t>Security / governance report</t>
-  </si>
-  <si>
-    <t>Practitioner standard</t>
-  </si>
-  <si>
-    <t>Covers governance and security issues for autonomous AI systems, including controls, oversight and operational risk.</t>
-  </si>
-  <si>
-    <t>Gives practitioners a deployment-oriented complement to academic governance work.</t>
-  </si>
-  <si>
-    <t>Agent security; enterprise governance; checklist design</t>
-  </si>
-  <si>
-    <t>What controls are necessary when agents receive tools, permissions and persistent access?</t>
-  </si>
-  <si>
-    <t>https://genai.owasp.org/resource/state-of-agentic-ai-security-and-governance/</t>
-  </si>
-  <si>
-    <t>Practitioner-focused resource.</t>
-  </si>
-  <si>
-    <t>AI in education ethics</t>
-  </si>
-  <si>
-    <t>AI and the future of education: Disruptions, dilemmas and directions</t>
-  </si>
-  <si>
-    <t>Policy / anthology</t>
-  </si>
-  <si>
-    <t>Official / expert collection</t>
-  </si>
-  <si>
-    <t>Explores philosophical, ethical and pedagogical dilemmas created by AI in education and human-machine co-creation.</t>
-  </si>
-  <si>
-    <t>Useful domain case study showing how general AI-ethics principles change in a real institution such as education.</t>
-  </si>
-  <si>
-    <t>Education case study; classroom discussion; policy</t>
-  </si>
-  <si>
-    <t>How should education preserve human agency, fairness and learning integrity in an AI-rich environment?</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/articles/ai-and-future-education-disruptions-dilemmas-and-directions</t>
-  </si>
-  <si>
-    <t>Published Jan 2026.</t>
-  </si>
-  <si>
-    <t>Scale, data and social harms</t>
-  </si>
-  <si>
-    <t>On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
-  </si>
-  <si>
-    <t>Bender et al.</t>
-  </si>
-  <si>
-    <t>FAccT research paper</t>
-  </si>
-  <si>
-    <t>Raises concerns about environmental cost, training-data scale, bias, documentation and the gap between linguistic form and meaning.</t>
-  </si>
-  <si>
-    <t>Foundational critical reading that explains why ethics concerns were present before today's frontier LLMs.</t>
-  </si>
-  <si>
-    <t>Historical foundation; data ethics; critical perspective</t>
-  </si>
-  <si>
-    <t>Does scaling language models without understanding data and social context create predictable harms?</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/10.1145/3442188.3445922</t>
-  </si>
-  <si>
-    <t>FAccT 2021; foundational.</t>
-  </si>
-  <si>
-    <t>Language-model harm taxonomy</t>
-  </si>
-  <si>
-    <t>Ethical and Social Risks of Harm from Language Models</t>
-  </si>
-  <si>
-    <t>Weidinger et al.</t>
-  </si>
-  <si>
-    <t>Risk taxonomy / research</t>
-  </si>
-  <si>
-    <t>Organizes harms around discrimination, information hazards, misinformation, malicious use, human-computer interaction and socioeconomic/environmental harms.</t>
-  </si>
-  <si>
-    <t>One of the clearest early taxonomies for turning 'LLM ethics' into categories of harm.</t>
-  </si>
-  <si>
-    <t>Foundations; risk taxonomy; related work</t>
-  </si>
-  <si>
-    <t>What types of harm can language models create, and through which pathways?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2112.04359</t>
-  </si>
-  <si>
-    <t>Published work originated from DeepMind research.</t>
-  </si>
-  <si>
-    <t>Foundation-model societal impact</t>
-  </si>
-  <si>
-    <t>On the Opportunities and Risks of Foundation Models</t>
-  </si>
-  <si>
-    <t>Bommasani et al.</t>
-  </si>
-  <si>
-    <t>Examines foundation models across capabilities, homogenization, adaptation, evaluation, robustness, security, fairness, misuse, law and societal impact.</t>
-  </si>
-  <si>
-    <t>Provides broad conceptual background for why one upstream model can propagate benefits and harms across many downstream systems.</t>
-  </si>
-  <si>
-    <t>Foundation models; societal impact; literature review</t>
-  </si>
-  <si>
-    <t>How does reliance on a small number of foundation models concentrate systemic risk?</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2108.07258</t>
-  </si>
-  <si>
-    <t>Stanford CRFM foundational report.</t>
-  </si>
-  <si>
-    <t>New This Week — Automatically Discovered</t>
-  </si>
-  <si>
-    <t>Recent high-scoring discoveries from scholarly APIs and official policy pages.</t>
-  </si>
-  <si>
-    <t>Detected</t>
-  </si>
-  <si>
-    <t>Published</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t>Importance Score</t>
-  </si>
-  <si>
-    <t>Why flagged</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>DOI</t>
-  </si>
-  <si>
-    <t>Decision</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>2026-08-16</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>A Common Standard for AI Incident Accountability</t>
-  </si>
-  <si>
-    <t>Zenodo (CERN European Organization for Nuclear Research)</t>
-  </si>
-  <si>
-    <t>article</t>
-  </si>
-  <si>
-    <t>Must Read Candidate</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, accountability, disclosure, reporting; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21907857</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21907857</t>
-  </si>
-  <si>
-    <t>Pending</t>
-  </si>
-  <si>
-    <t>Automatically discovered; verify bibliographic details before formal citation.</t>
-  </si>
-  <si>
-    <t>Autonomous Decision Assurance Layer for AI-Driven Enterprise Analytics: Bridging Governance, Multi-Agent AI, and Executive Decision Intelligence in Saudi Vision 2030 Organizations</t>
-  </si>
-  <si>
-    <t>International Journal for Research in Applied Science and Engineering Technology</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.22214/ijraset.2026.84573</t>
-  </si>
-  <si>
-    <t>10.22214/ijraset.2026.84573</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21907856</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21907856</t>
-  </si>
-  <si>
-    <t>Sustainability and Environmental Ethics in Sanskrit Texts: A Geographical Perspective</t>
-  </si>
-  <si>
-    <t>Environment &amp; Labor</t>
-  </si>
-  <si>
-    <t>Prantik Gabeshana Patrika</t>
-  </si>
-  <si>
-    <t>journal-article</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: water, environment, sustainability; strong scholarly metadata source; impact signal: framework, guidelines, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.67841/pgp.260501082</t>
-  </si>
-  <si>
-    <t>10.67841/pgp.260501082</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>Validating the Virtue Ethics Measurement Scale Within an Open Distance e-Learning Higher Education Institution in South Africa: Students’ Perspectives of Generative AI Practices</t>
-  </si>
-  <si>
-    <t>Algorithms</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3390/a19080682</t>
-  </si>
-  <si>
-    <t>10.3390/a19080682</t>
-  </si>
-  <si>
-    <t>2026-08-15</t>
-  </si>
-  <si>
-    <t>Examining the Impact of Social-Emotional Learning on Academic Achievement in African American Middle School Girls</t>
-  </si>
-  <si>
-    <t>Seton Hall University eRepository (Seton Hall University)</t>
-  </si>
-  <si>
-    <t>dissertation</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://openalex.org/W7160680247</t>
-  </si>
-  <si>
-    <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>Managing ESG and cyber risks in Kazakhstan’s low-carbon transition by aligning EU and Chinese standards through demoethics</t>
-  </si>
-  <si>
-    <t>Discover Sustainability</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, sustainability; impact signal: framework, standard, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s43621-026-04260-z</t>
-  </si>
-  <si>
-    <t>10.1007/s43621-026-04260-z</t>
-  </si>
-  <si>
-    <t>A Framework for Protecting Students Privacy in Online and Offline Digital Footprints</t>
-  </si>
-  <si>
-    <t>INTERNATIONAL JOURNAL OF COMPUTER SCIENCE AND MATHEMATICAL THEORY E-ISSN</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
-  </si>
-  <si>
-    <t>10.56201/ijcsmt.vol.12.no7.2026.pg51.68</t>
-  </si>
-  <si>
-    <t>A Review of the TITAN Guideline: Advancing Transparency and Responsible Artificial Intelligence Use in Medical Research and Scholarly Publishing</t>
-  </si>
-  <si>
-    <t>Electronic Journal of Medical Research</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, accountability, reporting; impact signal: framework, guidelines, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.64813/ejmr.2026.126</t>
-  </si>
-  <si>
-    <t>10.64813/ejmr.2026.126</t>
-  </si>
-  <si>
-    <t>Digital personas of AI use in nursing education: a latent class analysis of learning behaviors and academic engagement</t>
-  </si>
-  <si>
-    <t>Frontiers in Medicine</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fmed.2026.1859093</t>
-  </si>
-  <si>
-    <t>10.3389/fmed.2026.1859093</t>
-  </si>
-  <si>
-    <t>Brazil's ENAMED and the Governance of AI-Supported Exam Preparation: A Conceptual Policy Analysis</t>
-  </si>
-  <si>
-    <t>International Journal For Multidisciplinary Research</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: standard, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.36948/ijfmr.2026.v08i04.84125</t>
-  </si>
-  <si>
-    <t>10.36948/ijfmr.2026.v08i04.84125</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>Beyond Visual Evidence: Revealing and Mitigating Relational Privacy Leakage in Document MLLMs</t>
-  </si>
-  <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>matches Privacy: privacy, leakage, extraction; impact signal: benchmark, framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12911v1</t>
-  </si>
-  <si>
-    <t>10.1145/3767308.3835901</t>
-  </si>
-  <si>
-    <t>Digital Transformation of the Indonesian Public Sector: A Systematic Review of Governance, Audit, and Service Innovation</t>
-  </si>
-  <si>
-    <t>F1000Research</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: systematic review, framework, guidelines; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.12688/f1000research.188727.1</t>
-  </si>
-  <si>
-    <t>10.12688/f1000research.188727.1</t>
-  </si>
-  <si>
-    <t>Performance, interaction, and ethical evaluation in the use of generative artificial intelligence in engineering education</t>
-  </si>
-  <si>
-    <t>Education and Information Technologies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, regulation, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10639-026-14112-y</t>
-  </si>
-  <si>
-    <t>10.1007/s10639-026-14112-y</t>
-  </si>
-  <si>
-    <t>Exploring student use of generative AI in higher education: A dual-institutional study</t>
-  </si>
-  <si>
-    <t>book-chapter</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s10639-026-14100-2</t>
-  </si>
-  <si>
-    <t>10.1007/s10639-026-14100-2</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>How Personal and Cognitive Traits Influence AI Attitudes, Ethics, and Well-being: The Role of AI Autonomy and Criticality in Design</t>
-  </si>
-  <si>
-    <t>SN Computer Science</t>
-  </si>
-  <si>
-    <t>matches Persuasion &amp; Manipulation: influence, autonomy; impact signal: survey, framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s42979-026-05214-y</t>
-  </si>
-  <si>
-    <t>10.1007/s42979-026-05214-y</t>
-  </si>
-  <si>
-    <t>Ethics Suppression in AI Development: A Comparative Case Study of Responsible AI Under Competitive Pressure</t>
-  </si>
-  <si>
-    <t>International Journal of Applied Research in Business and Management</t>
-  </si>
-  <si>
-    <t>matches Foundations: ethics, responsible ai; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51137/wrp.ijarbm.869</t>
-  </si>
-  <si>
-    <t>10.51137/wrp.ijarbm.869</t>
-  </si>
-  <si>
-    <t>Generative AI in African Higher Education: A Systematic Review of Opportunities, Ethical Challenges, and Institutional Readiness</t>
-  </si>
-  <si>
-    <t>Journal of University Teaching and Learning Practice</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.53761/c682ye61</t>
-  </si>
-  <si>
-    <t>10.53761/c682ye61</t>
-  </si>
-  <si>
-    <t>Which LLM Is Your Ideal Companion? Evaluating Emotional Companion Capabilities of LLMs Based on Adult Attachment Theory</t>
-  </si>
-  <si>
-    <t>matches Human-AI Relationships: companion, emotional support, attachment; impact signal: benchmark, evaluation; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13168v1</t>
-  </si>
-  <si>
-    <t>InFactPlanner: Planning Sustainable Geo-Distributed LLM Data Centers</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, carbon, sustainability; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12915v1</t>
-  </si>
-  <si>
-    <t>Legitimacy Criteria for Strategic Communication in the Age of Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>The Proceedings of the World Conference on Social Sciences and Humanities.</t>
-  </si>
-  <si>
-    <t>conference-paper</t>
-  </si>
-  <si>
-    <t>matches Persuasion &amp; Manipulation: persuasion, manipulation, influence, behavioral influence; impact signal: framework, regulation, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.33422/shconf.v3i1.2047</t>
-  </si>
-  <si>
-    <t>10.33422/shconf.v3i1.2047</t>
-  </si>
-  <si>
-    <t>A carbon aware job scheduling framework for data center sustainability using deep learning training</t>
-  </si>
-  <si>
-    <t>Discover Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, environment, sustainability; strong scholarly metadata source; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s44163-026-02022-4</t>
-  </si>
-  <si>
-    <t>10.1007/s44163-026-02022-4</t>
-  </si>
-  <si>
-    <t>How electoral management bodies govern digital electoral systems: capacity, authority, and accountability</t>
-  </si>
-  <si>
-    <t>Frontiers in Political Science</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit, assurance; impact signal: systematic review, framework, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpos.2026.1877569</t>
-  </si>
-  <si>
-    <t>10.3389/fpos.2026.1877569</t>
-  </si>
-  <si>
-    <t>Leveraging strategic facilities management to achieve corporate ESG and sustainability: a literature review</t>
-  </si>
-  <si>
-    <t>Frontiers in Environmental Economics</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: environment, sustainability; impact signal: framework, governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/frevc.2026.1839120</t>
-  </si>
-  <si>
-    <t>10.3389/frevc.2026.1839120</t>
-  </si>
-  <si>
-    <t>Effect of Artificial Intelligence (AI) Study Tools on the Study Behaviour of Pharmacology and Medical Students in Bauchi State, Nigeria</t>
-  </si>
-  <si>
-    <t>WORLD JOURNAL OF INNOVATION AND MODERN TECHNOLOGY</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: survey, guidelines, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.56201/wjimt.v10.no7.2026.pg351.366</t>
-  </si>
-  <si>
-    <t>10.56201/wjimt.v10.no7.2026.pg351.366</t>
-  </si>
-  <si>
-    <t>Analysis of PAI Students' Readiness for the Integration of Artificial Intelligence in Learning at Ahmad Dahlan University</t>
-  </si>
-  <si>
-    <t>EDUSOSHUM Journal of Islamic Education and Social Humanities</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.52366/edusoshum.v6i3.550</t>
-  </si>
-  <si>
-    <t>10.52366/edusoshum.v6i3.550</t>
-  </si>
-  <si>
-    <t>Beyond the Device: Reforming Higher Education and Teacher Education Curricula from ICT Literacy to AI Pedagogical Readiness in East Africa</t>
-  </si>
-  <si>
-    <t>East African Journal of Education Studies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.37284/eajes.9.3.5567</t>
-  </si>
-  <si>
-    <t>10.37284/eajes.9.3.5567</t>
-  </si>
-  <si>
-    <t>Acceptance of Generative AI for Supporting Innovative Learning in Vocational Education</t>
-  </si>
-  <si>
-    <t>World Journal of Education</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: survey, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5430/wje.v16n3p30</t>
-  </si>
-  <si>
-    <t>10.5430/wje.v16n3p30</t>
-  </si>
-  <si>
-    <t>Benchmarking Knowledge-Extraction Attack and Defense on Retrieval-Augmented Generation (RAG)</t>
-  </si>
-  <si>
-    <t>OpenAlex</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>matches Privacy: privacy, extraction; impact signal: benchmark, framework, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1145/3770855.3817524</t>
-  </si>
-  <si>
-    <t>10.1145/3770855.3817524</t>
-  </si>
-  <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>Governing Agentic AI in FinTech</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11344v2</t>
-  </si>
-  <si>
-    <t>Toward Meaningful Transparency for AI Chatbots: Disclosing Persuasive Intent Reduces Persuasion</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, disclosure, provenance; impact signal: regulation, policy, randomized; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11794v1</t>
-  </si>
-  <si>
-    <t>Research on the Judicial Fairness Challenges and Legal Regulation of AI-Assisted Judgments in the Context of Digital Justice</t>
-  </si>
-  <si>
-    <t>Advanced Electromagnetics</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.7716/aem.v15i3.3403</t>
-  </si>
-  <si>
-    <t>10.7716/aem.v15i3.3403</t>
-  </si>
-  <si>
-    <t>The Correlation Between Exposure to English-Language Content on Instagram and Listening Comprehension among EFL Students at UIN Datokarama Palu</t>
-  </si>
-  <si>
-    <t>Journal of General Education and Humanities</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.58421/gehu.v5i4.1936</t>
-  </si>
-  <si>
-    <t>10.58421/gehu.v5i4.1936</t>
-  </si>
-  <si>
-    <t>Motivation to learn and teach home economics in higher education: Predictors and comparative analysis</t>
-  </si>
-  <si>
-    <t>Social Sciences &amp; Humanities Open</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.ssaho.2026.103414</t>
-  </si>
-  <si>
-    <t>10.1016/j.ssaho.2026.103414</t>
-  </si>
-  <si>
-    <t>The Impact of Artificial Intelligence on English Language Learning, Communication, and Linguistic Development: Opportunities and Challenges</t>
-  </si>
-  <si>
-    <t>Journal of Intelligent Decision Making and Information Science</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.59543/jidmis.v3.1938</t>
-  </si>
-  <si>
-    <t>10.59543/jidmis.v3.1938</t>
-  </si>
-  <si>
-    <t>AI literacy and subject specialization in pre-service teacher education: a mixed-methods study of dimensional profiles and perceived pedagogical challenges</t>
-  </si>
-  <si>
-    <t>Frontiers in Education</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1876627</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1876627</t>
-  </si>
-  <si>
-    <t>Development and pilot testing of multi-stakeholder questionnaires for assessing University 4.0 transformation in higher education institutions</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; impact signal: governance, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1908552</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1908552</t>
-  </si>
-  <si>
-    <t>PENGARUH MUSIK AI TERHADAP PENINGKATAN MOTIVASI BELAJAR SISWA PADA MATA PELAJARAN IPS DI KELAS IV SD NEGERI 73 AMBON</t>
-  </si>
-  <si>
-    <t>SOCIAL : Jurnal Inovasi Pendidikan IPS</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51878/social.v6i3.14523</t>
-  </si>
-  <si>
-    <t>10.51878/social.v6i3.14523</t>
-  </si>
-  <si>
-    <t>2026-09-01</t>
-  </si>
-  <si>
-    <t>Physical Processing of Aquatic Gel Foods: From Protein Structure Regulation to Health, Sustainability, and Personalized Design</t>
-  </si>
-  <si>
-    <t>Comprehensive Reviews in Food Science and Food Safety</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, sustainability; strong scholarly metadata source; impact signal: regulation, standard, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/1541-4337.70601</t>
-  </si>
-  <si>
-    <t>10.1111/1541-4337.70601</t>
-  </si>
-  <si>
-    <t>2026-08-08</t>
-  </si>
-  <si>
-    <t>ChatGPT and Large Language Models in Contemporary Nursing</t>
-  </si>
-  <si>
-    <t>Journal of Clinical Nursing</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, academic integrity, learning; impact signal: systematic review, framework, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1111/jocn.70490</t>
-  </si>
-  <si>
-    <t>10.1111/jocn.70490</t>
-  </si>
-  <si>
-    <t>Software Engineering for and with GUI Agent</t>
-  </si>
-  <si>
-    <t>arXiv (Cornell University)</t>
-  </si>
-  <si>
-    <t>preprint</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, evaluation, audit; impact signal: benchmark, framework, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.48550/arxiv.2608.09278</t>
-  </si>
-  <si>
-    <t>10.48550/arxiv.2608.09278</t>
-  </si>
-  <si>
-    <t>Banking Performance under the Lens of Earnings Management: A Theoretical and Bibliometric Systematic Review</t>
-  </si>
-  <si>
-    <t>Bulletin of Social Studies and Community Development</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: transparency, disclosure, reporting; impact signal: systematic review, framework, guidelines; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.61436/bsscd/v5i3.pp253-267</t>
-  </si>
-  <si>
-    <t>10.61436/bsscd/v5i3.pp253-267</t>
-  </si>
-  <si>
-    <t>Pedagogical prompting rather than technical mastery: Generative AI use by English and English-medium instruction teachers</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1901680</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1901680</t>
-  </si>
-  <si>
-    <t>Applied and Filtered: An End-to-End Algorithmic Fairness Audit of A Public Employment Agency</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: evaluation, audit; impact signal: evaluation, audit; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13022v1</t>
-  </si>
-  <si>
-    <t>Pre-service teachers' general pedagogical knowledge and pedagogical learning opportunities at entry into induction: comparing traditional and alternative teacher education programs</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: standard, longitudinal; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1790135</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1790135</t>
-  </si>
-  <si>
-    <t>Policy Integration and Implementation Gaps in China’s Dual-Carbon Strategy: A Multi-Dimensional Analysis of Carbon Trading System, New Energy Vehicle Incentives, and Air Quality Policies</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon; impact signal: policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.59543/jidmis.v3.1782</t>
-  </si>
-  <si>
-    <t>10.59543/jidmis.v3.1782</t>
-  </si>
-  <si>
-    <t>Dysfunction of Zakat Village Governance in Papua: Fragmentation of Collaboration and Inequality of Amil Capacity</t>
-  </si>
-  <si>
-    <t>JURNAL ILMIAH GEMA PERENCANA</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, evaluation; strong scholarly metadata source; impact signal: framework, regulation, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.61860/jigp.v5i1.411</t>
-  </si>
-  <si>
-    <t>10.61860/jigp.v5i1.411</t>
-  </si>
-  <si>
-    <t>Human-centric AI governance in the European Union. Accountability, fundamental rights, and institutional resilience in public administration</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/fpos.2026.1928481</t>
-  </si>
-  <si>
-    <t>10.3389/fpos.2026.1928481</t>
-  </si>
-  <si>
-    <t>Delivering building demand flexibility for grid-interactive operation: from perception and cognition to decision, execution, and verification</t>
-  </si>
-  <si>
-    <t>Applied Energy</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon; impact signal: framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.apenergy.2026.128668</t>
-  </si>
-  <si>
-    <t>10.1016/j.apenergy.2026.128668</t>
-  </si>
-  <si>
-    <t>PENGARUH MODEL PEMBELAJARAN PROJECT BASED LEARNING DAN KEDISIPLINAN BELAJAR TERHADAP KESIAPAN KERJA SISWA PADA JURUSAN AKUNTANSI KEUANGAN LEMABAGA DI SMK NEGERI 1 PANGKEP</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; impact signal: survey; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51878/social.v6i3.14617</t>
-  </si>
-  <si>
-    <t>10.51878/social.v6i3.14617</t>
-  </si>
-  <si>
-    <t>Large Language Model-facilitated national review on the use of ecological tools and processes in Environmental Impact Statements (EIS) in the U.S. with demonstrated use cases for environmental planners, legal practitioners, and researchers</t>
-  </si>
-  <si>
-    <t>Springer Science and Business Media LLC</t>
-  </si>
-  <si>
-    <t>posted-content</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, environment, labor; strong scholarly metadata source; impact signal: benchmark, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.21203/rs.3.rs-10627892/v1</t>
-  </si>
-  <si>
-    <t>10.21203/rs.3.rs-10627892/v1</t>
-  </si>
-  <si>
-    <t>Optimization of Household Equipment and Instrumentation in an Effort to Save Electrical Energy in a Restaurant</t>
-  </si>
-  <si>
-    <t>International Journal Of Community Service</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, carbon, environment; strong scholarly metadata source; impact signal: survey, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.51601/ijcs.v6i3.1022</t>
-  </si>
-  <si>
-    <t>10.51601/ijcs.v6i3.1022</t>
-  </si>
-  <si>
-    <t>Effect of Public Safety Center Video-Based Education on Emergency Response Attitudes Among High School Students</t>
-  </si>
-  <si>
-    <t>Jurnal Kegawatdaruratan Medis Indonesia</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.58545/jkmi.v5i2.827</t>
-  </si>
-  <si>
-    <t>10.58545/jkmi.v5i2.827</t>
-  </si>
-  <si>
-    <t>2026-08-07</t>
-  </si>
-  <si>
-    <t>From Single Chatbots to Governed Agent Ecosystems: An Agentic AI Pattern Catalogue and Orchestration Framework for Mission-Critical Hospital Information Management Systems</t>
-  </si>
-  <si>
-    <t>matches Agentic AI: agentic ai, autonomous agent, multi-agent; impact signal: framework, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.07627v1</t>
-  </si>
-  <si>
-    <t>10.38124/ijisrt/26jul830</t>
-  </si>
-  <si>
-    <t>Bias Smells in AI Software Development: Recognizing Potential Sources of Fairness Debt</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.48550/arxiv.2608.10248</t>
-  </si>
-  <si>
-    <t>10.48550/arxiv.2608.10248</t>
-  </si>
-  <si>
-    <t>Quantifying the Relationship Between Clinical Safety and Environmental Impact in Therapeutic LLMs</t>
-  </si>
-  <si>
-    <t>matches Environment &amp; Labor: energy, water, carbon, environment; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11830v1</t>
-  </si>
-  <si>
-    <t>Benchmark-Based Comparative Assessment of Publicly Benchmarked Indian Foundation Models: A Capability and Evaluation-Maturity Framework</t>
-  </si>
-  <si>
-    <t>matches India &amp; Global South: multilingual, india; impact signal: survey, benchmark, framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.11891v1</t>
-  </si>
-  <si>
-    <t>Academic League of Artificial Intelligence - An Integrative Perspective of Teaching, Research, and Extension</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; impact signal: framework, governance; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.13447v1</t>
-  </si>
-  <si>
-    <t>Educational Aspirations in Contemporary Indian Education: A Critical Conceptual Synthesis for Holistic Learner Development</t>
-  </si>
-  <si>
-    <t>Asian Journal of Education and Social Studies</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: policy, longitudinal; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.9734/ajess/2026/v52i83261</t>
-  </si>
-  <si>
-    <t>10.9734/ajess/2026/v52i83261</t>
-  </si>
-  <si>
-    <t>Solar Exposure and Photoprotection Behaviors as Determinants of Acne Vulgaris Severity Among University Students in Andalusia-Spain</t>
-  </si>
-  <si>
-    <t>Ibn Sina Journal of Medical Science Health &amp; Pharmacy</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student; impact signal: survey, framework, evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.64440/ibnsina/sina0027</t>
-  </si>
-  <si>
-    <t>10.64440/ibnsina/sina0027</t>
-  </si>
-  <si>
-    <t>FSGR: Mitigating Token Frequency Bias for Fair SID-Based Generative Recommendation</t>
-  </si>
-  <si>
-    <t>matches Bias &amp; Fairness: bias, fairness; impact signal: framework; recent</t>
-  </si>
-  <si>
-    <t>http://arxiv.org/abs/2608.12845v1</t>
-  </si>
-  <si>
-    <t>HEPE — Complete 16-State AI Governance Space with Lyapunov Values (Hardware-Enforced Policy Engine)</t>
-  </si>
-  <si>
-    <t>matches Governance &amp; Measurement: governance, audit; impact signal: policy, governance, audit; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.5281/zenodo.21935563</t>
-  </si>
-  <si>
-    <t>10.5281/zenodo.21935563</t>
-  </si>
-  <si>
-    <t>What Remains Ours to Think? Reclaiming Critical Thinking in AI‐Augmented Student Leadership Education</t>
-  </si>
-  <si>
-    <t>New Directions for Student Leadership</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1002/yd.70068</t>
-  </si>
-  <si>
-    <t>10.1002/yd.70068</t>
-  </si>
-  <si>
-    <t>Supervision in educational leadership: practices, challenges, and innovations in the UAE — a multi-level coupling analysis of the current and future</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, learning; impact signal: benchmark, policy, governance; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feduc.2026.1862260</t>
-  </si>
-  <si>
-    <t>10.3389/feduc.2026.1862260</t>
-  </si>
-  <si>
-    <t>Research ethics and publication policies in journals using the Korea Institute of Science and Technology Information (KISTI) academic publishing platform: a content analysis of 181 journals</t>
-  </si>
-  <si>
-    <t>Science Editing</t>
-  </si>
-  <si>
-    <t>matches Transparency &amp; Accountability: accountability, disclosure; impact signal: guidelines, standard, policy; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.6087/kcse.403</t>
-  </si>
-  <si>
-    <t>10.6087/kcse.403</t>
-  </si>
-  <si>
-    <t>Striking a Balance between the Right to Privacy and Freedom of Expression: A Case Study of Women’s Digital Rights in Tanzania</t>
-  </si>
-  <si>
-    <t>East African Journal of Law and Ethics</t>
-  </si>
-  <si>
-    <t>matches Regulation: regulation, legal framework, standard; impact signal: framework, regulation, standard; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.37284/eajle.9.3.5557</t>
-  </si>
-  <si>
-    <t>10.37284/eajle.9.3.5557</t>
-  </si>
-  <si>
-    <t>Evaluation of the CIPP Model in a Project-Based Basic Electronics Course: A Discriminant Validity and Common Method Bias Analysis</t>
-  </si>
-  <si>
-    <t>Educative: Jurnal Ilmiah Pendidikan</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: education, student, learning; strong scholarly metadata source; impact signal: evaluation; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.70437/educative.v4i2.2180</t>
-  </si>
-  <si>
-    <t>10.70437/educative.v4i2.2180</t>
-  </si>
-  <si>
-    <t>The effectiveness of the contextual teaching and learning model on mathematical literacy skills in terms of learning motivation</t>
-  </si>
-  <si>
-    <t>Union: Jurnal Ilmiah Pendidikan Matematika</t>
-  </si>
-  <si>
-    <t>matches Education &amp; Research: student, learning; strong scholarly metadata source; recent</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.30738/union.v14i2.22911</t>
-  </si>
-  <si>
-    <t>10.30738/union.v14i2.22911</t>
-  </si>
-  <si>
-    <t>Review Queue — Human-in-the-loop Curation</t>
-  </si>
-  <si>
-    <t>Promote only sources that are genuinely useful. Automatic discovery is intentionally not identical to automatic curation.</t>
-  </si>
-  <si>
-    <t>Topic Map — What to Read for Each AI / LLM Ethics Question</t>
-  </si>
-  <si>
-    <t>Theme-level map generated from the current curated library.</t>
-  </si>
-  <si>
-    <t>Sources in library</t>
-  </si>
-  <si>
-    <t>2026-heavy?</t>
-  </si>
-  <si>
-    <t>Start with</t>
-  </si>
-  <si>
-    <t>Then read</t>
-  </si>
-  <si>
-    <t>Typical reader question</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Recommendation on the Ethics of Artificial Intelligence; On the Dangers of Stochastic Parrots: Can Language Models Be Too Big?</t>
-  </si>
-  <si>
-    <t>Artificial Intelligence Risk Management Framework: Generative Artificial Intelligence Profile (NIST AI 600-1); Guidelines for providers of general-purpose AI models</t>
-  </si>
-  <si>
-    <t>An Evaluation of AI Companion Apps; Stumbling Into AI Emotional Dependence: How Routine AI Interactions Reshape Human Connection</t>
-  </si>
-  <si>
-    <t>Large Language Models Are More Persuasive Than Incentivized Human Persuaders; Evaluating Language Models for Harmful Manipulation</t>
-  </si>
-  <si>
-    <t>Spore: Efficient and Training-Free Privacy Extraction Attack on LLM Agent Memory; SoK: The Privacy Paradox of Large Language Models</t>
-  </si>
-  <si>
-    <t>2026-Only View</t>
-  </si>
-  <si>
-    <t>Current-year curated items.</t>
-  </si>
-  <si>
-    <t>Policy, Governance &amp; Regulation</t>
-  </si>
-  <si>
-    <t>Curated governance, standards, transparency, law and human-rights sources.</t>
-  </si>
-  <si>
-    <t>Source Configuration</t>
-  </si>
-  <si>
-    <t>Edit config/sources.yaml in the repository to change the automation. This sheet is a readable mirror.</t>
-  </si>
-  <si>
-    <t>Endpoint / URL</t>
-  </si>
-  <si>
-    <t>Enabled</t>
-  </si>
-  <si>
-    <t>Authority</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>API</t>
-  </si>
-  <si>
-    <t>https://export.arxiv.org/api/query</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Fresh preprints</t>
-  </si>
-  <si>
-    <t>3-second delay between repeated calls</t>
-  </si>
-  <si>
-    <t>https://api.openalex.org/works</t>
-  </si>
-  <si>
-    <t>Broad scholarly discovery</t>
-  </si>
-  <si>
-    <t>OPENALEX_API_KEY optional</t>
-  </si>
-  <si>
-    <t>Crossref</t>
-  </si>
-  <si>
-    <t>https://api.crossref.org/works</t>
-  </si>
-  <si>
-    <t>Published DOI metadata</t>
-  </si>
-  <si>
-    <t>CONTACT_EMAIL recommended</t>
-  </si>
-  <si>
-    <t>NIST Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>Official page watch</t>
-  </si>
-  <si>
-    <t>https://www.nist.gov/artificial-intelligence</t>
-  </si>
-  <si>
-    <t>Policy/news link discovery</t>
-  </si>
-  <si>
-    <t>First scan bootstraps without flooding</t>
-  </si>
-  <si>
-    <t>European Commission AI Act</t>
-  </si>
-  <si>
-    <t>OECD.AI Wonk</t>
-  </si>
-  <si>
-    <t>https://oecd.ai/en/wonk</t>
-  </si>
-  <si>
-    <t>UNESCO Artificial Intelligence</t>
-  </si>
-  <si>
-    <t>https://www.unesco.org/en/artificial-intelligence</t>
-  </si>
-  <si>
-    <t>IndiaAI / MeitY — PIB Releases</t>
-  </si>
-  <si>
-    <t>https://www.pib.gov.in/AllRelease.aspx?MenuId=30&amp;lang=1&amp;reg=3</t>
-  </si>
-  <si>
-    <t>Automation Update Log</t>
-  </si>
-  <si>
-    <t>Every run records discovery and deduplication counts.</t>
-  </si>
-  <si>
-    <t>New This Week</t>
-  </si>
-  <si>
-    <t>Review Queue</t>
-  </si>
-  <si>
-    <t>Auto-promoted</t>
-  </si>
-  <si>
-    <t>2026-08-16T12:18:00+05:30</t>
-  </si>
-  <si>
-    <t>Initial build</t>
-  </si>
-  <si>
-    <t>Living tracker package initialized</t>
-  </si>
-  <si>
-    <t>2026-08-16T07:19:28+00:00</t>
-  </si>
-  <si>
-    <t>Policy/IndiaAI Safe &amp; Trusted AI: HTTPError: 403 Client Error: Forbidden for url: https://indiaai.gov.in/hub/safe-trusted-ai</t>
-  </si>
-  <si>
-    <t>2026-08-16T07:39:54+00:00</t>
-  </si>
-  <si>
-    <t>2026-08-16T10:42:00+00:00</t>
   </si>
   <si>
     <t>Automation Guide</t>
@@ -3530,7 +3533,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="22.7109375" customWidth="1"/>
@@ -3711,7 +3714,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="7" t="s">
-        <v>26</v>
+        <v>820</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>28</v>
@@ -3735,6 +3738,35 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="7">
+        <v>29</v>
+      </c>
+      <c r="D10" s="7">
+        <v>640</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0</v>
+      </c>
+      <c r="F10" s="7">
+        <v>68</v>
+      </c>
+      <c r="G10" s="7">
+        <v>68</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3762,7 +3794,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3772,7 +3804,7 @@
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3785,16 +3817,16 @@
         <v>41</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>428</v>
@@ -3805,19 +3837,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>786</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3825,19 +3857,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>786</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -3845,19 +3877,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>786</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3865,19 +3897,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3885,19 +3917,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3905,19 +3937,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
   </sheetData>
